--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU17"/>
+  <dimension ref="A1:AU71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-02 10:30:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-02 11:30:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-02 11:30:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-02 11:30:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-02 12:30:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-02 13:00:00</t>
+          <t>2026-09-02 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-02 14:00:00</t>
+          <t>2026-09-02 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-02 14:30:00</t>
+          <t>2026-09-02 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-02 14:30:00</t>
+          <t>2026-09-02 11:30:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-02 15:00:00</t>
+          <t>2026-09-02 11:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,158 +3033,8960 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Zob Ahan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Paykan</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Segesta Sisak</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kustošija</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dugopolje</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Karlovac 1919</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mladost Ždralovi</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sesvete</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Croatia Zmijavci</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bijelo Brdo</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Jadran LP</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dubrava Zagreb</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Opatija</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hrvace</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Zbrojovka Brno</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hradec Králové</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tallinna FC Flora</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tammeka</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>1.41</v>
+      </c>
+      <c r="O25">
+        <v>4.5</v>
+      </c>
+      <c r="P25">
+        <v>6.17</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Esteghlal</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Persepolis</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Austria Wien</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Abu Qair Semad</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fatih Karagümrük</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kayserispor</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sivasspor</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mardin BB</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Slavia Sofia</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Levski Sofia</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>7</v>
+      </c>
+      <c r="O33">
+        <v>4.2</v>
+      </c>
+      <c r="P33">
+        <v>1.39</v>
+      </c>
+      <c r="Q33">
+        <v>7.28</v>
+      </c>
+      <c r="R33">
+        <v>2.3</v>
+      </c>
+      <c r="S33">
+        <v>1.35</v>
+      </c>
+      <c r="T33">
+        <v>2.85</v>
+      </c>
+      <c r="U33">
+        <v>2.84</v>
+      </c>
+      <c r="V33">
+        <v>1.4</v>
+      </c>
+      <c r="W33">
+        <v>1.06</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.25</v>
+      </c>
+      <c r="Z33">
+        <v>3.47</v>
+      </c>
+      <c r="AA33">
+        <v>1.88</v>
+      </c>
+      <c r="AB33">
+        <v>1.9</v>
+      </c>
+      <c r="AC33">
+        <v>3</v>
+      </c>
+      <c r="AD33">
+        <v>1.31</v>
+      </c>
+      <c r="AE33">
+        <v>1.08</v>
+      </c>
+      <c r="AF33">
+        <v>2.1</v>
+      </c>
+      <c r="AG33">
+        <v>1.65</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>2.8</v>
+      </c>
+      <c r="AK33">
+        <v>1.05</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sanat Naft</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sepahan</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cibalia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Orijent 1919</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aluminij</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>5.06</v>
+      </c>
+      <c r="O36">
+        <v>4.7</v>
+      </c>
+      <c r="P36">
+        <v>1.45</v>
+      </c>
+      <c r="Q36">
+        <v>5</v>
+      </c>
+      <c r="R36">
+        <v>2.63</v>
+      </c>
+      <c r="S36">
+        <v>1.2</v>
+      </c>
+      <c r="T36">
+        <v>4</v>
+      </c>
+      <c r="U36">
+        <v>1.93</v>
+      </c>
+      <c r="V36">
+        <v>1.67</v>
+      </c>
+      <c r="W36">
+        <v>1.17</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.08</v>
+      </c>
+      <c r="Z36">
+        <v>6.5</v>
+      </c>
+      <c r="AA36">
+        <v>1.33</v>
+      </c>
+      <c r="AB36">
+        <v>2.74</v>
+      </c>
+      <c r="AC36">
+        <v>1.96</v>
+      </c>
+      <c r="AD36">
+        <v>1.65</v>
+      </c>
+      <c r="AE36">
+        <v>1.28</v>
+      </c>
+      <c r="AF36">
+        <v>1.47</v>
+      </c>
+      <c r="AG36">
+        <v>2.5</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.13</v>
+      </c>
+      <c r="AK36">
+        <v>1.1</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bohemians 1905</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jablonec</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>2.45</v>
+      </c>
+      <c r="O37">
+        <v>3.4</v>
+      </c>
+      <c r="P37">
+        <v>2.62</v>
+      </c>
+      <c r="Q37">
+        <v>3.2</v>
+      </c>
+      <c r="R37">
+        <v>2.05</v>
+      </c>
+      <c r="S37">
+        <v>1.4</v>
+      </c>
+      <c r="T37">
+        <v>2.56</v>
+      </c>
+      <c r="U37">
+        <v>2.84</v>
+      </c>
+      <c r="V37">
+        <v>1.36</v>
+      </c>
+      <c r="W37">
+        <v>1.04</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37">
+        <v>1.33</v>
+      </c>
+      <c r="Z37">
+        <v>3.24</v>
+      </c>
+      <c r="AA37">
+        <v>2.05</v>
+      </c>
+      <c r="AB37">
+        <v>1.81</v>
+      </c>
+      <c r="AC37">
+        <v>3.28</v>
+      </c>
+      <c r="AD37">
+        <v>1.25</v>
+      </c>
+      <c r="AE37">
+        <v>1.08</v>
+      </c>
+      <c r="AF37">
+        <v>1.75</v>
+      </c>
+      <c r="AG37">
+        <v>1.95</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.3</v>
+      </c>
+      <c r="AK37">
+        <v>1.47</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vaduz</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rapid Wien</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Belgium Pro League</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Union Saint-Gilloise</t>
         </is>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-1</v>
-      </c>
-      <c r="AN17">
-        <v>-1</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>-1</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>2026-09-02 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Cardiff City</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Dundee</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blackpool</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Wigan Athletic</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Luton Town</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Stockport County</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1</v>
+      </c>
+      <c r="AN53">
+        <v>-1</v>
+      </c>
+      <c r="AO53">
+        <v>-1</v>
+      </c>
+      <c r="AP53">
+        <v>-1</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>-1</v>
+      </c>
+      <c r="AN54">
+        <v>-1</v>
+      </c>
+      <c r="AO54">
+        <v>-1</v>
+      </c>
+      <c r="AP54">
+        <v>-1</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-1</v>
+      </c>
+      <c r="AN55">
+        <v>-1</v>
+      </c>
+      <c r="AO55">
+        <v>-1</v>
+      </c>
+      <c r="AP55">
+        <v>-1</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Falkirk</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>-1</v>
+      </c>
+      <c r="AN57">
+        <v>-1</v>
+      </c>
+      <c r="AO57">
+        <v>-1</v>
+      </c>
+      <c r="AP57">
+        <v>-1</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mansfield Town</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-09-02 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N60">
+        <v>1.36</v>
+      </c>
+      <c r="O60">
+        <v>4.6</v>
+      </c>
+      <c r="P60">
+        <v>7.7</v>
+      </c>
+      <c r="Q60">
+        <v>1.83</v>
+      </c>
+      <c r="R60">
+        <v>2.33</v>
+      </c>
+      <c r="S60">
+        <v>1.34</v>
+      </c>
+      <c r="T60">
+        <v>2.91</v>
+      </c>
+      <c r="U60">
+        <v>2.45</v>
+      </c>
+      <c r="V60">
+        <v>1.5</v>
+      </c>
+      <c r="W60">
+        <v>1.11</v>
+      </c>
+      <c r="X60">
+        <v>1.03</v>
+      </c>
+      <c r="Y60">
+        <v>1.17</v>
+      </c>
+      <c r="Z60">
+        <v>4.1</v>
+      </c>
+      <c r="AA60">
+        <v>1.7</v>
+      </c>
+      <c r="AB60">
+        <v>2.04</v>
+      </c>
+      <c r="AC60">
+        <v>2.75</v>
+      </c>
+      <c r="AD60">
+        <v>1.4</v>
+      </c>
+      <c r="AE60">
+        <v>1.11</v>
+      </c>
+      <c r="AF60">
+        <v>1.9</v>
+      </c>
+      <c r="AG60">
+        <v>1.8</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.16</v>
+      </c>
+      <c r="AK60">
+        <v>2.88</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-1</v>
+      </c>
+      <c r="AN60">
+        <v>-1</v>
+      </c>
+      <c r="AO60">
+        <v>-1</v>
+      </c>
+      <c r="AP60">
+        <v>-1</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-09-02 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N61">
+        <v>1.4</v>
+      </c>
+      <c r="O61">
+        <v>4.33</v>
+      </c>
+      <c r="P61">
+        <v>8.5</v>
+      </c>
+      <c r="Q61">
+        <v>1.91</v>
+      </c>
+      <c r="R61">
+        <v>2.3</v>
+      </c>
+      <c r="S61">
+        <v>1.37</v>
+      </c>
+      <c r="T61">
+        <v>2.9</v>
+      </c>
+      <c r="U61">
+        <v>2.7</v>
+      </c>
+      <c r="V61">
+        <v>1.4</v>
+      </c>
+      <c r="W61">
+        <v>1.08</v>
+      </c>
+      <c r="X61">
+        <v>1.04</v>
+      </c>
+      <c r="Y61">
+        <v>1.25</v>
+      </c>
+      <c r="Z61">
+        <v>3.55</v>
+      </c>
+      <c r="AA61">
+        <v>1.89</v>
+      </c>
+      <c r="AB61">
+        <v>1.91</v>
+      </c>
+      <c r="AC61">
+        <v>3.1</v>
+      </c>
+      <c r="AD61">
+        <v>1.35</v>
+      </c>
+      <c r="AE61">
+        <v>1.09</v>
+      </c>
+      <c r="AF61">
+        <v>2.05</v>
+      </c>
+      <c r="AG61">
+        <v>1.75</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.22</v>
+      </c>
+      <c r="AK61">
+        <v>2.75</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>-1</v>
+      </c>
+      <c r="AN61">
+        <v>-1</v>
+      </c>
+      <c r="AO61">
+        <v>-1</v>
+      </c>
+      <c r="AP61">
+        <v>-1</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-09-02 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>0</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-1</v>
+      </c>
+      <c r="AN62">
+        <v>-1</v>
+      </c>
+      <c r="AO62">
+        <v>-1</v>
+      </c>
+      <c r="AP62">
+        <v>-1</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Midland</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>2.26</v>
+      </c>
+      <c r="O63">
+        <v>2.7</v>
+      </c>
+      <c r="P63">
+        <v>3.6</v>
+      </c>
+      <c r="Q63">
+        <v>3</v>
+      </c>
+      <c r="R63">
+        <v>1.71</v>
+      </c>
+      <c r="S63">
+        <v>1.59</v>
+      </c>
+      <c r="T63">
+        <v>2.33</v>
+      </c>
+      <c r="U63">
+        <v>3.6</v>
+      </c>
+      <c r="V63">
+        <v>1.15</v>
+      </c>
+      <c r="W63">
+        <v>1.04</v>
+      </c>
+      <c r="X63">
+        <v>1.1</v>
+      </c>
+      <c r="Y63">
+        <v>1.65</v>
+      </c>
+      <c r="Z63">
+        <v>2.11</v>
+      </c>
+      <c r="AA63">
+        <v>3.1</v>
+      </c>
+      <c r="AB63">
+        <v>1.3</v>
+      </c>
+      <c r="AC63">
+        <v>6.4</v>
+      </c>
+      <c r="AD63">
+        <v>1.05</v>
+      </c>
+      <c r="AE63">
+        <v>1.02</v>
+      </c>
+      <c r="AF63">
+        <v>2.25</v>
+      </c>
+      <c r="AG63">
+        <v>1.51</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>1.36</v>
+      </c>
+      <c r="AK63">
+        <v>1.53</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AGMK</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CSD Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Al Arabi</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Al Hussein</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Al Jazeera</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Shabab Al Ordon</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Al Ramtha</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Al Buqa'a</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Doqarah</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Al Wihdat</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Al Faisaly</t>
+        </is>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>2.2</v>
+      </c>
+      <c r="O71">
+        <v>3.4</v>
+      </c>
+      <c r="P71">
+        <v>2.9</v>
+      </c>
+      <c r="Q71">
+        <v>2.94</v>
+      </c>
+      <c r="R71">
+        <v>2.15</v>
+      </c>
+      <c r="S71">
+        <v>1.3</v>
+      </c>
+      <c r="T71">
+        <v>2.82</v>
+      </c>
+      <c r="U71">
+        <v>2.48</v>
+      </c>
+      <c r="V71">
+        <v>1.45</v>
+      </c>
+      <c r="W71">
+        <v>1.1</v>
+      </c>
+      <c r="X71">
+        <v>1.05</v>
+      </c>
+      <c r="Y71">
+        <v>1.25</v>
+      </c>
+      <c r="Z71">
+        <v>3.5</v>
+      </c>
+      <c r="AA71">
+        <v>1.79</v>
+      </c>
+      <c r="AB71">
+        <v>1.91</v>
+      </c>
+      <c r="AC71">
+        <v>2.88</v>
+      </c>
+      <c r="AD71">
+        <v>1.36</v>
+      </c>
+      <c r="AE71">
+        <v>1.08</v>
+      </c>
+      <c r="AF71">
+        <v>1.63</v>
+      </c>
+      <c r="AG71">
+        <v>2.15</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.3</v>
+      </c>
+      <c r="AK71">
+        <v>1.6</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU71"/>
+  <dimension ref="A1:AU72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G11">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G31">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G35">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-02 15:00:00</t>
+          <t>2026-09-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
-        <v>2.45</v>
+        <v>5.06</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="P37">
-        <v>2.62</v>
+        <v>1.45</v>
       </c>
       <c r="Q37">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.84</v>
+        <v>1.93</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.08</v>
+      </c>
+      <c r="Z37">
+        <v>6.5</v>
+      </c>
+      <c r="AA37">
         <v>1.33</v>
       </c>
-      <c r="Z37">
-        <v>3.24</v>
-      </c>
-      <c r="AA37">
-        <v>2.05</v>
-      </c>
       <c r="AB37">
-        <v>1.81</v>
+        <v>2.74</v>
       </c>
       <c r="AC37">
-        <v>3.28</v>
+        <v>1.96</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:00</t>
+          <t>2026-09-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-02 15:45:00</t>
+          <t>2026-09-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G54">
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-02 16:00:00</t>
+          <t>2026-09-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G58">
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-02 18:30:00</t>
+          <t>2026-09-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,68 +10085,68 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-02 19:00:00</t>
+          <t>2026-09-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>1.36</v>
+      </c>
+      <c r="O61">
+        <v>4.6</v>
+      </c>
+      <c r="P61">
+        <v>7.7</v>
+      </c>
+      <c r="Q61">
+        <v>1.83</v>
+      </c>
+      <c r="R61">
+        <v>2.33</v>
+      </c>
+      <c r="S61">
+        <v>1.34</v>
+      </c>
+      <c r="T61">
+        <v>2.91</v>
+      </c>
+      <c r="U61">
+        <v>2.45</v>
+      </c>
+      <c r="V61">
+        <v>1.5</v>
+      </c>
+      <c r="W61">
+        <v>1.11</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.17</v>
+      </c>
+      <c r="Z61">
+        <v>4.1</v>
+      </c>
+      <c r="AA61">
+        <v>1.7</v>
+      </c>
+      <c r="AB61">
+        <v>2.04</v>
+      </c>
+      <c r="AC61">
+        <v>2.75</v>
+      </c>
+      <c r="AD61">
         <v>1.4</v>
       </c>
-      <c r="O61">
-        <v>4.33</v>
-      </c>
-      <c r="P61">
-        <v>8.5</v>
-      </c>
-      <c r="Q61">
-        <v>1.91</v>
-      </c>
-      <c r="R61">
-        <v>2.3</v>
-      </c>
-      <c r="S61">
-        <v>1.37</v>
-      </c>
-      <c r="T61">
-        <v>2.9</v>
-      </c>
-      <c r="U61">
-        <v>2.7</v>
-      </c>
-      <c r="V61">
-        <v>1.4</v>
-      </c>
-      <c r="W61">
-        <v>1.08</v>
-      </c>
-      <c r="X61">
-        <v>1.04</v>
-      </c>
-      <c r="Y61">
-        <v>1.25</v>
-      </c>
-      <c r="Z61">
-        <v>3.55</v>
-      </c>
-      <c r="AA61">
-        <v>1.89</v>
-      </c>
-      <c r="AB61">
-        <v>1.91</v>
-      </c>
-      <c r="AC61">
-        <v>3.1</v>
-      </c>
-      <c r="AD61">
-        <v>1.35</v>
-      </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG61">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-09-02 19:30:00</t>
+          <t>2026-09-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,68 +10411,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-09-02 20:00:00</t>
+          <t>2026-09-02 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-02 21:00:00</t>
+          <t>2026-09-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G70">
@@ -11835,156 +11835,319 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Al Wihdat</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Al Faisaly</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
+        <v>0</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Ñublense</t>
         </is>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N71">
+      <c r="N72">
         <v>2.2</v>
       </c>
-      <c r="O71">
+      <c r="O72">
         <v>3.4</v>
       </c>
-      <c r="P71">
+      <c r="P72">
         <v>2.9</v>
       </c>
-      <c r="Q71">
+      <c r="Q72">
         <v>2.94</v>
       </c>
-      <c r="R71">
+      <c r="R72">
         <v>2.15</v>
       </c>
-      <c r="S71">
+      <c r="S72">
         <v>1.3</v>
       </c>
-      <c r="T71">
+      <c r="T72">
         <v>2.82</v>
       </c>
-      <c r="U71">
+      <c r="U72">
         <v>2.48</v>
       </c>
-      <c r="V71">
+      <c r="V72">
         <v>1.45</v>
       </c>
-      <c r="W71">
+      <c r="W72">
         <v>1.1</v>
       </c>
-      <c r="X71">
+      <c r="X72">
         <v>1.05</v>
       </c>
-      <c r="Y71">
+      <c r="Y72">
         <v>1.25</v>
       </c>
-      <c r="Z71">
+      <c r="Z72">
         <v>3.5</v>
       </c>
-      <c r="AA71">
+      <c r="AA72">
         <v>1.79</v>
       </c>
-      <c r="AB71">
+      <c r="AB72">
         <v>1.91</v>
       </c>
-      <c r="AC71">
+      <c r="AC72">
         <v>2.88</v>
       </c>
-      <c r="AD71">
+      <c r="AD72">
         <v>1.36</v>
       </c>
-      <c r="AE71">
+      <c r="AE72">
         <v>1.08</v>
       </c>
-      <c r="AF71">
+      <c r="AF72">
         <v>1.63</v>
       </c>
-      <c r="AG71">
+      <c r="AG72">
         <v>2.15</v>
       </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.3</v>
       </c>
-      <c r="AK71">
+      <c r="AK72">
         <v>1.6</v>
       </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>-1</v>
+      </c>
+      <c r="AN72">
+        <v>-1</v>
+      </c>
+      <c r="AO72">
+        <v>-1</v>
+      </c>
+      <c r="AP72">
+        <v>-1</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G11">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G70">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -12041,7 +12041,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N72">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU72"/>
+  <dimension ref="A1:AU71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G70">
@@ -11835,27 +11835,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -11985,169 +11985,6 @@
         <v>0</v>
       </c>
       <c r="AU71" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Ñublense</t>
-        </is>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N72">
-        <v>2.2</v>
-      </c>
-      <c r="O72">
-        <v>3.4</v>
-      </c>
-      <c r="P72">
-        <v>2.9</v>
-      </c>
-      <c r="Q72">
-        <v>2.94</v>
-      </c>
-      <c r="R72">
-        <v>2.15</v>
-      </c>
-      <c r="S72">
-        <v>1.3</v>
-      </c>
-      <c r="T72">
-        <v>2.82</v>
-      </c>
-      <c r="U72">
-        <v>2.48</v>
-      </c>
-      <c r="V72">
-        <v>1.45</v>
-      </c>
-      <c r="W72">
-        <v>1.1</v>
-      </c>
-      <c r="X72">
-        <v>1.05</v>
-      </c>
-      <c r="Y72">
-        <v>1.25</v>
-      </c>
-      <c r="Z72">
-        <v>3.5</v>
-      </c>
-      <c r="AA72">
-        <v>1.79</v>
-      </c>
-      <c r="AB72">
-        <v>1.91</v>
-      </c>
-      <c r="AC72">
-        <v>2.88</v>
-      </c>
-      <c r="AD72">
-        <v>1.36</v>
-      </c>
-      <c r="AE72">
-        <v>1.08</v>
-      </c>
-      <c r="AF72">
-        <v>1.63</v>
-      </c>
-      <c r="AG72">
-        <v>2.15</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.3</v>
-      </c>
-      <c r="AK72">
-        <v>1.6</v>
-      </c>
-      <c r="AL72">
-        <v>0</v>
-      </c>
-      <c r="AM72">
-        <v>-1</v>
-      </c>
-      <c r="AN72">
-        <v>-1</v>
-      </c>
-      <c r="AO72">
-        <v>-1</v>
-      </c>
-      <c r="AP72">
-        <v>-1</v>
-      </c>
-      <c r="AQ72">
-        <v>0</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
-        <v>0</v>
-      </c>
-      <c r="AT72">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G55">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU71"/>
+  <dimension ref="A1:AU78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G65">
@@ -10900,68 +10900,68 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G66">
@@ -11063,68 +11063,68 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G67">
@@ -11226,68 +11226,68 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G68">
@@ -11389,68 +11389,68 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G69">
@@ -11552,68 +11552,68 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G70">
@@ -11715,68 +11715,68 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11835,27 +11835,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G71">
@@ -11878,113 +11878,1254 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71">
+        <v>1.46</v>
+      </c>
+      <c r="O71">
+        <v>4.2</v>
+      </c>
+      <c r="P71">
+        <v>6.56</v>
+      </c>
+      <c r="Q71">
+        <v>2.04</v>
+      </c>
+      <c r="R71">
         <v>2.2</v>
       </c>
-      <c r="O71">
-        <v>3.4</v>
-      </c>
-      <c r="P71">
+      <c r="S71">
+        <v>1.4</v>
+      </c>
+      <c r="T71">
+        <v>2.7</v>
+      </c>
+      <c r="U71">
         <v>2.9</v>
       </c>
-      <c r="Q71">
-        <v>2.94</v>
-      </c>
-      <c r="R71">
-        <v>2.15</v>
-      </c>
-      <c r="S71">
+      <c r="V71">
+        <v>1.35</v>
+      </c>
+      <c r="W71">
+        <v>1.08</v>
+      </c>
+      <c r="X71">
+        <v>1.02</v>
+      </c>
+      <c r="Y71">
         <v>1.3</v>
       </c>
-      <c r="T71">
-        <v>2.82</v>
-      </c>
-      <c r="U71">
-        <v>2.48</v>
-      </c>
-      <c r="V71">
-        <v>1.45</v>
-      </c>
-      <c r="W71">
-        <v>1.1</v>
-      </c>
-      <c r="X71">
-        <v>1.05</v>
-      </c>
-      <c r="Y71">
-        <v>1.25</v>
-      </c>
       <c r="Z71">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA71">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AB71">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC71">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE71">
         <v>1.08</v>
       </c>
       <c r="AF71">
+        <v>2.1</v>
+      </c>
+      <c r="AG71">
+        <v>1.67</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.19</v>
+      </c>
+      <c r="AK71">
+        <v>2.55</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CSD Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>-1</v>
+      </c>
+      <c r="AN72">
+        <v>-1</v>
+      </c>
+      <c r="AO72">
+        <v>-1</v>
+      </c>
+      <c r="AP72">
+        <v>-1</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Al Hussein</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Al Jazeera</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-1</v>
+      </c>
+      <c r="AN73">
+        <v>-1</v>
+      </c>
+      <c r="AO73">
+        <v>-1</v>
+      </c>
+      <c r="AP73">
+        <v>-1</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Al Buqa'a</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Doqarah</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>-1</v>
+      </c>
+      <c r="AN74">
+        <v>-1</v>
+      </c>
+      <c r="AO74">
+        <v>-1</v>
+      </c>
+      <c r="AP74">
+        <v>-1</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>0</v>
+      </c>
+      <c r="AS74">
+        <v>0</v>
+      </c>
+      <c r="AT74">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Al Arabi</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>-1</v>
+      </c>
+      <c r="AN75">
+        <v>-1</v>
+      </c>
+      <c r="AO75">
+        <v>-1</v>
+      </c>
+      <c r="AP75">
+        <v>-1</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>0</v>
+      </c>
+      <c r="AT75">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Shabab Al Ordon</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Al Ramtha</t>
+        </is>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+      <c r="AG76">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
+        <v>0</v>
+      </c>
+      <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>-1</v>
+      </c>
+      <c r="AN76">
+        <v>-1</v>
+      </c>
+      <c r="AO76">
+        <v>-1</v>
+      </c>
+      <c r="AP76">
+        <v>-1</v>
+      </c>
+      <c r="AQ76">
+        <v>0</v>
+      </c>
+      <c r="AR76">
+        <v>0</v>
+      </c>
+      <c r="AS76">
+        <v>0</v>
+      </c>
+      <c r="AT76">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Al Wihdat</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Al Faisaly</t>
+        </is>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>-1</v>
+      </c>
+      <c r="AN77">
+        <v>-1</v>
+      </c>
+      <c r="AO77">
+        <v>-1</v>
+      </c>
+      <c r="AP77">
+        <v>-1</v>
+      </c>
+      <c r="AQ77">
+        <v>0</v>
+      </c>
+      <c r="AR77">
+        <v>0</v>
+      </c>
+      <c r="AS77">
+        <v>0</v>
+      </c>
+      <c r="AT77">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N78">
+        <v>2.2</v>
+      </c>
+      <c r="O78">
+        <v>3.4</v>
+      </c>
+      <c r="P78">
+        <v>2.9</v>
+      </c>
+      <c r="Q78">
+        <v>2.94</v>
+      </c>
+      <c r="R78">
+        <v>2.15</v>
+      </c>
+      <c r="S78">
+        <v>1.3</v>
+      </c>
+      <c r="T78">
+        <v>2.82</v>
+      </c>
+      <c r="U78">
+        <v>2.48</v>
+      </c>
+      <c r="V78">
+        <v>1.45</v>
+      </c>
+      <c r="W78">
+        <v>1.1</v>
+      </c>
+      <c r="X78">
+        <v>1.05</v>
+      </c>
+      <c r="Y78">
+        <v>1.25</v>
+      </c>
+      <c r="Z78">
+        <v>3.5</v>
+      </c>
+      <c r="AA78">
+        <v>1.79</v>
+      </c>
+      <c r="AB78">
+        <v>1.91</v>
+      </c>
+      <c r="AC78">
+        <v>2.88</v>
+      </c>
+      <c r="AD78">
+        <v>1.36</v>
+      </c>
+      <c r="AE78">
+        <v>1.08</v>
+      </c>
+      <c r="AF78">
         <v>1.63</v>
       </c>
-      <c r="AG71">
+      <c r="AG78">
         <v>2.15</v>
       </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.3</v>
       </c>
-      <c r="AK71">
+      <c r="AK78">
         <v>1.6</v>
       </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>-1</v>
+      </c>
+      <c r="AN78">
+        <v>-1</v>
+      </c>
+      <c r="AO78">
+        <v>-1</v>
+      </c>
+      <c r="AP78">
+        <v>-1</v>
+      </c>
+      <c r="AQ78">
+        <v>0</v>
+      </c>
+      <c r="AR78">
+        <v>0</v>
+      </c>
+      <c r="AS78">
+        <v>0</v>
+      </c>
+      <c r="AT78">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G22">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU78"/>
+  <dimension ref="A1:AU79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G42">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.64</v>
+        <v>2.08</v>
       </c>
       <c r="O66">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P66">
-        <v>2.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q66">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="R66">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T66">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U66">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="V66">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W66">
         <v>1.04</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="Z66">
+        <v>2.52</v>
+      </c>
+      <c r="AA66">
         <v>2.39</v>
       </c>
-      <c r="AA66">
-        <v>2.56</v>
-      </c>
       <c r="AB66">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC66">
-        <v>5.15</v>
+        <v>4.45</v>
       </c>
       <c r="AD66">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG66">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.08</v>
+        <v>5.27</v>
       </c>
       <c r="O67">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q67">
-        <v>2.86</v>
+        <v>6.2</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S67">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T67">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U67">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V67">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y67">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="Z67">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AA67">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AB67">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AC67">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AD67">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AG67">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>5.27</v>
+        <v>1.48</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>1.67</v>
+        <v>6.5</v>
       </c>
       <c r="Q68">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="R68">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T68">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="U68">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="V68">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W68">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y68">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="Z68">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AA68">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB68">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AC68">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD68">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE68">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AG68">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK68">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="O69">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>6.5</v>
+        <v>5.53</v>
       </c>
       <c r="Q69">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="R69">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S69">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T69">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U69">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V69">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
         <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z69">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AA69">
         <v>2.35</v>
       </c>
       <c r="AB69">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC69">
         <v>4.33</v>
       </c>
       <c r="AD69">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AE69">
         <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AG69">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK69">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G72">
@@ -12041,68 +12041,68 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G75">
@@ -12976,156 +12976,319 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Al Arabi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78">
+        <v>0</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+      <c r="AG78">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>0</v>
+      </c>
+      <c r="AK78">
+        <v>0</v>
+      </c>
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>-1</v>
+      </c>
+      <c r="AN78">
+        <v>-1</v>
+      </c>
+      <c r="AO78">
+        <v>-1</v>
+      </c>
+      <c r="AP78">
+        <v>-1</v>
+      </c>
+      <c r="AQ78">
+        <v>0</v>
+      </c>
+      <c r="AR78">
+        <v>0</v>
+      </c>
+      <c r="AS78">
+        <v>0</v>
+      </c>
+      <c r="AT78">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Ñublense</t>
         </is>
       </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78" t="inlineStr">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N78">
+      <c r="N79">
         <v>2.2</v>
       </c>
-      <c r="O78">
+      <c r="O79">
         <v>3.4</v>
       </c>
-      <c r="P78">
+      <c r="P79">
         <v>2.9</v>
       </c>
-      <c r="Q78">
+      <c r="Q79">
         <v>2.94</v>
       </c>
-      <c r="R78">
+      <c r="R79">
         <v>2.15</v>
       </c>
-      <c r="S78">
+      <c r="S79">
         <v>1.3</v>
       </c>
-      <c r="T78">
+      <c r="T79">
         <v>2.82</v>
       </c>
-      <c r="U78">
+      <c r="U79">
         <v>2.48</v>
       </c>
-      <c r="V78">
+      <c r="V79">
         <v>1.45</v>
       </c>
-      <c r="W78">
+      <c r="W79">
         <v>1.1</v>
       </c>
-      <c r="X78">
+      <c r="X79">
         <v>1.05</v>
       </c>
-      <c r="Y78">
+      <c r="Y79">
         <v>1.25</v>
       </c>
-      <c r="Z78">
+      <c r="Z79">
         <v>3.5</v>
       </c>
-      <c r="AA78">
+      <c r="AA79">
         <v>1.79</v>
       </c>
-      <c r="AB78">
+      <c r="AB79">
         <v>1.91</v>
       </c>
-      <c r="AC78">
+      <c r="AC79">
         <v>2.88</v>
       </c>
-      <c r="AD78">
+      <c r="AD79">
         <v>1.36</v>
       </c>
-      <c r="AE78">
+      <c r="AE79">
         <v>1.08</v>
       </c>
-      <c r="AF78">
+      <c r="AF79">
         <v>1.63</v>
       </c>
-      <c r="AG78">
+      <c r="AG79">
         <v>2.15</v>
       </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.3</v>
       </c>
-      <c r="AK78">
+      <c r="AK79">
         <v>1.6</v>
       </c>
-      <c r="AL78">
-        <v>0</v>
-      </c>
-      <c r="AM78">
-        <v>-1</v>
-      </c>
-      <c r="AN78">
-        <v>-1</v>
-      </c>
-      <c r="AO78">
-        <v>-1</v>
-      </c>
-      <c r="AP78">
-        <v>-1</v>
-      </c>
-      <c r="AQ78">
-        <v>0</v>
-      </c>
-      <c r="AR78">
-        <v>0</v>
-      </c>
-      <c r="AS78">
-        <v>0</v>
-      </c>
-      <c r="AT78">
-        <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>-1</v>
+      </c>
+      <c r="AN79">
+        <v>-1</v>
+      </c>
+      <c r="AO79">
+        <v>-1</v>
+      </c>
+      <c r="AP79">
+        <v>-1</v>
+      </c>
+      <c r="AQ79">
+        <v>0</v>
+      </c>
+      <c r="AR79">
+        <v>0</v>
+      </c>
+      <c r="AS79">
+        <v>0</v>
+      </c>
+      <c r="AT79">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G17">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q13">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU79"/>
+  <dimension ref="A1:AU75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G22">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.02</v>
+        <v>5.27</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>3.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q65">
-        <v>2.77</v>
+        <v>6.2</v>
       </c>
       <c r="R65">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S65">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T65">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U65">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V65">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y65">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Z65">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AA65">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AB65">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AC65">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AD65">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="O66">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="Q66">
-        <v>2.86</v>
+        <v>2.18</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T66">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U66">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="V66">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.05</v>
@@ -11106,25 +11106,25 @@
         <v>2.52</v>
       </c>
       <c r="AA66">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AB66">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AC66">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AD66">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG66">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>5.27</v>
+        <v>2.5</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P67">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="Q67">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="R67">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S67">
         <v>1.51</v>
       </c>
       <c r="T67">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U67">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="V67">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W67">
         <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z67">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AA67">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AB67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC67">
         <v>4.6</v>
       </c>
       <c r="AD67">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF67">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AG67">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.48</v>
+        <v>3.64</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P68">
-        <v>6.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q68">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S68">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="T68">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U68">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
       <c r="V68">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y68">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="Z68">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AA68">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AB68">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC68">
-        <v>4.33</v>
+        <v>5.15</v>
       </c>
       <c r="AD68">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF68">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AG68">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="AK68">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G69">
@@ -11552,68 +11552,68 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N69">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X69">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK69">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G70">
@@ -11715,68 +11715,68 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N70">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X70">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK70">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G71">
@@ -11878,68 +11878,68 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T71">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U71">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V71">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y71">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z71">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC71">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD71">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG71">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK71">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G72">
@@ -12041,68 +12041,68 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N72">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S72">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T72">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U72">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V72">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X72">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z72">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA72">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AD72">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG72">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AK72">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G74">
@@ -12487,27 +12487,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12637,658 +12637,6 @@
         <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Shabab Al Ordon</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Al Ramtha</t>
-        </is>
-      </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76">
-        <v>0</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>0</v>
-      </c>
-      <c r="Z76">
-        <v>0</v>
-      </c>
-      <c r="AA76">
-        <v>0</v>
-      </c>
-      <c r="AB76">
-        <v>0</v>
-      </c>
-      <c r="AC76">
-        <v>0</v>
-      </c>
-      <c r="AD76">
-        <v>0</v>
-      </c>
-      <c r="AE76">
-        <v>0</v>
-      </c>
-      <c r="AF76">
-        <v>0</v>
-      </c>
-      <c r="AG76">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>0</v>
-      </c>
-      <c r="AK76">
-        <v>0</v>
-      </c>
-      <c r="AL76">
-        <v>0</v>
-      </c>
-      <c r="AM76">
-        <v>-1</v>
-      </c>
-      <c r="AN76">
-        <v>-1</v>
-      </c>
-      <c r="AO76">
-        <v>-1</v>
-      </c>
-      <c r="AP76">
-        <v>-1</v>
-      </c>
-      <c r="AQ76">
-        <v>0</v>
-      </c>
-      <c r="AR76">
-        <v>0</v>
-      </c>
-      <c r="AS76">
-        <v>0</v>
-      </c>
-      <c r="AT76">
-        <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Al Wihdat</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Al Faisaly</t>
-        </is>
-      </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <v>0</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>0</v>
-      </c>
-      <c r="AB77">
-        <v>0</v>
-      </c>
-      <c r="AC77">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>0</v>
-      </c>
-      <c r="AE77">
-        <v>0</v>
-      </c>
-      <c r="AF77">
-        <v>0</v>
-      </c>
-      <c r="AG77">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>0</v>
-      </c>
-      <c r="AK77">
-        <v>0</v>
-      </c>
-      <c r="AL77">
-        <v>0</v>
-      </c>
-      <c r="AM77">
-        <v>-1</v>
-      </c>
-      <c r="AN77">
-        <v>-1</v>
-      </c>
-      <c r="AO77">
-        <v>-1</v>
-      </c>
-      <c r="AP77">
-        <v>-1</v>
-      </c>
-      <c r="AQ77">
-        <v>0</v>
-      </c>
-      <c r="AR77">
-        <v>0</v>
-      </c>
-      <c r="AS77">
-        <v>0</v>
-      </c>
-      <c r="AT77">
-        <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Al Arabi</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Al Salt</t>
-        </is>
-      </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>0</v>
-      </c>
-      <c r="R78">
-        <v>0</v>
-      </c>
-      <c r="S78">
-        <v>0</v>
-      </c>
-      <c r="T78">
-        <v>0</v>
-      </c>
-      <c r="U78">
-        <v>0</v>
-      </c>
-      <c r="V78">
-        <v>0</v>
-      </c>
-      <c r="W78">
-        <v>0</v>
-      </c>
-      <c r="X78">
-        <v>0</v>
-      </c>
-      <c r="Y78">
-        <v>0</v>
-      </c>
-      <c r="Z78">
-        <v>0</v>
-      </c>
-      <c r="AA78">
-        <v>0</v>
-      </c>
-      <c r="AB78">
-        <v>0</v>
-      </c>
-      <c r="AC78">
-        <v>0</v>
-      </c>
-      <c r="AD78">
-        <v>0</v>
-      </c>
-      <c r="AE78">
-        <v>0</v>
-      </c>
-      <c r="AF78">
-        <v>0</v>
-      </c>
-      <c r="AG78">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>0</v>
-      </c>
-      <c r="AK78">
-        <v>0</v>
-      </c>
-      <c r="AL78">
-        <v>0</v>
-      </c>
-      <c r="AM78">
-        <v>-1</v>
-      </c>
-      <c r="AN78">
-        <v>-1</v>
-      </c>
-      <c r="AO78">
-        <v>-1</v>
-      </c>
-      <c r="AP78">
-        <v>-1</v>
-      </c>
-      <c r="AQ78">
-        <v>0</v>
-      </c>
-      <c r="AR78">
-        <v>0</v>
-      </c>
-      <c r="AS78">
-        <v>0</v>
-      </c>
-      <c r="AT78">
-        <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ñublense</t>
-        </is>
-      </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N79">
-        <v>2.2</v>
-      </c>
-      <c r="O79">
-        <v>3.4</v>
-      </c>
-      <c r="P79">
-        <v>2.9</v>
-      </c>
-      <c r="Q79">
-        <v>2.94</v>
-      </c>
-      <c r="R79">
-        <v>2.15</v>
-      </c>
-      <c r="S79">
-        <v>1.3</v>
-      </c>
-      <c r="T79">
-        <v>2.82</v>
-      </c>
-      <c r="U79">
-        <v>2.48</v>
-      </c>
-      <c r="V79">
-        <v>1.45</v>
-      </c>
-      <c r="W79">
-        <v>1.1</v>
-      </c>
-      <c r="X79">
-        <v>1.05</v>
-      </c>
-      <c r="Y79">
-        <v>1.25</v>
-      </c>
-      <c r="Z79">
-        <v>3.5</v>
-      </c>
-      <c r="AA79">
-        <v>1.79</v>
-      </c>
-      <c r="AB79">
-        <v>1.91</v>
-      </c>
-      <c r="AC79">
-        <v>2.88</v>
-      </c>
-      <c r="AD79">
-        <v>1.36</v>
-      </c>
-      <c r="AE79">
-        <v>1.08</v>
-      </c>
-      <c r="AF79">
-        <v>1.63</v>
-      </c>
-      <c r="AG79">
-        <v>2.15</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.3</v>
-      </c>
-      <c r="AK79">
-        <v>1.6</v>
-      </c>
-      <c r="AL79">
-        <v>0</v>
-      </c>
-      <c r="AM79">
-        <v>-1</v>
-      </c>
-      <c r="AN79">
-        <v>-1</v>
-      </c>
-      <c r="AO79">
-        <v>-1</v>
-      </c>
-      <c r="AP79">
-        <v>-1</v>
-      </c>
-      <c r="AQ79">
-        <v>0</v>
-      </c>
-      <c r="AR79">
-        <v>0</v>
-      </c>
-      <c r="AS79">
-        <v>0</v>
-      </c>
-      <c r="AT79">
-        <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU75"/>
+  <dimension ref="A1:AU73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,55 +2437,55 @@
         <v>2.85</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G22">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G30">
@@ -5208,55 +5208,55 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G31">
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>5.27</v>
+        <v>1.48</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>1.67</v>
+        <v>6.5</v>
       </c>
       <c r="Q65">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="R65">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S65">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T65">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="U65">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="V65">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="Z65">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AA65">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB65">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AC65">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD65">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE65">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AG65">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK65">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.48</v>
+        <v>3.64</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P66">
-        <v>6.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q66">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S66">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="T66">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U66">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
       <c r="V66">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="Z66">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AA66">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AB66">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC66">
-        <v>4.33</v>
+        <v>5.15</v>
       </c>
       <c r="AD66">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AG66">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="AK66">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G67">
@@ -11226,68 +11226,68 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N67">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK67">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G68">
@@ -11389,68 +11389,68 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N68">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,27 +12161,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12311,332 +12311,6 @@
         <v>0</v>
       </c>
       <c r="AU73" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Al Arabi</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Al Salt</t>
-        </is>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>0</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>0</v>
-      </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
-      <c r="W74">
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <v>0</v>
-      </c>
-      <c r="Z74">
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <v>0</v>
-      </c>
-      <c r="AB74">
-        <v>0</v>
-      </c>
-      <c r="AC74">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>0</v>
-      </c>
-      <c r="AE74">
-        <v>0</v>
-      </c>
-      <c r="AF74">
-        <v>0</v>
-      </c>
-      <c r="AG74">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>0</v>
-      </c>
-      <c r="AK74">
-        <v>0</v>
-      </c>
-      <c r="AL74">
-        <v>0</v>
-      </c>
-      <c r="AM74">
-        <v>-1</v>
-      </c>
-      <c r="AN74">
-        <v>-1</v>
-      </c>
-      <c r="AO74">
-        <v>-1</v>
-      </c>
-      <c r="AP74">
-        <v>-1</v>
-      </c>
-      <c r="AQ74">
-        <v>0</v>
-      </c>
-      <c r="AR74">
-        <v>0</v>
-      </c>
-      <c r="AS74">
-        <v>0</v>
-      </c>
-      <c r="AT74">
-        <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Ñublense</t>
-        </is>
-      </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N75">
-        <v>2.2</v>
-      </c>
-      <c r="O75">
-        <v>3.4</v>
-      </c>
-      <c r="P75">
-        <v>2.9</v>
-      </c>
-      <c r="Q75">
-        <v>2.94</v>
-      </c>
-      <c r="R75">
-        <v>2.15</v>
-      </c>
-      <c r="S75">
-        <v>1.3</v>
-      </c>
-      <c r="T75">
-        <v>2.82</v>
-      </c>
-      <c r="U75">
-        <v>2.48</v>
-      </c>
-      <c r="V75">
-        <v>1.45</v>
-      </c>
-      <c r="W75">
-        <v>1.1</v>
-      </c>
-      <c r="X75">
-        <v>1.05</v>
-      </c>
-      <c r="Y75">
-        <v>1.25</v>
-      </c>
-      <c r="Z75">
-        <v>3.5</v>
-      </c>
-      <c r="AA75">
-        <v>1.79</v>
-      </c>
-      <c r="AB75">
-        <v>1.91</v>
-      </c>
-      <c r="AC75">
-        <v>2.88</v>
-      </c>
-      <c r="AD75">
-        <v>1.36</v>
-      </c>
-      <c r="AE75">
-        <v>1.08</v>
-      </c>
-      <c r="AF75">
-        <v>1.63</v>
-      </c>
-      <c r="AG75">
-        <v>2.15</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.3</v>
-      </c>
-      <c r="AK75">
-        <v>1.6</v>
-      </c>
-      <c r="AL75">
-        <v>0</v>
-      </c>
-      <c r="AM75">
-        <v>-1</v>
-      </c>
-      <c r="AN75">
-        <v>-1</v>
-      </c>
-      <c r="AO75">
-        <v>-1</v>
-      </c>
-      <c r="AP75">
-        <v>-1</v>
-      </c>
-      <c r="AQ75">
-        <v>0</v>
-      </c>
-      <c r="AR75">
-        <v>0</v>
-      </c>
-      <c r="AS75">
-        <v>0</v>
-      </c>
-      <c r="AT75">
-        <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="P16">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G30">
@@ -5208,55 +5208,55 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R30">
         <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U30">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z30">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB30">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC30">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AD30">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG30">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G31">
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
         <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U31">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1.26</v>
+      </c>
+      <c r="Z31">
+        <v>3.2</v>
+      </c>
+      <c r="AA31">
+        <v>1.93</v>
+      </c>
+      <c r="AB31">
+        <v>1.71</v>
+      </c>
+      <c r="AC31">
+        <v>3.25</v>
+      </c>
+      <c r="AD31">
+        <v>1.26</v>
+      </c>
+      <c r="AE31">
         <v>1.06</v>
       </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.31</v>
-      </c>
-      <c r="Z31">
-        <v>3</v>
-      </c>
-      <c r="AA31">
-        <v>1.96</v>
-      </c>
-      <c r="AB31">
-        <v>1.68</v>
-      </c>
-      <c r="AC31">
-        <v>3.48</v>
-      </c>
-      <c r="AD31">
-        <v>1.22</v>
-      </c>
-      <c r="AE31">
-        <v>1.05</v>
-      </c>
       <c r="AF31">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G55">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU73"/>
+  <dimension ref="A1:AU76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>6.17</v>
+        <v>2.75</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-02 13:30:00</t>
+          <t>2026-09-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-02 14:00:00</t>
+          <t>2026-09-02 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="T30">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="U30">
-        <v>2.91</v>
+        <v>3.6</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W30">
+        <v>1.03</v>
+      </c>
+      <c r="X30">
         <v>1.06</v>
       </c>
-      <c r="X30">
+      <c r="Y30">
+        <v>1.47</v>
+      </c>
+      <c r="Z30">
+        <v>2.63</v>
+      </c>
+      <c r="AA30">
+        <v>2.44</v>
+      </c>
+      <c r="AB30">
+        <v>1.49</v>
+      </c>
+      <c r="AC30">
+        <v>4.65</v>
+      </c>
+      <c r="AD30">
+        <v>1.12</v>
+      </c>
+      <c r="AE30">
         <v>1.02</v>
       </c>
-      <c r="Y30">
-        <v>1.31</v>
-      </c>
-      <c r="Z30">
-        <v>3</v>
-      </c>
-      <c r="AA30">
-        <v>1.96</v>
-      </c>
-      <c r="AB30">
-        <v>1.68</v>
-      </c>
-      <c r="AC30">
-        <v>3.48</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.05</v>
-      </c>
       <c r="AF30">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK30">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G31">
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
         <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U31">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z31">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA31">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB31">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AD31">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG31">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G32">
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-02 14:30:00</t>
+          <t>2026-09-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-02 15:00:00</t>
+          <t>2026-09-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>2.45</v>
+        <v>5.06</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="P38">
-        <v>2.62</v>
+        <v>1.45</v>
       </c>
       <c r="Q38">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.84</v>
+        <v>1.93</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
+        <v>1.08</v>
+      </c>
+      <c r="Z38">
+        <v>6.5</v>
+      </c>
+      <c r="AA38">
         <v>1.33</v>
       </c>
-      <c r="Z38">
-        <v>3.24</v>
-      </c>
-      <c r="AA38">
-        <v>2.05</v>
-      </c>
       <c r="AB38">
-        <v>1.81</v>
+        <v>2.74</v>
       </c>
       <c r="AC38">
-        <v>3.28</v>
+        <v>1.96</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK38">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
       </c>
       <c r="R39">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S39">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z39">
-        <v>5.1</v>
+        <v>3.24</v>
       </c>
       <c r="AA39">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>2.45</v>
+        <v>3.28</v>
       </c>
       <c r="AD39">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:00</t>
+          <t>2026-09-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-02 15:45:00</t>
+          <t>2026-09-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-02 15:45:00</t>
+          <t>2026-09-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-02 15:45:00</t>
+          <t>2026-09-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>6</v>
+        <v>3.38</v>
       </c>
       <c r="P51">
-        <v>9</v>
+        <v>2.71</v>
       </c>
       <c r="Q51">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="R51">
-        <v>2.78</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.98</v>
+        <v>2.89</v>
       </c>
       <c r="U51">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="V51">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>7</v>
+        <v>3.44</v>
       </c>
       <c r="AA51">
-        <v>1.34</v>
+        <v>1.92</v>
       </c>
       <c r="AB51">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="AD51">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
+        <v>1.09</v>
+      </c>
+      <c r="AF51">
+        <v>1.63</v>
+      </c>
+      <c r="AG51">
+        <v>2.14</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.3</v>
       </c>
-      <c r="AF51">
-        <v>1.7</v>
-      </c>
-      <c r="AG51">
-        <v>2.04</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.11</v>
-      </c>
       <c r="AK51">
-        <v>3.7</v>
+        <v>1.54</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G55">
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-09-02 16:00:00</t>
+          <t>2026-09-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-09-02 16:00:00</t>
+          <t>2026-09-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-09-02 16:00:00</t>
+          <t>2026-09-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-02 18:30:00</t>
+          <t>2026-09-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.36</v>
+        <v>5.35</v>
       </c>
       <c r="O61">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P61">
-        <v>7.7</v>
+        <v>1.57</v>
       </c>
       <c r="Q61">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="R61">
+        <v>2.4</v>
+      </c>
+      <c r="S61">
+        <v>1.25</v>
+      </c>
+      <c r="T61">
+        <v>3.34</v>
+      </c>
+      <c r="U61">
+        <v>2.23</v>
+      </c>
+      <c r="V61">
+        <v>1.58</v>
+      </c>
+      <c r="W61">
+        <v>1.14</v>
+      </c>
+      <c r="X61">
+        <v>1.01</v>
+      </c>
+      <c r="Y61">
+        <v>1.15</v>
+      </c>
+      <c r="Z61">
+        <v>4.65</v>
+      </c>
+      <c r="AA61">
+        <v>1.58</v>
+      </c>
+      <c r="AB61">
         <v>2.33</v>
       </c>
-      <c r="S61">
-        <v>1.34</v>
-      </c>
-      <c r="T61">
-        <v>2.91</v>
-      </c>
-      <c r="U61">
-        <v>2.45</v>
-      </c>
-      <c r="V61">
-        <v>1.5</v>
-      </c>
-      <c r="W61">
-        <v>1.11</v>
-      </c>
-      <c r="X61">
-        <v>1.03</v>
-      </c>
-      <c r="Y61">
-        <v>1.17</v>
-      </c>
-      <c r="Z61">
-        <v>4.1</v>
-      </c>
-      <c r="AA61">
-        <v>1.7</v>
-      </c>
-      <c r="AB61">
-        <v>2.04</v>
-      </c>
       <c r="AC61">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AE61">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF61">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AG61">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>2.88</v>
+        <v>1.13</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-09-02 19:00:00</t>
+          <t>2026-09-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-09-02 19:30:00</t>
+          <t>2026-09-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-02 20:00:00</t>
+          <t>2026-09-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="O64">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="P64">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q64">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="R64">
-        <v>1.71</v>
+        <v>2.33</v>
       </c>
       <c r="S64">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="T64">
-        <v>2.33</v>
+        <v>2.91</v>
       </c>
       <c r="U64">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="V64">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>2.11</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AB64">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="AC64">
-        <v>6.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD64">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF64">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG64">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK64">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-02 20:00:00</t>
+          <t>2026-09-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G65">
@@ -10900,68 +10900,68 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N65">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P65">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q65">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="R65">
+        <v>2.3</v>
+      </c>
+      <c r="S65">
+        <v>1.37</v>
+      </c>
+      <c r="T65">
+        <v>2.9</v>
+      </c>
+      <c r="U65">
+        <v>2.7</v>
+      </c>
+      <c r="V65">
+        <v>1.4</v>
+      </c>
+      <c r="W65">
+        <v>1.08</v>
+      </c>
+      <c r="X65">
+        <v>1.04</v>
+      </c>
+      <c r="Y65">
+        <v>1.25</v>
+      </c>
+      <c r="Z65">
+        <v>3.55</v>
+      </c>
+      <c r="AA65">
+        <v>1.89</v>
+      </c>
+      <c r="AB65">
+        <v>1.91</v>
+      </c>
+      <c r="AC65">
+        <v>3.1</v>
+      </c>
+      <c r="AD65">
+        <v>1.35</v>
+      </c>
+      <c r="AE65">
+        <v>1.09</v>
+      </c>
+      <c r="AF65">
         <v>2.05</v>
       </c>
-      <c r="S65">
-        <v>1.46</v>
-      </c>
-      <c r="T65">
-        <v>2.33</v>
-      </c>
-      <c r="U65">
-        <v>3.32</v>
-      </c>
-      <c r="V65">
-        <v>1.26</v>
-      </c>
-      <c r="W65">
-        <v>1.05</v>
-      </c>
-      <c r="X65">
-        <v>1.05</v>
-      </c>
-      <c r="Y65">
-        <v>1.41</v>
-      </c>
-      <c r="Z65">
-        <v>2.52</v>
-      </c>
-      <c r="AA65">
-        <v>2.35</v>
-      </c>
-      <c r="AB65">
-        <v>1.55</v>
-      </c>
-      <c r="AC65">
-        <v>4.33</v>
-      </c>
-      <c r="AD65">
-        <v>1.11</v>
-      </c>
-      <c r="AE65">
-        <v>1.05</v>
-      </c>
-      <c r="AF65">
-        <v>2.45</v>
-      </c>
       <c r="AG65">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-02 21:00:00</t>
+          <t>2026-09-02 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,27 +11020,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G66">
@@ -11063,68 +11063,68 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N66">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S66">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T66">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U66">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V66">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y66">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z66">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA66">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC66">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE66">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF66">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AK66">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-02 21:00:00</t>
+          <t>2026-09-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-02 21:00:00</t>
+          <t>2026-09-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G68">
@@ -11389,68 +11389,68 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G69">
@@ -11552,68 +11552,68 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,156 +12161,645 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Shabab Al Ordon</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Al Ramtha</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-1</v>
+      </c>
+      <c r="AN73">
+        <v>-1</v>
+      </c>
+      <c r="AO73">
+        <v>-1</v>
+      </c>
+      <c r="AP73">
+        <v>-1</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Al Arabi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>-1</v>
+      </c>
+      <c r="AN74">
+        <v>-1</v>
+      </c>
+      <c r="AO74">
+        <v>-1</v>
+      </c>
+      <c r="AP74">
+        <v>-1</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>0</v>
+      </c>
+      <c r="AS74">
+        <v>0</v>
+      </c>
+      <c r="AT74">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Al Wihdat</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Al Faisaly</t>
+        </is>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>-1</v>
+      </c>
+      <c r="AN75">
+        <v>-1</v>
+      </c>
+      <c r="AO75">
+        <v>-1</v>
+      </c>
+      <c r="AP75">
+        <v>-1</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>0</v>
+      </c>
+      <c r="AT75">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Ñublense</t>
         </is>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73" t="inlineStr">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N73">
+      <c r="N76">
         <v>2.2</v>
       </c>
-      <c r="O73">
+      <c r="O76">
         <v>3.4</v>
       </c>
-      <c r="P73">
+      <c r="P76">
         <v>2.9</v>
       </c>
-      <c r="Q73">
+      <c r="Q76">
         <v>2.94</v>
       </c>
-      <c r="R73">
+      <c r="R76">
         <v>2.15</v>
       </c>
-      <c r="S73">
+      <c r="S76">
         <v>1.3</v>
       </c>
-      <c r="T73">
+      <c r="T76">
         <v>2.82</v>
       </c>
-      <c r="U73">
+      <c r="U76">
         <v>2.48</v>
       </c>
-      <c r="V73">
+      <c r="V76">
         <v>1.45</v>
       </c>
-      <c r="W73">
+      <c r="W76">
         <v>1.1</v>
       </c>
-      <c r="X73">
+      <c r="X76">
         <v>1.05</v>
       </c>
-      <c r="Y73">
+      <c r="Y76">
         <v>1.25</v>
       </c>
-      <c r="Z73">
+      <c r="Z76">
         <v>3.5</v>
       </c>
-      <c r="AA73">
+      <c r="AA76">
         <v>1.79</v>
       </c>
-      <c r="AB73">
+      <c r="AB76">
         <v>1.91</v>
       </c>
-      <c r="AC73">
+      <c r="AC76">
         <v>2.88</v>
       </c>
-      <c r="AD73">
+      <c r="AD76">
         <v>1.36</v>
       </c>
-      <c r="AE73">
+      <c r="AE76">
         <v>1.08</v>
       </c>
-      <c r="AF73">
+      <c r="AF76">
         <v>1.63</v>
       </c>
-      <c r="AG73">
+      <c r="AG76">
         <v>2.15</v>
       </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.3</v>
       </c>
-      <c r="AK73">
+      <c r="AK76">
         <v>1.6</v>
       </c>
-      <c r="AL73">
-        <v>0</v>
-      </c>
-      <c r="AM73">
-        <v>-1</v>
-      </c>
-      <c r="AN73">
-        <v>-1</v>
-      </c>
-      <c r="AO73">
-        <v>-1</v>
-      </c>
-      <c r="AP73">
-        <v>-1</v>
-      </c>
-      <c r="AQ73">
-        <v>0</v>
-      </c>
-      <c r="AR73">
-        <v>0</v>
-      </c>
-      <c r="AS73">
-        <v>0</v>
-      </c>
-      <c r="AT73">
-        <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>-1</v>
+      </c>
+      <c r="AN76">
+        <v>-1</v>
+      </c>
+      <c r="AO76">
+        <v>-1</v>
+      </c>
+      <c r="AP76">
+        <v>-1</v>
+      </c>
+      <c r="AQ76">
+        <v>0</v>
+      </c>
+      <c r="AR76">
+        <v>0</v>
+      </c>
+      <c r="AS76">
+        <v>0</v>
+      </c>
+      <c r="AT76">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="R14">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD14">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O13">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="P13">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="Q13">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R13">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="T13">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="U13">
         <v>4.5</v>
       </c>
       <c r="V13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
         <v>1.01</v>
@@ -2461,10 +2461,10 @@
         <v>1.11</v>
       </c>
       <c r="Y13">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z13">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AA13">
         <v>2.92</v>
@@ -2473,19 +2473,19 @@
         <v>1.31</v>
       </c>
       <c r="AC13">
-        <v>6.05</v>
+        <v>6.6</v>
       </c>
       <c r="AD13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG13">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G31">
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
         <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U31">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1.26</v>
+      </c>
+      <c r="Z31">
+        <v>3.2</v>
+      </c>
+      <c r="AA31">
+        <v>1.93</v>
+      </c>
+      <c r="AB31">
+        <v>1.71</v>
+      </c>
+      <c r="AC31">
+        <v>3.25</v>
+      </c>
+      <c r="AD31">
+        <v>1.26</v>
+      </c>
+      <c r="AE31">
         <v>1.06</v>
       </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.31</v>
-      </c>
-      <c r="Z31">
-        <v>3</v>
-      </c>
-      <c r="AA31">
-        <v>1.96</v>
-      </c>
-      <c r="AB31">
-        <v>1.68</v>
-      </c>
-      <c r="AC31">
-        <v>3.48</v>
-      </c>
-      <c r="AD31">
-        <v>1.22</v>
-      </c>
-      <c r="AE31">
-        <v>1.05</v>
-      </c>
       <c r="AF31">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G32">
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
         <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U32">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA32">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB32">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG32">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6666,37 +6666,37 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
         <v>2.62</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R39">
         <v>2.05</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
         <v>1.33</v>
@@ -6705,25 +6705,25 @@
         <v>3.24</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE39">
         <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G56">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G73">

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
-        <v>2.48</v>
+        <v>4.55</v>
       </c>
       <c r="R2">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.54</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="AB2">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AC2">
-        <v>2.94</v>
+        <v>3.62</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AG2">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK2">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>4.55</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA3">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AB3">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AC3">
-        <v>3.62</v>
+        <v>2.94</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
-        <v>4.3</v>
+        <v>2.94</v>
       </c>
       <c r="R4">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T4">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="U4">
-        <v>2.89</v>
+        <v>3.34</v>
       </c>
       <c r="V4">
+        <v>1.28</v>
+      </c>
+      <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.39</v>
+      </c>
+      <c r="Z4">
+        <v>2.61</v>
+      </c>
+      <c r="AA4">
+        <v>2.38</v>
+      </c>
+      <c r="AB4">
+        <v>1.59</v>
+      </c>
+      <c r="AC4">
+        <v>4.25</v>
+      </c>
+      <c r="AD4">
+        <v>1.15</v>
+      </c>
+      <c r="AE4">
+        <v>1.01</v>
+      </c>
+      <c r="AF4">
+        <v>1.97</v>
+      </c>
+      <c r="AG4">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.36</v>
       </c>
-      <c r="W4">
-        <v>1.04</v>
-      </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
-        <v>1.3</v>
-      </c>
-      <c r="Z4">
-        <v>2.99</v>
-      </c>
-      <c r="AA4">
-        <v>2.04</v>
-      </c>
-      <c r="AB4">
-        <v>1.8</v>
-      </c>
-      <c r="AC4">
-        <v>3.38</v>
-      </c>
-      <c r="AD4">
-        <v>1.24</v>
-      </c>
-      <c r="AE4">
-        <v>1.05</v>
-      </c>
-      <c r="AF4">
-        <v>1.82</v>
-      </c>
-      <c r="AG4">
-        <v>1.88</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.3</v>
-      </c>
       <c r="AK4">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q6">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="R6">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="U6">
-        <v>3.34</v>
+        <v>2.89</v>
       </c>
       <c r="V6">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>2.61</v>
+        <v>2.99</v>
       </c>
       <c r="AA6">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AB6">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>4.25</v>
+        <v>3.38</v>
       </c>
       <c r="AD6">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>2</v>
       </c>
       <c r="Q14">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="R14">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
         <v>1.34</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
         <v>1.28</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
         <v>1.04</v>
@@ -5395,22 +5395,22 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z31">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA31">
         <v>1.93</v>
       </c>
       <c r="AB31">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC31">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
         <v>1.06</v>
@@ -5419,7 +5419,7 @@
         <v>1.71</v>
       </c>
       <c r="AG31">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S32">
         <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V32">
         <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -5561,19 +5561,19 @@
         <v>1.31</v>
       </c>
       <c r="Z32">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA32">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AB32">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC32">
         <v>3.48</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6512,46 +6512,46 @@
         <v>1.45</v>
       </c>
       <c r="Q38">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="S38">
+        <v>1.22</v>
+      </c>
+      <c r="T38">
+        <v>3.75</v>
+      </c>
+      <c r="U38">
+        <v>2.2</v>
+      </c>
+      <c r="V38">
+        <v>1.62</v>
+      </c>
+      <c r="W38">
         <v>1.2</v>
-      </c>
-      <c r="T38">
-        <v>4</v>
-      </c>
-      <c r="U38">
-        <v>1.93</v>
-      </c>
-      <c r="V38">
-        <v>1.67</v>
-      </c>
-      <c r="W38">
-        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z38">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA38">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB38">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC38">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD38">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE38">
         <v>1.28</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
-        <v>4.55</v>
+        <v>2.48</v>
       </c>
       <c r="R2">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA2">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AB2">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AC2">
-        <v>3.62</v>
+        <v>2.94</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>2.41</v>
       </c>
       <c r="U3">
-        <v>2.69</v>
+        <v>3.34</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="Z3">
-        <v>3.54</v>
+        <v>2.61</v>
       </c>
       <c r="AA3">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AB3">
+        <v>1.59</v>
+      </c>
+      <c r="AC3">
+        <v>4.25</v>
+      </c>
+      <c r="AD3">
+        <v>1.15</v>
+      </c>
+      <c r="AE3">
+        <v>1.01</v>
+      </c>
+      <c r="AF3">
         <v>1.97</v>
       </c>
-      <c r="AC3">
-        <v>2.94</v>
-      </c>
-      <c r="AD3">
-        <v>1.31</v>
-      </c>
-      <c r="AE3">
-        <v>1.08</v>
-      </c>
-      <c r="AF3">
-        <v>1.68</v>
-      </c>
       <c r="AG3">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>2.94</v>
+        <v>4.55</v>
       </c>
       <c r="R4">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T4">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="U4">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>1.33</v>
+      </c>
+      <c r="Z4">
+        <v>2.85</v>
+      </c>
+      <c r="AA4">
+        <v>2.16</v>
+      </c>
+      <c r="AB4">
+        <v>1.71</v>
+      </c>
+      <c r="AC4">
+        <v>3.62</v>
+      </c>
+      <c r="AD4">
+        <v>1.21</v>
+      </c>
+      <c r="AE4">
         <v>1.04</v>
       </c>
-      <c r="Y4">
-        <v>1.39</v>
-      </c>
-      <c r="Z4">
-        <v>2.61</v>
-      </c>
-      <c r="AA4">
-        <v>2.38</v>
-      </c>
-      <c r="AB4">
-        <v>1.59</v>
-      </c>
-      <c r="AC4">
-        <v>4.25</v>
-      </c>
-      <c r="AD4">
-        <v>1.15</v>
-      </c>
-      <c r="AE4">
-        <v>1.01</v>
-      </c>
       <c r="AF4">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="R5">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
+        <v>2.69</v>
+      </c>
+      <c r="U5">
+        <v>2.89</v>
+      </c>
+      <c r="V5">
+        <v>1.36</v>
+      </c>
+      <c r="W5">
+        <v>1.04</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.3</v>
+      </c>
+      <c r="Z5">
         <v>2.99</v>
       </c>
-      <c r="U5">
-        <v>2.65</v>
-      </c>
-      <c r="V5">
-        <v>1.42</v>
-      </c>
-      <c r="W5">
+      <c r="AA5">
+        <v>2.04</v>
+      </c>
+      <c r="AB5">
+        <v>1.8</v>
+      </c>
+      <c r="AC5">
+        <v>3.38</v>
+      </c>
+      <c r="AD5">
+        <v>1.24</v>
+      </c>
+      <c r="AE5">
         <v>1.05</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.21</v>
-      </c>
-      <c r="Z5">
-        <v>3.62</v>
-      </c>
-      <c r="AA5">
-        <v>1.85</v>
-      </c>
-      <c r="AB5">
-        <v>1.98</v>
-      </c>
-      <c r="AC5">
-        <v>2.94</v>
-      </c>
-      <c r="AD5">
-        <v>1.31</v>
-      </c>
-      <c r="AE5">
-        <v>1.08</v>
-      </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AG5">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="P6">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Q6">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
+        <v>1.21</v>
+      </c>
+      <c r="Z6">
+        <v>3.62</v>
+      </c>
+      <c r="AA6">
+        <v>1.85</v>
+      </c>
+      <c r="AB6">
+        <v>1.98</v>
+      </c>
+      <c r="AC6">
+        <v>2.94</v>
+      </c>
+      <c r="AD6">
+        <v>1.31</v>
+      </c>
+      <c r="AE6">
+        <v>1.08</v>
+      </c>
+      <c r="AF6">
+        <v>1.65</v>
+      </c>
+      <c r="AG6">
+        <v>2.11</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.25</v>
+      </c>
+      <c r="AK6">
         <v>1.3</v>
-      </c>
-      <c r="Z6">
-        <v>2.99</v>
-      </c>
-      <c r="AA6">
-        <v>2.04</v>
-      </c>
-      <c r="AB6">
-        <v>1.8</v>
-      </c>
-      <c r="AC6">
-        <v>3.38</v>
-      </c>
-      <c r="AD6">
-        <v>1.24</v>
-      </c>
-      <c r="AE6">
-        <v>1.05</v>
-      </c>
-      <c r="AF6">
-        <v>1.82</v>
-      </c>
-      <c r="AG6">
-        <v>1.88</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.3</v>
-      </c>
-      <c r="AK6">
-        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O65">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="P65">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q65">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S65">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V65">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA65">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AB65">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="AD65">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE65">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG65">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK65">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P67">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q67">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R67">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="S67">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="T67">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="U67">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="V67">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y67">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z67">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AA67">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AB67">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC67">
-        <v>6.4</v>
+        <v>6.41</v>
       </c>
       <c r="AD67">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF67">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AG67">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
         <v>1.53</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -662,10 +662,10 @@
         <v>1.41</v>
       </c>
       <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
         <v>1.05</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
       </c>
       <c r="Y2">
         <v>1.22</v>
@@ -674,10 +674,10 @@
         <v>3.54</v>
       </c>
       <c r="AA2">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AB2">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AC2">
         <v>2.94</v>
@@ -686,13 +686,13 @@
         <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
         <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q3">
-        <v>2.94</v>
+        <v>4.52</v>
       </c>
       <c r="R3">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="S3">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="V3">
+        <v>1.37</v>
+      </c>
+      <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
         <v>1.28</v>
       </c>
-      <c r="W3">
-        <v>1.01</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.39</v>
-      </c>
       <c r="Z3">
-        <v>2.61</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AB3">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AC3">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q4">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="R4">
+        <v>2.14</v>
+      </c>
+      <c r="S4">
+        <v>1.34</v>
+      </c>
+      <c r="T4">
+        <v>2.99</v>
+      </c>
+      <c r="U4">
+        <v>2.5</v>
+      </c>
+      <c r="V4">
+        <v>1.45</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.25</v>
+      </c>
+      <c r="Z4">
+        <v>3.7</v>
+      </c>
+      <c r="AA4">
+        <v>1.83</v>
+      </c>
+      <c r="AB4">
         <v>2.01</v>
       </c>
-      <c r="S4">
-        <v>1.45</v>
-      </c>
-      <c r="T4">
-        <v>2.56</v>
-      </c>
-      <c r="U4">
-        <v>3.04</v>
-      </c>
-      <c r="V4">
-        <v>1.33</v>
-      </c>
-      <c r="W4">
-        <v>1.03</v>
-      </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
-      <c r="Y4">
-        <v>1.33</v>
-      </c>
-      <c r="Z4">
-        <v>2.85</v>
-      </c>
-      <c r="AA4">
-        <v>2.16</v>
-      </c>
-      <c r="AB4">
-        <v>1.71</v>
-      </c>
       <c r="AC4">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="AK4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="Q5">
-        <v>4.3</v>
+        <v>2.94</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="S5">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="U5">
-        <v>2.89</v>
+        <v>3.34</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W5">
+        <v>1.01</v>
+      </c>
+      <c r="X5">
         <v>1.04</v>
       </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z5">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AA5">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AC5">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK5">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>3.84</v>
+        <v>4.42</v>
       </c>
       <c r="R6">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
+        <v>2.69</v>
+      </c>
+      <c r="U6">
+        <v>2.89</v>
+      </c>
+      <c r="V6">
+        <v>1.37</v>
+      </c>
+      <c r="W6">
+        <v>1.04</v>
+      </c>
+      <c r="X6">
+        <v>1.04</v>
+      </c>
+      <c r="Y6">
+        <v>1.3</v>
+      </c>
+      <c r="Z6">
         <v>2.99</v>
       </c>
-      <c r="U6">
-        <v>2.65</v>
-      </c>
-      <c r="V6">
-        <v>1.42</v>
-      </c>
-      <c r="W6">
+      <c r="AA6">
+        <v>2.04</v>
+      </c>
+      <c r="AB6">
+        <v>1.8</v>
+      </c>
+      <c r="AC6">
+        <v>3.6</v>
+      </c>
+      <c r="AD6">
+        <v>1.29</v>
+      </c>
+      <c r="AE6">
         <v>1.05</v>
       </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.21</v>
-      </c>
-      <c r="Z6">
-        <v>3.62</v>
-      </c>
-      <c r="AA6">
-        <v>1.85</v>
-      </c>
-      <c r="AB6">
-        <v>1.98</v>
-      </c>
-      <c r="AC6">
-        <v>2.94</v>
-      </c>
-      <c r="AD6">
-        <v>1.31</v>
-      </c>
-      <c r="AE6">
-        <v>1.08</v>
-      </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q7">
         <v>1.99</v>
@@ -1489,19 +1489,19 @@
         <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
         <v>1.72</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="O8">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="P8">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
         <v>4.75</v>
@@ -1628,19 +1628,19 @@
         <v>1.9</v>
       </c>
       <c r="S8">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="U8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V8">
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1.06</v>
@@ -1652,10 +1652,10 @@
         <v>2.52</v>
       </c>
       <c r="AA8">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AB8">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC8">
         <v>4.65</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
         <v>4.2</v>
       </c>
       <c r="R9">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
         <v>2.94</v>
@@ -1803,37 +1803,37 @@
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AA9">
         <v>2.03</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG9">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="AK9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="O10">
         <v>3.5</v>
@@ -1948,10 +1948,10 @@
         <v>2.34</v>
       </c>
       <c r="Q10">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="R10">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.34</v>
@@ -1990,13 +1990,13 @@
         <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
         <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>2.08</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
         <v>2.81</v>
@@ -2129,22 +2129,22 @@
         <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB11">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
         <v>3.38</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="O13">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P13">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="Q13">
         <v>3.82</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="S13">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="T13">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U13">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W13">
         <v>1.01</v>
@@ -2461,31 +2461,31 @@
         <v>1.11</v>
       </c>
       <c r="Y13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z13">
         <v>2.07</v>
       </c>
       <c r="AA13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AB13">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC13">
         <v>6.6</v>
       </c>
       <c r="AD13">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG13">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AK13">
         <v>1.34</v>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>3.3</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q14">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S14">
         <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U14">
         <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2627,10 +2627,10 @@
         <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB14">
         <v>1.85</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
         <v>4.41</v>
@@ -4888,13 +4888,13 @@
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U28">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -4906,13 +4906,13 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
         <v>2</v>
@@ -4927,10 +4927,10 @@
         <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O29">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="S29">
         <v>1.57</v>
       </c>
       <c r="T29">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="U29">
         <v>3.6</v>
       </c>
       <c r="V29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y29">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z29">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AA29">
         <v>2.44</v>
       </c>
       <c r="AB29">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC29">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AD29">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG29">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5371,10 +5371,10 @@
         <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.37</v>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V32">
         <v>1.33</v>
@@ -5564,13 +5564,13 @@
         <v>2.92</v>
       </c>
       <c r="AA32">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB32">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC32">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
         <v>1.25</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O34">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="P34">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="Q34">
         <v>7.28</v>
@@ -5869,7 +5869,7 @@
         <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U34">
         <v>2.84</v>
@@ -5890,7 +5890,7 @@
         <v>3.47</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
         <v>1.9</v>
@@ -6675,10 +6675,10 @@
         <v>2.62</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
         <v>1.41</v>
@@ -6693,37 +6693,37 @@
         <v>1.39</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
         <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC39">
-        <v>3.68</v>
+        <v>3.08</v>
       </c>
       <c r="AD39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R40">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
         <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA40">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB40">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC40">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AD40">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE40">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF40">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="Q46">
         <v>2.49</v>
@@ -7846,7 +7846,7 @@
         <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB46">
         <v>2.35</v>
@@ -7864,7 +7864,7 @@
         <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA48">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB48">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="O49">
+        <v>3.9</v>
+      </c>
+      <c r="P49">
         <v>3.5</v>
       </c>
-      <c r="P49">
-        <v>4.8</v>
-      </c>
       <c r="Q49">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R49">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="S49">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="V49">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA49">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>3.62</v>
+        <v>2.99</v>
       </c>
       <c r="AD49">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG49">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA50">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8625,16 +8625,16 @@
         <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q51">
         <v>3</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.36</v>
@@ -8649,22 +8649,22 @@
         <v>1.43</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA51">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
         <v>2.85</v>
@@ -8673,10 +8673,10 @@
         <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
         <v>2.14</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
         <v>1.54</v>
@@ -8788,10 +8788,10 @@
         <v>1.85</v>
       </c>
       <c r="O52">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -8818,7 +8818,7 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z52">
         <v>4.1</v>
@@ -8836,13 +8836,13 @@
         <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG52">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
         <v>1.91</v>
@@ -8951,7 +8951,7 @@
         <v>2.6</v>
       </c>
       <c r="O53">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
         <v>2.7</v>
@@ -8969,22 +8969,22 @@
         <v>2.85</v>
       </c>
       <c r="U53">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V53">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y53">
         <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA53">
         <v>1.88</v>
@@ -8999,13 +8999,13 @@
         <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O54">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P54">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q54">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R54">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="S54">
         <v>1.19</v>
       </c>
       <c r="T54">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="U54">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA54">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
         <v>2.8</v>
       </c>
       <c r="AC54">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AD54">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE54">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF54">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG54">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK54">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
+        <v>2.93</v>
+      </c>
+      <c r="Q58">
+        <v>2.9</v>
+      </c>
+      <c r="R58">
+        <v>2.12</v>
+      </c>
+      <c r="S58">
+        <v>1.35</v>
+      </c>
+      <c r="T58">
+        <v>2.89</v>
+      </c>
+      <c r="U58">
+        <v>2.43</v>
+      </c>
+      <c r="V58">
+        <v>1.46</v>
+      </c>
+      <c r="W58">
+        <v>1.06</v>
+      </c>
+      <c r="X58">
+        <v>1.05</v>
+      </c>
+      <c r="Y58">
+        <v>1.19</v>
+      </c>
+      <c r="Z58">
+        <v>3.82</v>
+      </c>
+      <c r="AA58">
+        <v>1.76</v>
+      </c>
+      <c r="AB58">
+        <v>2.2</v>
+      </c>
+      <c r="AC58">
         <v>2.8</v>
       </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
-      </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>0</v>
-      </c>
-      <c r="AB58">
-        <v>0</v>
-      </c>
-      <c r="AC58">
-        <v>0</v>
-      </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="O60">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P60">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA60">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB60">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,34 +10252,34 @@
         </is>
       </c>
       <c r="N61">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="O61">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
         <v>1.57</v>
       </c>
       <c r="Q61">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S61">
         <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U61">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="V61">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10288,28 +10288,28 @@
         <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB61">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AD61">
         <v>1.58</v>
       </c>
       <c r="AE61">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG61">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK61">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10747,7 +10747,7 @@
         <v>4.6</v>
       </c>
       <c r="P64">
-        <v>7.7</v>
+        <v>6.91</v>
       </c>
       <c r="Q64">
         <v>1.83</v>
@@ -10774,13 +10774,13 @@
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z64">
         <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB64">
         <v>2.04</v>
@@ -10792,10 +10792,10 @@
         <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG64">
         <v>1.8</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK64">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="Q66">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="O26">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P26">
         <v>6.17</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O63">
         <v>3.3</v>
       </c>
       <c r="P63">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O65">
         <v>5.75</v>
       </c>
       <c r="P65">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q65">
         <v>1.62</v>
       </c>
       <c r="R65">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S65">
         <v>1.25</v>
@@ -10946,7 +10946,7 @@
         <v>1.63</v>
       </c>
       <c r="AB65">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC65">
         <v>2.36</v>
@@ -10958,7 +10958,7 @@
         <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG65">
         <v>1.7</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>6.53</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O67">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="P67">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q67">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="R67">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="S67">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="T67">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="U67">
         <v>4</v>
@@ -11275,7 +11275,7 @@
         <v>1.36</v>
       </c>
       <c r="AC67">
-        <v>6.41</v>
+        <v>6.05</v>
       </c>
       <c r="AD67">
         <v>1.08</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12703,43 +12703,43 @@
         <v>3.4</v>
       </c>
       <c r="P76">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q76">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="R76">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="U76">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V76">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
         <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA76">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC76">
         <v>2.88</v>
@@ -12748,13 +12748,13 @@
         <v>1.36</v>
       </c>
       <c r="AE76">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
-        <v>2.48</v>
+        <v>4.45</v>
       </c>
       <c r="R2">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="U2">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z2">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="AA2">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AB2">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AC2">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>4.52</v>
+        <v>3.9</v>
       </c>
       <c r="R3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>3.17</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC3">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
         <v>1.26</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>2.15</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
         <v>3.1</v>
       </c>
-      <c r="O4">
-        <v>3.3</v>
-      </c>
-      <c r="P4">
-        <v>2.05</v>
-      </c>
       <c r="Q4">
-        <v>3.84</v>
+        <v>3.13</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="T4">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Z4">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="AA4">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="AC4">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>2.08</v>
+      </c>
+      <c r="S5">
+        <v>1.36</v>
+      </c>
+      <c r="T5">
+        <v>2.6</v>
+      </c>
+      <c r="U5">
         <v>3</v>
       </c>
-      <c r="Q5">
-        <v>2.94</v>
-      </c>
-      <c r="R5">
-        <v>1.92</v>
-      </c>
-      <c r="S5">
-        <v>1.5</v>
-      </c>
-      <c r="T5">
-        <v>2.41</v>
-      </c>
-      <c r="U5">
-        <v>3.34</v>
-      </c>
       <c r="V5">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AA5">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AB5">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD5">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>1.94</v>
+      </c>
+      <c r="O6">
         <v>3.4</v>
       </c>
-      <c r="O6">
-        <v>3.2</v>
-      </c>
       <c r="P6">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q6">
-        <v>4.42</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>2.99</v>
+        <v>3.7</v>
       </c>
       <c r="AA6">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O7">
-        <v>4.3</v>
+        <v>4.48</v>
       </c>
       <c r="P7">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="Q7">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="R7">
         <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
         <v>1.08</v>
@@ -1489,25 +1489,25 @@
         <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AC7">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="AD7">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
         <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,58 +1613,58 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="U8">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
         <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z8">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AA8">
         <v>2.5</v>
       </c>
       <c r="AB8">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AC8">
-        <v>4.65</v>
+        <v>5.02</v>
       </c>
       <c r="AD8">
         <v>1.13</v>
       </c>
       <c r="AE8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
         <v>2.13</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AK8">
         <v>1.25</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>4.2</v>
       </c>
       <c r="R9">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
         <v>2.94</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD9">
         <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG9">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.74</v>
+        <v>1.31</v>
       </c>
       <c r="AK9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,58 +1942,58 @@
         <v>2.93</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
         <v>2.99</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AB10">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AC10">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="AD10">
         <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
         <v>2.11</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>2.17</v>
+      </c>
+      <c r="O11">
+        <v>3.35</v>
+      </c>
+      <c r="P11">
+        <v>3.15</v>
+      </c>
+      <c r="Q11">
+        <v>2.86</v>
+      </c>
+      <c r="R11">
         <v>2.1</v>
       </c>
-      <c r="O11">
-        <v>3.2</v>
-      </c>
-      <c r="P11">
-        <v>3.1</v>
-      </c>
-      <c r="Q11">
-        <v>2.77</v>
-      </c>
-      <c r="R11">
-        <v>2.08</v>
-      </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA11">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC11">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AD11">
         <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -8139,10 +8139,10 @@
         <v>3.62</v>
       </c>
       <c r="P48">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q48">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R48">
         <v>2.1</v>
@@ -8160,7 +8160,7 @@
         <v>1.35</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
         <v>1.02</v>
@@ -8172,13 +8172,13 @@
         <v>2.94</v>
       </c>
       <c r="AA48">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB48">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC48">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="AD48">
         <v>1.23</v>
@@ -8187,10 +8187,10 @@
         <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG48">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         <v>1.91</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="P49">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="Q49">
         <v>2.44</v>
@@ -8311,10 +8311,10 @@
         <v>2.24</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U49">
         <v>2.65</v>
@@ -8326,7 +8326,7 @@
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
@@ -8347,7 +8347,7 @@
         <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
         <v>1.7</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P50">
         <v>3.45</v>
@@ -8498,7 +8498,7 @@
         <v>3.24</v>
       </c>
       <c r="AA50">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB50">
         <v>1.8</v>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9313,7 +9313,7 @@
         <v>3.24</v>
       </c>
       <c r="AA55">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB55">
         <v>1.85</v>
@@ -9325,7 +9325,7 @@
         <v>1.27</v>
       </c>
       <c r="AE55">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF55">
         <v>1.74</v>
@@ -9446,10 +9446,10 @@
         <v>3.08</v>
       </c>
       <c r="Q56">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R56">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9476,10 +9476,10 @@
         <v>4.15</v>
       </c>
       <c r="AA56">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB56">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC56">
         <v>2.61</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>1.67</v>
@@ -9609,10 +9609,10 @@
         <v>2.43</v>
       </c>
       <c r="Q57">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R57">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S57">
         <v>1.39</v>
@@ -9633,7 +9633,7 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z57">
         <v>3.18</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="Q58">
         <v>2.9</v>
@@ -9778,13 +9778,13 @@
         <v>2.12</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T58">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="U58">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="V58">
         <v>1.46</v>
@@ -9793,7 +9793,7 @@
         <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.19</v>
@@ -9805,16 +9805,16 @@
         <v>1.76</v>
       </c>
       <c r="AB58">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AC58">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD58">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
         <v>1.59</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O60">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P60">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q60">
         <v>3.06</v>
@@ -10104,43 +10104,43 @@
         <v>2.11</v>
       </c>
       <c r="S60">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U60">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="V60">
         <v>1.39</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z60">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="AA60">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB60">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC60">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AD60">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF60">
         <v>1.69</v>
@@ -10488,7 +10488,7 @@
         <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>2.99</v>
+        <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="AD5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P6">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.7</v>
+        <v>2.99</v>
       </c>
       <c r="AA6">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AB6">
+        <v>1.8</v>
+      </c>
+      <c r="AC6">
+        <v>3.6</v>
+      </c>
+      <c r="AD6">
+        <v>1.29</v>
+      </c>
+      <c r="AE6">
+        <v>1.05</v>
+      </c>
+      <c r="AF6">
         <v>1.88</v>
       </c>
-      <c r="AC6">
-        <v>2.94</v>
-      </c>
-      <c r="AD6">
-        <v>1.31</v>
-      </c>
-      <c r="AE6">
-        <v>1.08</v>
-      </c>
-      <c r="AF6">
-        <v>1.67</v>
-      </c>
       <c r="AG6">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.23</v>
+        <v>2.1</v>
       </c>
       <c r="O15">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="P15">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.1</v>
+        <v>3.23</v>
       </c>
       <c r="O16">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G19">
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
         <v>3.3</v>
@@ -6675,16 +6675,16 @@
         <v>2.62</v>
       </c>
       <c r="Q39">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
         <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="U39">
         <v>2.73</v>
@@ -6693,16 +6693,16 @@
         <v>1.39</v>
       </c>
       <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
         <v>1.05</v>
       </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AA39">
         <v>1.88</v>
@@ -6717,10 +6717,10 @@
         <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
         <v>1.95</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK39">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,58 +6829,58 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="Q40">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R40">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
         <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA40">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
         <v>1.49</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
         <v>1.5</v>
@@ -6902,7 +6902,7 @@
         <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
+        <v>1.85</v>
+      </c>
+      <c r="O51">
+        <v>3.6</v>
+      </c>
+      <c r="P51">
+        <v>3.9</v>
+      </c>
+      <c r="Q51">
+        <v>2.4</v>
+      </c>
+      <c r="R51">
+        <v>2.25</v>
+      </c>
+      <c r="S51">
+        <v>1.33</v>
+      </c>
+      <c r="T51">
+        <v>3.04</v>
+      </c>
+      <c r="U51">
         <v>2.5</v>
       </c>
-      <c r="O51">
-        <v>3.3</v>
-      </c>
-      <c r="P51">
-        <v>2.65</v>
-      </c>
-      <c r="Q51">
-        <v>3</v>
-      </c>
-      <c r="R51">
-        <v>2.15</v>
-      </c>
-      <c r="S51">
-        <v>1.36</v>
-      </c>
-      <c r="T51">
-        <v>2.89</v>
-      </c>
-      <c r="U51">
-        <v>2.62</v>
-      </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>3.52</v>
+        <v>3.78</v>
       </c>
       <c r="AA51">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB51">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC51">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AD51">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="Q52">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T52">
+        <v>2.77</v>
+      </c>
+      <c r="U52">
+        <v>2.6</v>
+      </c>
+      <c r="V52">
+        <v>1.38</v>
+      </c>
+      <c r="W52">
+        <v>1.06</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.22</v>
+      </c>
+      <c r="Z52">
+        <v>3.52</v>
+      </c>
+      <c r="AA52">
+        <v>1.9</v>
+      </c>
+      <c r="AB52">
+        <v>2</v>
+      </c>
+      <c r="AC52">
         <v>3.1</v>
       </c>
-      <c r="U52">
-        <v>2.44</v>
-      </c>
-      <c r="V52">
-        <v>1.5</v>
-      </c>
-      <c r="W52">
-        <v>1.08</v>
-      </c>
-      <c r="X52">
-        <v>1.02</v>
-      </c>
-      <c r="Y52">
-        <v>1.19</v>
-      </c>
-      <c r="Z52">
-        <v>4.1</v>
-      </c>
-      <c r="AA52">
-        <v>1.73</v>
-      </c>
-      <c r="AB52">
-        <v>2.07</v>
-      </c>
-      <c r="AC52">
-        <v>2.64</v>
-      </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P53">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
       </c>
       <c r="R53">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S53">
         <v>1.37</v>
@@ -8984,28 +8984,28 @@
         <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA53">
         <v>1.88</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC53">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
         <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK53">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,34 +9111,34 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O54">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="P54">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q54">
         <v>1.66</v>
       </c>
       <c r="R54">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="S54">
         <v>1.19</v>
       </c>
       <c r="T54">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U54">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V54">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9147,25 +9147,25 @@
         <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>6.75</v>
+        <v>5.9</v>
       </c>
       <c r="AA54">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB54">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC54">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AD54">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE54">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF54">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG54">
         <v>2.02</v>
@@ -9274,16 +9274,16 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O55">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="P55">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="Q55">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R55">
         <v>2.06</v>
@@ -9292,37 +9292,37 @@
         <v>1.4</v>
       </c>
       <c r="T55">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="U55">
         <v>2.81</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W55">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z55">
         <v>3.24</v>
       </c>
       <c r="AA55">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB55">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC55">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="AD55">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
@@ -9331,7 +9331,7 @@
         <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,10 +9446,10 @@
         <v>3.08</v>
       </c>
       <c r="Q56">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9458,10 +9458,10 @@
         <v>3.28</v>
       </c>
       <c r="U56">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W56">
         <v>1.07</v>
@@ -9476,10 +9476,10 @@
         <v>4.15</v>
       </c>
       <c r="AA56">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB56">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AC56">
         <v>2.61</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -9615,10 +9615,10 @@
         <v>2.05</v>
       </c>
       <c r="S57">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U57">
         <v>2.89</v>
@@ -9633,22 +9633,22 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z57">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="AA57">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB57">
         <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD57">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
         <v>1.04</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="O58">
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q58">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R58">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T58">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U58">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V58">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
         <v>1.19</v>
       </c>
       <c r="Z58">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="AA58">
         <v>1.76</v>
       </c>
       <c r="AB58">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF58">
+        <v>1.57</v>
+      </c>
+      <c r="AG58">
+        <v>2.18</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.29</v>
+      </c>
+      <c r="AK58">
         <v>1.59</v>
-      </c>
-      <c r="AG58">
-        <v>2.21</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.23</v>
-      </c>
-      <c r="AK58">
-        <v>1.5</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>1.57</v>
       </c>
       <c r="Q61">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="R61">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T61">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U61">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA61">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB61">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC61">
         <v>2.27</v>
       </c>
       <c r="AD61">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,16 +10415,16 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O62">
         <v>3.38</v>
       </c>
       <c r="P62">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q62">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R62">
         <v>2.1</v>
@@ -10439,7 +10439,7 @@
         <v>2.81</v>
       </c>
       <c r="V62">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W62">
         <v>1.05</v>
@@ -10454,25 +10454,25 @@
         <v>3.18</v>
       </c>
       <c r="AA62">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB62">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC62">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AD62">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF62">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG62">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -647,16 +647,16 @@
         <v>4.45</v>
       </c>
       <c r="R2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V2">
         <v>1.37</v>
@@ -674,10 +674,10 @@
         <v>3.25</v>
       </c>
       <c r="AA2">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
         <v>3.6</v>
@@ -831,10 +831,10 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AA3">
         <v>1.82</v>
@@ -849,7 +849,7 @@
         <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
         <v>1.67</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q4">
         <v>3.13</v>
@@ -1290,16 +1290,16 @@
         <v>3.6</v>
       </c>
       <c r="O6">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S6">
         <v>1.36</v>
@@ -1329,13 +1329,13 @@
         <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
         <v>3.6</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
         <v>1.05</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
         <v>1.26</v>
@@ -1453,55 +1453,55 @@
         <v>1.5</v>
       </c>
       <c r="O7">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>1.95</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U7">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AC7">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
         <v>1.73</v>
@@ -1523,7 +1523,7 @@
         <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T8">
         <v>2.25</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y8">
         <v>1.5</v>
@@ -1655,22 +1655,22 @@
         <v>2.5</v>
       </c>
       <c r="AB8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC8">
-        <v>5.02</v>
+        <v>5.14</v>
       </c>
       <c r="AD8">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
         <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.29</v>
@@ -1818,22 +1818,22 @@
         <v>2</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
         <v>3.55</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="O10">
         <v>3.4</v>
@@ -1987,7 +1987,7 @@
         <v>2.48</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
@@ -2111,10 +2111,10 @@
         <v>3.15</v>
       </c>
       <c r="Q11">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
         <v>1.36</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O13">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P13">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="Q13">
         <v>3.82</v>
       </c>
       <c r="R13">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S13">
         <v>1.57</v>
       </c>
       <c r="T13">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U13">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W13">
         <v>1.01</v>
       </c>
       <c r="X13">
+        <v>1.13</v>
+      </c>
+      <c r="Y13">
+        <v>1.67</v>
+      </c>
+      <c r="Z13">
+        <v>2.19</v>
+      </c>
+      <c r="AA13">
+        <v>2.85</v>
+      </c>
+      <c r="AB13">
+        <v>1.33</v>
+      </c>
+      <c r="AC13">
+        <v>6.1</v>
+      </c>
+      <c r="AD13">
         <v>1.11</v>
-      </c>
-      <c r="Y13">
-        <v>1.62</v>
-      </c>
-      <c r="Z13">
-        <v>2.07</v>
-      </c>
-      <c r="AA13">
-        <v>3</v>
-      </c>
-      <c r="AB13">
-        <v>1.4</v>
-      </c>
-      <c r="AC13">
-        <v>6.6</v>
-      </c>
-      <c r="AD13">
-        <v>1.07</v>
       </c>
       <c r="AE13">
         <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG13">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
         <v>2.05</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="R14">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
         <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
         <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2627,7 +2627,7 @@
         <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
         <v>1.86</v>
@@ -2648,7 +2648,7 @@
         <v>1.68</v>
       </c>
       <c r="AG14">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -4882,10 +4882,10 @@
         <v>4.41</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
         <v>1.29</v>
@@ -4912,7 +4912,7 @@
         <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
         <v>2</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
         <v>2.06</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O29">
         <v>2.9</v>
@@ -5045,16 +5045,16 @@
         <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R29">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="S29">
         <v>1.57</v>
       </c>
       <c r="T29">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
         <v>3.6</v>
@@ -5063,28 +5063,28 @@
         <v>1.25</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z29">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AA29">
         <v>2.44</v>
       </c>
       <c r="AB29">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC29">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD29">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5368,13 +5368,13 @@
         <v>3.3</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
         <v>1.37</v>
@@ -5383,10 +5383,10 @@
         <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
         <v>1.04</v>
@@ -5416,10 +5416,10 @@
         <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
         <v>2.91</v>
@@ -5552,7 +5552,7 @@
         <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -5564,16 +5564,16 @@
         <v>2.92</v>
       </c>
       <c r="AA32">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AB32">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC32">
         <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
@@ -5582,7 +5582,7 @@
         <v>1.79</v>
       </c>
       <c r="AG32">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>4.65</v>
+        <v>4.05</v>
       </c>
       <c r="P34">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Q34">
         <v>7.28</v>
@@ -6672,7 +6672,7 @@
         <v>3.3</v>
       </c>
       <c r="P39">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7813,19 +7813,19 @@
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="Q46">
         <v>2.49</v>
       </c>
       <c r="R46">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
         <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U46">
         <v>2.31</v>
@@ -7840,16 +7840,16 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA46">
         <v>1.58</v>
       </c>
       <c r="AB46">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC46">
         <v>2.32</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="O48">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q48">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S48">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U48">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="V48">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
         <v>1.05</v>
       </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
       <c r="Y48">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AA48">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB48">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC48">
-        <v>3.7</v>
+        <v>2.99</v>
       </c>
       <c r="AD48">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="O49">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>3.61</v>
+        <v>4.5</v>
       </c>
       <c r="Q49">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T49">
+        <v>2.56</v>
+      </c>
+      <c r="U49">
         <v>2.9</v>
       </c>
-      <c r="U49">
-        <v>2.65</v>
-      </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
+        <v>1.07</v>
+      </c>
+      <c r="X49">
         <v>1.06</v>
       </c>
-      <c r="X49">
-        <v>1.05</v>
-      </c>
       <c r="Y49">
+        <v>1.36</v>
+      </c>
+      <c r="Z49">
+        <v>3.1</v>
+      </c>
+      <c r="AA49">
+        <v>2.1</v>
+      </c>
+      <c r="AB49">
+        <v>1.7</v>
+      </c>
+      <c r="AC49">
+        <v>3.44</v>
+      </c>
+      <c r="AD49">
+        <v>1.23</v>
+      </c>
+      <c r="AE49">
+        <v>1.08</v>
+      </c>
+      <c r="AF49">
+        <v>1.9</v>
+      </c>
+      <c r="AG49">
+        <v>1.8</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.22</v>
       </c>
-      <c r="Z49">
-        <v>3.54</v>
-      </c>
-      <c r="AA49">
-        <v>1.83</v>
-      </c>
-      <c r="AB49">
-        <v>1.8</v>
-      </c>
-      <c r="AC49">
-        <v>2.99</v>
-      </c>
-      <c r="AD49">
-        <v>1.3</v>
-      </c>
-      <c r="AE49">
-        <v>1.13</v>
-      </c>
-      <c r="AF49">
-        <v>1.7</v>
-      </c>
-      <c r="AG49">
-        <v>2.04</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.2</v>
-      </c>
       <c r="AK49">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="O50">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="R50">
         <v>2.05</v>
@@ -8498,13 +8498,13 @@
         <v>3.24</v>
       </c>
       <c r="AA50">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC50">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AD50">
         <v>1.27</v>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
         <v>3.9</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -8815,7 +8815,7 @@
         <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
@@ -8824,7 +8824,7 @@
         <v>3.52</v>
       </c>
       <c r="AA52">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB52">
         <v>2</v>
@@ -8833,16 +8833,16 @@
         <v>3.1</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O53">
         <v>3.38</v>
@@ -9002,7 +9002,7 @@
         <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG53">
         <v>2.1</v>
@@ -9114,61 +9114,61 @@
         <v>1.28</v>
       </c>
       <c r="O54">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="P54">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Q54">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R54">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S54">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T54">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U54">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V54">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W54">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="AA54">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
         <v>3</v>
       </c>
       <c r="AC54">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AD54">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE54">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AF54">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.12</v>
       </c>
       <c r="AK54">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,58 +9277,58 @@
         <v>2.04</v>
       </c>
       <c r="O55">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="Q55">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="R55">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T55">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U55">
-        <v>2.81</v>
+        <v>3.01</v>
       </c>
       <c r="V55">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA55">
         <v>1.95</v>
       </c>
       <c r="AB55">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC55">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG55">
         <v>2</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="O56">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -9603,61 +9603,61 @@
         <v>2.8</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q57">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R57">
         <v>2.05</v>
       </c>
       <c r="S57">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U57">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="AA57">
         <v>2</v>
       </c>
       <c r="AB57">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC57">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
         <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="O58">
         <v>3.4</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="O60">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q60">
         <v>3.06</v>
       </c>
       <c r="R60">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T60">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U60">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="V60">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y60">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z60">
-        <v>3.63</v>
+        <v>3.44</v>
       </c>
       <c r="AA60">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB60">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC60">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="AD60">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE60">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF60">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG60">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AK60">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O61">
         <v>4.2</v>
@@ -10261,13 +10261,13 @@
         <v>1.57</v>
       </c>
       <c r="Q61">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T61">
         <v>3.34</v>
@@ -10279,50 +10279,50 @@
         <v>1.62</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA61">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AB61">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AC61">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AD61">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE61">
+        <v>1.16</v>
+      </c>
+      <c r="AF61">
+        <v>1.6</v>
+      </c>
+      <c r="AG61">
+        <v>2.2</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.17</v>
-      </c>
-      <c r="AF61">
-        <v>1.57</v>
-      </c>
-      <c r="AG61">
-        <v>2.25</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.15</v>
       </c>
       <c r="AK61">
         <v>1.17</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="O62">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P62">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="Q62">
         <v>2.85</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK62">
         <v>1.57</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O65">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="P65">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q65">
         <v>1.62</v>
       </c>
       <c r="R65">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="S65">
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U65">
         <v>2.34</v>
@@ -10931,7 +10931,7 @@
         <v>1.53</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10940,16 +10940,16 @@
         <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA65">
         <v>1.63</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AD65">
         <v>1.45</v>
@@ -10958,10 +10958,10 @@
         <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK65">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AL65">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2603,7 +2603,7 @@
         <v>3.82</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S14">
         <v>1.34</v>
@@ -2648,7 +2648,7 @@
         <v>1.68</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
         <v>3.16</v>
@@ -5413,7 +5413,7 @@
         <v>1.25</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
         <v>1.7</v>
@@ -5534,7 +5534,7 @@
         <v>2.85</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R32">
         <v>2.03</v>
@@ -5570,7 +5570,7 @@
         <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD32">
         <v>1.22</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>4.05</v>
       </c>
       <c r="P34">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Q34">
         <v>7.28</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>5.06</v>
+        <v>4.25</v>
       </c>
       <c r="O38">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="P38">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="Q38">
-        <v>4.91</v>
+        <v>4.14</v>
       </c>
       <c r="R38">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
         <v>1.22</v>
@@ -6524,43 +6524,43 @@
         <v>3.75</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA38">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AB38">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AC38">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="AD38">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AG38">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
         <v>3.3</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R39">
         <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="U39">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V39">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
         <v>1.06</v>
@@ -6705,19 +6705,19 @@
         <v>3.35</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
         <v>1.8</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
+        <v>1.53</v>
+      </c>
+      <c r="AK39">
         <v>1.44</v>
-      </c>
-      <c r="AK39">
-        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P45">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O64">
         <v>4.6</v>
@@ -10922,7 +10922,7 @@
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
         <v>2.34</v>
@@ -10961,7 +10961,7 @@
         <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="O66">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P66">
-        <v>6.53</v>
+        <v>5.9</v>
       </c>
       <c r="Q66">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R66">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S66">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T66">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U66">
         <v>2.33</v>
@@ -11103,7 +11103,7 @@
         <v>1.16</v>
       </c>
       <c r="Z66">
-        <v>4.15</v>
+        <v>4.03</v>
       </c>
       <c r="AA66">
         <v>1.63</v>
@@ -11112,19 +11112,19 @@
         <v>2.14</v>
       </c>
       <c r="AC66">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD66">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF66">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG66">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK66">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="P67">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q67">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R67">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="S67">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T67">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="U67">
         <v>4</v>
       </c>
       <c r="V67">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W67">
         <v>1.03</v>
@@ -11266,16 +11266,16 @@
         <v>1.63</v>
       </c>
       <c r="Z67">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA67">
         <v>2.6</v>
       </c>
       <c r="AB67">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AC67">
-        <v>6.05</v>
+        <v>6.37</v>
       </c>
       <c r="AD67">
         <v>1.08</v>
@@ -11284,10 +11284,10 @@
         <v>1.01</v>
       </c>
       <c r="AF67">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG67">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
         <v>1.53</v>
@@ -11725,58 +11725,58 @@
         <v>3.1</v>
       </c>
       <c r="P70">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>3.7</v>
       </c>
       <c r="AA76">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB76">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC76">
         <v>2.88</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="O56">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P56">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q56">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S56">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T56">
-        <v>3.28</v>
+        <v>2.69</v>
       </c>
       <c r="U56">
-        <v>2.34</v>
+        <v>2.99</v>
       </c>
       <c r="V56">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="AA56">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AB56">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AC56">
-        <v>2.61</v>
+        <v>3.44</v>
       </c>
       <c r="AD56">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG56">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK56">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
+        <v>2.19</v>
+      </c>
+      <c r="O57">
+        <v>3.7</v>
+      </c>
+      <c r="P57">
         <v>2.8</v>
       </c>
-      <c r="O57">
-        <v>3.2</v>
-      </c>
-      <c r="P57">
-        <v>2.62</v>
-      </c>
       <c r="Q57">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="R57">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>2.69</v>
+        <v>3.28</v>
       </c>
       <c r="U57">
-        <v>2.99</v>
+        <v>2.34</v>
       </c>
       <c r="V57">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="W57">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z57">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB57">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AC57">
-        <v>3.44</v>
+        <v>2.61</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG57">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK57">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O64">
         <v>4.6</v>
       </c>
       <c r="P64">
-        <v>6.91</v>
+        <v>6.3</v>
       </c>
       <c r="Q64">
         <v>1.83</v>
@@ -10907,58 +10907,58 @@
         <v>1.28</v>
       </c>
       <c r="O65">
-        <v>5.35</v>
+        <v>5.55</v>
       </c>
       <c r="P65">
         <v>9.5</v>
       </c>
       <c r="Q65">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R65">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U65">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V65">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W65">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
         <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA65">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB65">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC65">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD65">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE65">
         <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG65">
         <v>1.7</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK65">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,19 +11076,19 @@
         <v>5.9</v>
       </c>
       <c r="Q66">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="R66">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="S66">
         <v>1.28</v>
       </c>
       <c r="T66">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V66">
         <v>1.5</v>
@@ -11100,7 +11100,7 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
         <v>4.03</v>
@@ -11121,10 +11121,10 @@
         <v>1.17</v>
       </c>
       <c r="AF66">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK66">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,28 +11233,28 @@
         <v>2.1</v>
       </c>
       <c r="O67">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="P67">
         <v>3.4</v>
       </c>
       <c r="Q67">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="R67">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="S67">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T67">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="U67">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V67">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W67">
         <v>1.03</v>
@@ -11263,19 +11263,19 @@
         <v>1.08</v>
       </c>
       <c r="Y67">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="Z67">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA67">
         <v>2.6</v>
       </c>
       <c r="AB67">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AC67">
-        <v>6.37</v>
+        <v>6.35</v>
       </c>
       <c r="AD67">
         <v>1.08</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK67">
         <v>1.53</v>
@@ -12706,52 +12706,52 @@
         <v>3.05</v>
       </c>
       <c r="Q76">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R76">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T76">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U76">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V76">
         <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y76">
         <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA76">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD76">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF76">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
         <v>2.1</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="O55">
+        <v>3.2</v>
+      </c>
+      <c r="P55">
+        <v>2.62</v>
+      </c>
+      <c r="Q55">
         <v>3.3</v>
       </c>
-      <c r="P55">
-        <v>3.64</v>
-      </c>
-      <c r="Q55">
-        <v>2.67</v>
-      </c>
       <c r="R55">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S55">
         <v>1.41</v>
       </c>
       <c r="T55">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U55">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="V55">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y55">
         <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AA55">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB55">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AD55">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE55">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK55">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,65 +9437,65 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="O56">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>2.62</v>
+        <v>3.64</v>
       </c>
       <c r="Q56">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="R56">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S56">
         <v>1.41</v>
       </c>
       <c r="T56">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U56">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="V56">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W56">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA56">
+        <v>1.95</v>
+      </c>
+      <c r="AB56">
+        <v>1.85</v>
+      </c>
+      <c r="AC56">
+        <v>3.25</v>
+      </c>
+      <c r="AD56">
+        <v>1.28</v>
+      </c>
+      <c r="AE56">
+        <v>1.06</v>
+      </c>
+      <c r="AF56">
+        <v>1.8</v>
+      </c>
+      <c r="AG56">
         <v>2</v>
       </c>
-      <c r="AB56">
-        <v>1.77</v>
-      </c>
-      <c r="AC56">
-        <v>3.44</v>
-      </c>
-      <c r="AD56">
-        <v>1.23</v>
-      </c>
-      <c r="AE56">
-        <v>1.04</v>
-      </c>
-      <c r="AF56">
-        <v>1.75</v>
-      </c>
-      <c r="AG56">
-        <v>1.97</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>4</v>
       </c>
       <c r="Q63">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R63">
         <v>1.96</v>
@@ -10596,7 +10596,7 @@
         <v>1.45</v>
       </c>
       <c r="T63">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U63">
         <v>3.18</v>
@@ -10605,7 +10605,7 @@
         <v>1.28</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -11755,7 +11755,7 @@
         <v>1.34</v>
       </c>
       <c r="Z70">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA70">
         <v>2.1</v>
@@ -11773,10 +11773,10 @@
         <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG70">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -644,10 +644,10 @@
         <v>1.95</v>
       </c>
       <c r="Q2">
-        <v>4.45</v>
+        <v>3.89</v>
       </c>
       <c r="R2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
         <v>1.41</v>
@@ -659,37 +659,37 @@
         <v>2.99</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AA2">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
         <v>1.9</v>
@@ -708,7 +708,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,52 +807,52 @@
         <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3.17</v>
+        <v>2.99</v>
       </c>
       <c r="U3">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
         <v>2.05</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,13 +970,13 @@
         <v>2.9</v>
       </c>
       <c r="Q4">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="R4">
         <v>1.91</v>
       </c>
       <c r="S4">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T4">
         <v>2.57</v>
@@ -1000,13 +1000,13 @@
         <v>2.61</v>
       </c>
       <c r="AA4">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB4">
         <v>1.59</v>
       </c>
       <c r="AC4">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="AD4">
         <v>1.15</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
         <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
         <v>2.5</v>
@@ -1157,31 +1157,31 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA5">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
         <v>2.94</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,34 +1296,34 @@
         <v>1.95</v>
       </c>
       <c r="Q6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="R6">
         <v>2.06</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
         <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z6">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AA6">
         <v>2.06</v>
@@ -1341,11 +1341,11 @@
         <v>1.05</v>
       </c>
       <c r="AF6">
+        <v>1.82</v>
+      </c>
+      <c r="AG6">
         <v>1.88</v>
       </c>
-      <c r="AG6">
-        <v>1.86</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,34 +1459,34 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
         <v>3.6</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>4.66</v>
       </c>
       <c r="AA7">
         <v>1.64</v>
@@ -1495,19 +1495,19 @@
         <v>2.28</v>
       </c>
       <c r="AC7">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD7">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE7">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,16 +1622,16 @@
         <v>2</v>
       </c>
       <c r="Q8">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="R8">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="S8">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U8">
         <v>3.5</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z8">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AA8">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB8">
         <v>1.5</v>
       </c>
       <c r="AC8">
-        <v>5.14</v>
+        <v>4.7</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF8">
         <v>2.15</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
         <v>1.25</v>
@@ -1776,55 +1776,55 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="O9">
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q9">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="R9">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S9">
         <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U9">
         <v>2.94</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
         <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AK9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,52 +1942,52 @@
         <v>2.95</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q10">
         <v>3.3</v>
       </c>
       <c r="R10">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AA10">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
@@ -1996,7 +1996,7 @@
         <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="Q11">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U11">
         <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2138,13 +2138,13 @@
         <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="AA11">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
         <v>3.5</v>
@@ -2153,10 +2153,10 @@
         <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG11">
         <v>1.95</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="O13">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P13">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="Q13">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R13">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S13">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="T13">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="U13">
         <v>4.5</v>
@@ -2458,25 +2458,25 @@
         <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y13">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Z13">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AA13">
         <v>2.85</v>
       </c>
       <c r="AB13">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC13">
         <v>6.1</v>
       </c>
       <c r="AD13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AE13">
         <v>1.02</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,25 +2600,25 @@
         <v>2.05</v>
       </c>
       <c r="Q14">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R14">
         <v>2.11</v>
       </c>
       <c r="S14">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U14">
         <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O17">
         <v>2.9</v>
       </c>
       <c r="P17">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P28">
-        <v>4.41</v>
+        <v>3.59</v>
       </c>
       <c r="Q28">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
         <v>1.07</v>
@@ -4912,25 +4912,25 @@
         <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD28">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O29">
         <v>2.9</v>
@@ -5045,55 +5045,55 @@
         <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="S29">
         <v>1.57</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="U29">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="V29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z29">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AA29">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AB29">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC29">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD29">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG29">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5371,10 +5371,10 @@
         <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.37</v>
@@ -5383,10 +5383,10 @@
         <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
         <v>1.04</v>
@@ -5534,7 +5534,7 @@
         <v>2.85</v>
       </c>
       <c r="Q32">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
         <v>2.03</v>
@@ -5552,7 +5552,7 @@
         <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -5851,43 +5851,43 @@
         </is>
       </c>
       <c r="N34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O34">
-        <v>4.05</v>
+        <v>5.15</v>
       </c>
       <c r="P34">
         <v>1.28</v>
       </c>
       <c r="Q34">
-        <v>7.28</v>
+        <v>10.5</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U34">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.47</v>
+        <v>3.77</v>
       </c>
       <c r="AA34">
         <v>1.9</v>
@@ -5896,19 +5896,19 @@
         <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG34">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="AK34">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="O38">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Q38">
-        <v>4.14</v>
+        <v>4.46</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T38">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U38">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V38">
         <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
         <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB38">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AC38">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AD38">
+        <v>1.5</v>
+      </c>
+      <c r="AE38">
+        <v>1.23</v>
+      </c>
+      <c r="AF38">
         <v>1.53</v>
       </c>
-      <c r="AE38">
-        <v>1.18</v>
-      </c>
-      <c r="AF38">
-        <v>1.51</v>
-      </c>
       <c r="AG38">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q39">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R39">
         <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V39">
+        <v>1.4</v>
+      </c>
+      <c r="W39">
+        <v>1.05</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.23</v>
+      </c>
+      <c r="Z39">
+        <v>3.42</v>
+      </c>
+      <c r="AA39">
+        <v>1.86</v>
+      </c>
+      <c r="AB39">
+        <v>1.81</v>
+      </c>
+      <c r="AC39">
+        <v>3.4</v>
+      </c>
+      <c r="AD39">
+        <v>1.29</v>
+      </c>
+      <c r="AE39">
+        <v>1.07</v>
+      </c>
+      <c r="AF39">
+        <v>1.73</v>
+      </c>
+      <c r="AG39">
+        <v>2.05</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.28</v>
+      </c>
+      <c r="AK39">
         <v>1.41</v>
-      </c>
-      <c r="W39">
-        <v>1.06</v>
-      </c>
-      <c r="X39">
-        <v>1.05</v>
-      </c>
-      <c r="Y39">
-        <v>1.3</v>
-      </c>
-      <c r="Z39">
-        <v>3.35</v>
-      </c>
-      <c r="AA39">
-        <v>1.8</v>
-      </c>
-      <c r="AB39">
-        <v>1.96</v>
-      </c>
-      <c r="AC39">
-        <v>2.88</v>
-      </c>
-      <c r="AD39">
-        <v>1.32</v>
-      </c>
-      <c r="AE39">
-        <v>1.09</v>
-      </c>
-      <c r="AF39">
-        <v>1.8</v>
-      </c>
-      <c r="AG39">
-        <v>1.95</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.53</v>
-      </c>
-      <c r="AK39">
-        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,25 +6835,25 @@
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q40">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
       <c r="R40">
+        <v>2.26</v>
+      </c>
+      <c r="S40">
+        <v>1.29</v>
+      </c>
+      <c r="T40">
+        <v>3.34</v>
+      </c>
+      <c r="U40">
         <v>2.25</v>
       </c>
-      <c r="S40">
-        <v>1.25</v>
-      </c>
-      <c r="T40">
-        <v>3.6</v>
-      </c>
-      <c r="U40">
-        <v>2.36</v>
-      </c>
       <c r="V40">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
         <v>1.11</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB40">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC40">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AD40">
         <v>1.49</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG40">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,28 +7318,28 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P43">
         <v>1.67</v>
       </c>
       <c r="Q43">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="R43">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="V43">
         <v>1.62</v>
@@ -7351,31 +7351,31 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB43">
         <v>2.38</v>
       </c>
       <c r="AC43">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD43">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE43">
         <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG43">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
         <v>1.2</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O45">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="Q45">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="S45">
         <v>1.28</v>
@@ -7668,7 +7668,7 @@
         <v>2.2</v>
       </c>
       <c r="V45">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W45">
         <v>1.14</v>
@@ -7680,7 +7680,7 @@
         <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA45">
         <v>1.47</v>
@@ -7695,7 +7695,7 @@
         <v>1.65</v>
       </c>
       <c r="AE45">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF45">
         <v>1.42</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P46">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q46">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.34</v>
+        <v>3.66</v>
       </c>
       <c r="U46">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="V46">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA46">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AC46">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AD46">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O47">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O48">
         <v>3.6</v>
       </c>
       <c r="P48">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="S48">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U48">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V48">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z48">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="AA48">
+        <v>1.83</v>
+      </c>
+      <c r="AB48">
         <v>2</v>
       </c>
-      <c r="AB48">
-        <v>1.94</v>
-      </c>
       <c r="AC48">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AD48">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE48">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P49">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S49">
         <v>1.43</v>
@@ -8326,34 +8326,34 @@
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA49">
         <v>2.1</v>
       </c>
       <c r="AB49">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC49">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD49">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG49">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="R50">
         <v>2.05</v>
@@ -8480,28 +8480,28 @@
         <v>2.73</v>
       </c>
       <c r="U50">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V50">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W50">
         <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
         <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>3.24</v>
+        <v>3.49</v>
       </c>
       <c r="AA50">
         <v>2</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC50">
         <v>3.4</v>
@@ -8510,13 +8510,13 @@
         <v>1.27</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P51">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
         <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
         <v>1.08</v>
@@ -8655,31 +8655,31 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="AA51">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AD51">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q52">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S52">
         <v>1.37</v>
       </c>
       <c r="T52">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U52">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V52">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AA52">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD52">
         <v>1.3</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
         <v>1.62</v>
       </c>
       <c r="AG52">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK52">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,77 +8951,77 @@
         <v>2.62</v>
       </c>
       <c r="O53">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
+        <v>2.6</v>
+      </c>
+      <c r="Q53">
+        <v>3.2</v>
+      </c>
+      <c r="R53">
+        <v>2.15</v>
+      </c>
+      <c r="S53">
+        <v>1.34</v>
+      </c>
+      <c r="T53">
+        <v>3.16</v>
+      </c>
+      <c r="U53">
         <v>2.65</v>
       </c>
-      <c r="Q53">
-        <v>3.1</v>
-      </c>
-      <c r="R53">
-        <v>2.17</v>
-      </c>
-      <c r="S53">
-        <v>1.37</v>
-      </c>
-      <c r="T53">
-        <v>2.85</v>
-      </c>
-      <c r="U53">
-        <v>2.77</v>
-      </c>
       <c r="V53">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z53">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AA53">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC53">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="AD53">
+        <v>1.31</v>
+      </c>
+      <c r="AE53">
+        <v>1.08</v>
+      </c>
+      <c r="AF53">
+        <v>1.62</v>
+      </c>
+      <c r="AG53">
+        <v>2.15</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.28</v>
       </c>
-      <c r="AE53">
-        <v>1.06</v>
-      </c>
-      <c r="AF53">
-        <v>1.66</v>
-      </c>
-      <c r="AG53">
-        <v>2.1</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.33</v>
-      </c>
       <c r="AK53">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O54">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="P54">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Q54">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="R54">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S54">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="U54">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V54">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="W54">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z54">
-        <v>6.15</v>
+        <v>6.69</v>
       </c>
       <c r="AA54">
+        <v>1.32</v>
+      </c>
+      <c r="AB54">
+        <v>3.05</v>
+      </c>
+      <c r="AC54">
+        <v>1.78</v>
+      </c>
+      <c r="AD54">
+        <v>1.95</v>
+      </c>
+      <c r="AE54">
         <v>1.4</v>
       </c>
-      <c r="AB54">
-        <v>3</v>
-      </c>
-      <c r="AC54">
-        <v>1.89</v>
-      </c>
-      <c r="AD54">
-        <v>1.82</v>
-      </c>
-      <c r="AE54">
-        <v>1.34</v>
-      </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG54">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK54">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q55">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R55">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S55">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T55">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="U55">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="V55">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
         <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA55">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB55">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE55">
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG55">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.32</v>
       </c>
       <c r="AK55">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="O56">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P56">
-        <v>3.64</v>
+        <v>3.87</v>
       </c>
       <c r="Q56">
         <v>2.67</v>
       </c>
       <c r="R56">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="S56">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T56">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U56">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="V56">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W56">
+        <v>1.03</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
+        <v>1.26</v>
+      </c>
+      <c r="Z56">
+        <v>3.4</v>
+      </c>
+      <c r="AA56">
+        <v>2.05</v>
+      </c>
+      <c r="AB56">
+        <v>1.75</v>
+      </c>
+      <c r="AC56">
+        <v>3.62</v>
+      </c>
+      <c r="AD56">
+        <v>1.24</v>
+      </c>
+      <c r="AE56">
         <v>1.05</v>
       </c>
-      <c r="X56">
-        <v>1.04</v>
-      </c>
-      <c r="Y56">
-        <v>1.28</v>
-      </c>
-      <c r="Z56">
-        <v>3.08</v>
-      </c>
-      <c r="AA56">
-        <v>1.95</v>
-      </c>
-      <c r="AB56">
-        <v>1.85</v>
-      </c>
-      <c r="AC56">
-        <v>3.25</v>
-      </c>
-      <c r="AD56">
-        <v>1.28</v>
-      </c>
-      <c r="AE56">
-        <v>1.06</v>
-      </c>
       <c r="AF56">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P57">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q57">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="R57">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S57">
         <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U57">
         <v>2.34</v>
@@ -9636,28 +9636,28 @@
         <v>1.16</v>
       </c>
       <c r="Z57">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA57">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB57">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AC57">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AD57">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE57">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF57">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG57">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AK57">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R58">
         <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="V58">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA58">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC58">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD58">
         <v>1.42</v>
       </c>
       <c r="AE58">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK58">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O59">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>6.02</v>
+        <v>5.5</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,22 +10089,22 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P60">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q60">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="R60">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
         <v>2.77</v>
@@ -10113,13 +10113,13 @@
         <v>2.69</v>
       </c>
       <c r="V60">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X60">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
         <v>1.23</v>
@@ -10128,41 +10128,41 @@
         <v>3.44</v>
       </c>
       <c r="AA60">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB60">
         <v>1.92</v>
       </c>
       <c r="AC60">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="AD60">
+        <v>1.36</v>
+      </c>
+      <c r="AE60">
+        <v>1.13</v>
+      </c>
+      <c r="AF60">
+        <v>1.65</v>
+      </c>
+      <c r="AG60">
+        <v>2.11</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>1.3</v>
       </c>
-      <c r="AE60">
-        <v>1.08</v>
-      </c>
-      <c r="AF60">
-        <v>1.66</v>
-      </c>
-      <c r="AG60">
-        <v>2.09</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.42</v>
-      </c>
       <c r="AK60">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,34 +10252,34 @@
         </is>
       </c>
       <c r="N61">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O61">
         <v>4.2</v>
       </c>
       <c r="P61">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q61">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R61">
         <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
         <v>3.34</v>
       </c>
       <c r="U61">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V61">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W61">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10297,19 +10297,19 @@
         <v>2.31</v>
       </c>
       <c r="AC61">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD61">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE61">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
         <v>1.6</v>
       </c>
       <c r="AG61">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
         <v>1.17</v>
@@ -10415,65 +10415,65 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="O62">
+        <v>3.54</v>
+      </c>
+      <c r="P62">
         <v>3.35</v>
       </c>
-      <c r="P62">
-        <v>3.02</v>
-      </c>
       <c r="Q62">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="R62">
+        <v>2.2</v>
+      </c>
+      <c r="S62">
+        <v>1.32</v>
+      </c>
+      <c r="T62">
+        <v>3.24</v>
+      </c>
+      <c r="U62">
+        <v>2.56</v>
+      </c>
+      <c r="V62">
+        <v>1.45</v>
+      </c>
+      <c r="W62">
+        <v>1.07</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>1.21</v>
+      </c>
+      <c r="Z62">
+        <v>4.05</v>
+      </c>
+      <c r="AA62">
+        <v>1.72</v>
+      </c>
+      <c r="AB62">
+        <v>2.05</v>
+      </c>
+      <c r="AC62">
+        <v>2.67</v>
+      </c>
+      <c r="AD62">
+        <v>1.4</v>
+      </c>
+      <c r="AE62">
+        <v>1.08</v>
+      </c>
+      <c r="AF62">
+        <v>1.62</v>
+      </c>
+      <c r="AG62">
         <v>2.1</v>
       </c>
-      <c r="S62">
-        <v>1.39</v>
-      </c>
-      <c r="T62">
-        <v>2.77</v>
-      </c>
-      <c r="U62">
-        <v>2.81</v>
-      </c>
-      <c r="V62">
-        <v>1.36</v>
-      </c>
-      <c r="W62">
-        <v>1.05</v>
-      </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.27</v>
-      </c>
-      <c r="Z62">
-        <v>3.18</v>
-      </c>
-      <c r="AA62">
-        <v>1.95</v>
-      </c>
-      <c r="AB62">
-        <v>1.82</v>
-      </c>
-      <c r="AC62">
-        <v>3.24</v>
-      </c>
-      <c r="AD62">
-        <v>1.26</v>
-      </c>
-      <c r="AE62">
-        <v>1.06</v>
-      </c>
-      <c r="AF62">
-        <v>1.7</v>
-      </c>
-      <c r="AG62">
-        <v>2</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O63">
         <v>3.25</v>
@@ -10587,7 +10587,7 @@
         <v>4</v>
       </c>
       <c r="Q63">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R63">
         <v>1.96</v>
@@ -10611,25 +10611,25 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z63">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="AA63">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC63">
         <v>4.1</v>
       </c>
       <c r="AD63">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE63">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF63">
         <v>2</v>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="O64">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P64">
         <v>6.3</v>
       </c>
       <c r="Q64">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="R64">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
         <v>1.34</v>
@@ -10762,16 +10762,16 @@
         <v>2.91</v>
       </c>
       <c r="U64">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y64">
         <v>1.23</v>
@@ -10780,22 +10780,22 @@
         <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AB64">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AC64">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD64">
         <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG64">
         <v>1.8</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK64">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11082,7 +11082,7 @@
         <v>2.29</v>
       </c>
       <c r="S66">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
         <v>3.3</v>
@@ -11091,7 +11091,7 @@
         <v>2.38</v>
       </c>
       <c r="V66">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W66">
         <v>1.09</v>
@@ -11103,7 +11103,7 @@
         <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>4.03</v>
+        <v>4.15</v>
       </c>
       <c r="AA66">
         <v>1.63</v>
@@ -11233,22 +11233,22 @@
         <v>2.1</v>
       </c>
       <c r="O67">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="P67">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q67">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="R67">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="S67">
         <v>1.66</v>
       </c>
       <c r="T67">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="U67">
         <v>4.05</v>
@@ -11263,10 +11263,10 @@
         <v>1.08</v>
       </c>
       <c r="Y67">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="Z67">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AA67">
         <v>2.6</v>
@@ -11275,7 +11275,7 @@
         <v>1.32</v>
       </c>
       <c r="AC67">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="AD67">
         <v>1.08</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK67">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11734,16 +11734,16 @@
         <v>1.95</v>
       </c>
       <c r="S70">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U70">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V70">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W70">
         <v>1.06</v>
@@ -11758,10 +11758,10 @@
         <v>2.95</v>
       </c>
       <c r="AA70">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB70">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC70">
         <v>3.52</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O76">
         <v>3.4</v>
       </c>
       <c r="P76">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -12715,7 +12715,7 @@
         <v>1.3</v>
       </c>
       <c r="T76">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U76">
         <v>2.45</v>
@@ -12730,10 +12730,10 @@
         <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA76">
         <v>1.8</v>
@@ -12742,13 +12742,13 @@
         <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD76">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE76">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
         <v>1.6</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU76"/>
+  <dimension ref="A1:AU71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10907,22 +10907,22 @@
         <v>1.28</v>
       </c>
       <c r="O65">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="P65">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q65">
         <v>1.67</v>
       </c>
       <c r="R65">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="S65">
         <v>1.29</v>
       </c>
       <c r="T65">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U65">
         <v>2.36</v>
@@ -10931,7 +10931,7 @@
         <v>1.54</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -10940,28 +10940,28 @@
         <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA65">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
         <v>2.3</v>
       </c>
       <c r="AC65">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD65">
         <v>1.44</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
         <v>3.75</v>
@@ -11835,27 +11835,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -11985,821 +11985,6 @@
         <v>0</v>
       </c>
       <c r="AU71" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Al Hussein</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Al Jazeera</t>
-        </is>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>0</v>
-      </c>
-      <c r="AE72">
-        <v>0</v>
-      </c>
-      <c r="AF72">
-        <v>0</v>
-      </c>
-      <c r="AG72">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>0</v>
-      </c>
-      <c r="AK72">
-        <v>0</v>
-      </c>
-      <c r="AL72">
-        <v>0</v>
-      </c>
-      <c r="AM72">
-        <v>-1</v>
-      </c>
-      <c r="AN72">
-        <v>-1</v>
-      </c>
-      <c r="AO72">
-        <v>-1</v>
-      </c>
-      <c r="AP72">
-        <v>-1</v>
-      </c>
-      <c r="AQ72">
-        <v>0</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
-        <v>0</v>
-      </c>
-      <c r="AT72">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Al Buqa'a</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Doqarah</t>
-        </is>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="T73">
-        <v>0</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
-      </c>
-      <c r="Z73">
-        <v>0</v>
-      </c>
-      <c r="AA73">
-        <v>0</v>
-      </c>
-      <c r="AB73">
-        <v>0</v>
-      </c>
-      <c r="AC73">
-        <v>0</v>
-      </c>
-      <c r="AD73">
-        <v>0</v>
-      </c>
-      <c r="AE73">
-        <v>0</v>
-      </c>
-      <c r="AF73">
-        <v>0</v>
-      </c>
-      <c r="AG73">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>0</v>
-      </c>
-      <c r="AK73">
-        <v>0</v>
-      </c>
-      <c r="AL73">
-        <v>0</v>
-      </c>
-      <c r="AM73">
-        <v>-1</v>
-      </c>
-      <c r="AN73">
-        <v>-1</v>
-      </c>
-      <c r="AO73">
-        <v>-1</v>
-      </c>
-      <c r="AP73">
-        <v>-1</v>
-      </c>
-      <c r="AQ73">
-        <v>0</v>
-      </c>
-      <c r="AR73">
-        <v>0</v>
-      </c>
-      <c r="AS73">
-        <v>0</v>
-      </c>
-      <c r="AT73">
-        <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Al Arabi</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Al Salt</t>
-        </is>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>0</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>0</v>
-      </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
-      <c r="W74">
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <v>0</v>
-      </c>
-      <c r="Z74">
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <v>0</v>
-      </c>
-      <c r="AB74">
-        <v>0</v>
-      </c>
-      <c r="AC74">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>0</v>
-      </c>
-      <c r="AE74">
-        <v>0</v>
-      </c>
-      <c r="AF74">
-        <v>0</v>
-      </c>
-      <c r="AG74">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>0</v>
-      </c>
-      <c r="AK74">
-        <v>0</v>
-      </c>
-      <c r="AL74">
-        <v>0</v>
-      </c>
-      <c r="AM74">
-        <v>-1</v>
-      </c>
-      <c r="AN74">
-        <v>-1</v>
-      </c>
-      <c r="AO74">
-        <v>-1</v>
-      </c>
-      <c r="AP74">
-        <v>-1</v>
-      </c>
-      <c r="AQ74">
-        <v>0</v>
-      </c>
-      <c r="AR74">
-        <v>0</v>
-      </c>
-      <c r="AS74">
-        <v>0</v>
-      </c>
-      <c r="AT74">
-        <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Al Wihdat</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Al Faisaly</t>
-        </is>
-      </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>0</v>
-      </c>
-      <c r="AB75">
-        <v>0</v>
-      </c>
-      <c r="AC75">
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <v>0</v>
-      </c>
-      <c r="AE75">
-        <v>0</v>
-      </c>
-      <c r="AF75">
-        <v>0</v>
-      </c>
-      <c r="AG75">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>0</v>
-      </c>
-      <c r="AK75">
-        <v>0</v>
-      </c>
-      <c r="AL75">
-        <v>0</v>
-      </c>
-      <c r="AM75">
-        <v>-1</v>
-      </c>
-      <c r="AN75">
-        <v>-1</v>
-      </c>
-      <c r="AO75">
-        <v>-1</v>
-      </c>
-      <c r="AP75">
-        <v>-1</v>
-      </c>
-      <c r="AQ75">
-        <v>0</v>
-      </c>
-      <c r="AR75">
-        <v>0</v>
-      </c>
-      <c r="AS75">
-        <v>0</v>
-      </c>
-      <c r="AT75">
-        <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>2026-09-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Ñublense</t>
-        </is>
-      </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N76">
-        <v>2.25</v>
-      </c>
-      <c r="O76">
-        <v>3.4</v>
-      </c>
-      <c r="P76">
-        <v>2.89</v>
-      </c>
-      <c r="Q76">
-        <v>2.88</v>
-      </c>
-      <c r="R76">
-        <v>2.2</v>
-      </c>
-      <c r="S76">
-        <v>1.3</v>
-      </c>
-      <c r="T76">
-        <v>2.95</v>
-      </c>
-      <c r="U76">
-        <v>2.45</v>
-      </c>
-      <c r="V76">
-        <v>1.4</v>
-      </c>
-      <c r="W76">
-        <v>1.1</v>
-      </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
-        <v>1.2</v>
-      </c>
-      <c r="Z76">
-        <v>3.7</v>
-      </c>
-      <c r="AA76">
-        <v>1.8</v>
-      </c>
-      <c r="AB76">
-        <v>2</v>
-      </c>
-      <c r="AC76">
-        <v>2.78</v>
-      </c>
-      <c r="AD76">
-        <v>1.34</v>
-      </c>
-      <c r="AE76">
-        <v>1.1</v>
-      </c>
-      <c r="AF76">
-        <v>1.6</v>
-      </c>
-      <c r="AG76">
-        <v>2.1</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.25</v>
-      </c>
-      <c r="AK76">
-        <v>1.53</v>
-      </c>
-      <c r="AL76">
-        <v>0</v>
-      </c>
-      <c r="AM76">
-        <v>-1</v>
-      </c>
-      <c r="AN76">
-        <v>-1</v>
-      </c>
-      <c r="AO76">
-        <v>-1</v>
-      </c>
-      <c r="AP76">
-        <v>-1</v>
-      </c>
-      <c r="AQ76">
-        <v>0</v>
-      </c>
-      <c r="AR76">
-        <v>0</v>
-      </c>
-      <c r="AS76">
-        <v>0</v>
-      </c>
-      <c r="AT76">
-        <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU71"/>
+  <dimension ref="A1:AU73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-02 07:00:00</t>
+          <t>2026-09-02 06:30:00</t>
         </is>
       </c>
     </row>
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-02 07:00:00</t>
+          <t>2026-09-02 06:30:00</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
+        <v>3.25</v>
+      </c>
+      <c r="P4">
+        <v>1.95</v>
+      </c>
+      <c r="Q4">
+        <v>4.4</v>
+      </c>
+      <c r="R4">
+        <v>2.15</v>
+      </c>
+      <c r="S4">
+        <v>1.36</v>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
-      <c r="P4">
-        <v>2.9</v>
-      </c>
-      <c r="Q4">
-        <v>3.06</v>
-      </c>
-      <c r="R4">
+      <c r="U4">
+        <v>2.86</v>
+      </c>
+      <c r="V4">
+        <v>1.4</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.24</v>
+      </c>
+      <c r="Z4">
+        <v>3.38</v>
+      </c>
+      <c r="AA4">
+        <v>1.9</v>
+      </c>
+      <c r="AB4">
         <v>1.91</v>
       </c>
-      <c r="S4">
-        <v>1.51</v>
-      </c>
-      <c r="T4">
-        <v>2.57</v>
-      </c>
-      <c r="U4">
-        <v>3.34</v>
-      </c>
-      <c r="V4">
-        <v>1.28</v>
-      </c>
-      <c r="W4">
-        <v>1.01</v>
-      </c>
-      <c r="X4">
-        <v>1.04</v>
-      </c>
-      <c r="Y4">
-        <v>1.43</v>
-      </c>
-      <c r="Z4">
-        <v>2.61</v>
-      </c>
-      <c r="AA4">
-        <v>2.35</v>
-      </c>
-      <c r="AB4">
-        <v>1.59</v>
-      </c>
       <c r="AC4">
-        <v>4.52</v>
+        <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AK4">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P5">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q5">
-        <v>2.49</v>
+        <v>3.95</v>
       </c>
       <c r="R5">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
         <v>1.34</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1154,16 +1154,16 @@
         <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB5">
         <v>2.01</v>
@@ -1172,13 +1172,13 @@
         <v>2.94</v>
       </c>
       <c r="AD5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
         <v>2.05</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q6">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="U6">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
         <v>1.04</v>
       </c>
-      <c r="X6">
-        <v>1.06</v>
-      </c>
       <c r="Y6">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z6">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="AA6">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
-        <v>3.6</v>
+        <v>4.43</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
+        <v>3.3</v>
+      </c>
+      <c r="P7">
+        <v>1.91</v>
+      </c>
+      <c r="Q7">
         <v>4</v>
       </c>
-      <c r="P7">
-        <v>5</v>
-      </c>
-      <c r="Q7">
-        <v>1.99</v>
-      </c>
       <c r="R7">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="S7">
+        <v>1.36</v>
+      </c>
+      <c r="T7">
+        <v>2.69</v>
+      </c>
+      <c r="U7">
+        <v>2.89</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.33</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7">
+        <v>1.8</v>
+      </c>
+      <c r="AC7">
+        <v>3.55</v>
+      </c>
+      <c r="AD7">
         <v>1.28</v>
       </c>
-      <c r="T7">
-        <v>3.6</v>
-      </c>
-      <c r="U7">
-        <v>2.29</v>
-      </c>
-      <c r="V7">
-        <v>1.53</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.17</v>
-      </c>
-      <c r="Z7">
-        <v>4.66</v>
-      </c>
-      <c r="AA7">
-        <v>1.64</v>
-      </c>
-      <c r="AB7">
-        <v>2.28</v>
-      </c>
-      <c r="AC7">
-        <v>2.45</v>
-      </c>
-      <c r="AD7">
-        <v>1.49</v>
-      </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AK7">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.85</v>
+      </c>
+      <c r="O8">
         <v>3.6</v>
       </c>
-      <c r="O8">
-        <v>3</v>
-      </c>
       <c r="P8">
+        <v>3.7</v>
+      </c>
+      <c r="Q8">
+        <v>2.4</v>
+      </c>
+      <c r="R8">
+        <v>2.13</v>
+      </c>
+      <c r="S8">
+        <v>1.34</v>
+      </c>
+      <c r="T8">
+        <v>2.94</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.42</v>
+      </c>
+      <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.79</v>
+      </c>
+      <c r="AA8">
+        <v>1.85</v>
+      </c>
+      <c r="AB8">
+        <v>1.95</v>
+      </c>
+      <c r="AC8">
+        <v>3.15</v>
+      </c>
+      <c r="AD8">
+        <v>1.31</v>
+      </c>
+      <c r="AE8">
+        <v>1.08</v>
+      </c>
+      <c r="AF8">
+        <v>1.67</v>
+      </c>
+      <c r="AG8">
         <v>2</v>
       </c>
-      <c r="Q8">
-        <v>4.27</v>
-      </c>
-      <c r="R8">
-        <v>1.88</v>
-      </c>
-      <c r="S8">
-        <v>1.58</v>
-      </c>
-      <c r="T8">
-        <v>2.29</v>
-      </c>
-      <c r="U8">
-        <v>3.5</v>
-      </c>
-      <c r="V8">
-        <v>1.25</v>
-      </c>
-      <c r="W8">
-        <v>1.01</v>
-      </c>
-      <c r="X8">
-        <v>1.07</v>
-      </c>
-      <c r="Y8">
-        <v>1.52</v>
-      </c>
-      <c r="Z8">
-        <v>2.56</v>
-      </c>
-      <c r="AA8">
-        <v>2.62</v>
-      </c>
-      <c r="AB8">
-        <v>1.5</v>
-      </c>
-      <c r="AC8">
-        <v>4.7</v>
-      </c>
-      <c r="AD8">
-        <v>1.12</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>2.15</v>
-      </c>
-      <c r="AG8">
-        <v>1.63</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.66</v>
+        <v>1.52</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="Q9">
-        <v>3.86</v>
+        <v>1.91</v>
       </c>
       <c r="R9">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T9">
-        <v>2.87</v>
+        <v>3.34</v>
       </c>
       <c r="U9">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
+        <v>1.62</v>
+      </c>
+      <c r="AB9">
+        <v>2.25</v>
+      </c>
+      <c r="AC9">
+        <v>2.5</v>
+      </c>
+      <c r="AD9">
+        <v>1.5</v>
+      </c>
+      <c r="AE9">
+        <v>1.2</v>
+      </c>
+      <c r="AF9">
+        <v>1.68</v>
+      </c>
+      <c r="AG9">
         <v>2.05</v>
       </c>
-      <c r="AB9">
-        <v>1.75</v>
-      </c>
-      <c r="AC9">
-        <v>3.45</v>
-      </c>
-      <c r="AD9">
-        <v>1.25</v>
-      </c>
-      <c r="AE9">
-        <v>1.04</v>
-      </c>
-      <c r="AF9">
-        <v>1.8</v>
-      </c>
-      <c r="AG9">
-        <v>1.9</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>1.25</v>
+        <v>2.55</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="O10">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="P10">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="T10">
-        <v>2.94</v>
+        <v>2.29</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
+        <v>1.07</v>
+      </c>
+      <c r="Y10">
+        <v>1.47</v>
+      </c>
+      <c r="Z10">
+        <v>2.38</v>
+      </c>
+      <c r="AA10">
+        <v>2.6</v>
+      </c>
+      <c r="AB10">
+        <v>1.5</v>
+      </c>
+      <c r="AC10">
+        <v>4.7</v>
+      </c>
+      <c r="AD10">
+        <v>1.12</v>
+      </c>
+      <c r="AE10">
         <v>1.04</v>
       </c>
-      <c r="Y10">
-        <v>1.26</v>
-      </c>
-      <c r="Z10">
-        <v>3.6</v>
-      </c>
-      <c r="AA10">
-        <v>1.85</v>
-      </c>
-      <c r="AB10">
-        <v>1.95</v>
-      </c>
-      <c r="AC10">
-        <v>3</v>
-      </c>
-      <c r="AD10">
-        <v>1.33</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
       <c r="AF10">
+        <v>2.1</v>
+      </c>
+      <c r="AG10">
         <v>1.62</v>
       </c>
-      <c r="AG10">
-        <v>2.16</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.24</v>
+        <v>2.05</v>
       </c>
       <c r="Q11">
-        <v>2.86</v>
+        <v>3.86</v>
       </c>
       <c r="R11">
         <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
         <v>1.06</v>
       </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD11">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-02 10:30:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
+        <v>3.2</v>
+      </c>
+      <c r="Q13">
+        <v>2.71</v>
+      </c>
+      <c r="R13">
+        <v>2.27</v>
+      </c>
+      <c r="S13">
+        <v>1.36</v>
+      </c>
+      <c r="T13">
         <v>2.85</v>
       </c>
-      <c r="Q13">
-        <v>3.6</v>
-      </c>
-      <c r="R13">
-        <v>1.75</v>
-      </c>
-      <c r="S13">
-        <v>1.72</v>
-      </c>
-      <c r="T13">
-        <v>2.13</v>
-      </c>
       <c r="U13">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="V13">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>2.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC13">
-        <v>6.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD13">
+        <v>1.28</v>
+      </c>
+      <c r="AE13">
         <v>1.06</v>
       </c>
-      <c r="AE13">
-        <v>1.02</v>
-      </c>
       <c r="AF13">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-02 11:00:00</t>
+          <t>2026-09-02 07:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-02 11:00:00</t>
+          <t>2026-09-02 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="O15">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-02 11:30:00</t>
+          <t>2026-09-02 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-02 11:30:00</t>
+          <t>2026-09-02 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="P17">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 11:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-02 12:00:00</t>
+          <t>2026-09-02 11:30:00</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-02 12:30:00</t>
+          <t>2026-09-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-02 13:00:00</t>
+          <t>2026-09-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-02 13:00:00</t>
+          <t>2026-09-02 12:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="O28">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="P28">
-        <v>3.59</v>
+        <v>6.17</v>
       </c>
       <c r="Q28">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="R28">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="T28">
-        <v>2.99</v>
+        <v>3.85</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z28">
-        <v>3.54</v>
+        <v>6.25</v>
       </c>
       <c r="AA28">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="AC28">
-        <v>2.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AF28">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AG28">
-        <v>2.06</v>
+        <v>2.63</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-02 13:30:00</t>
+          <t>2026-09-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>2.61</v>
       </c>
       <c r="O29">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q29">
-        <v>2.7</v>
+        <v>3.82</v>
       </c>
       <c r="R29">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S29">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T29">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="U29">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="V29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="Z29">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AA29">
         <v>2.46</v>
       </c>
       <c r="AB29">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AC29">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AD29">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF29">
         <v>2.09</v>
       </c>
       <c r="AG29">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-02 14:00:00</t>
+          <t>2026-09-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-02 14:00:00</t>
+          <t>2026-09-02 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="S31">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="U31">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="Z31">
-        <v>3.14</v>
+        <v>2.43</v>
       </c>
       <c r="AA31">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="AB31">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AC31">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="AD31">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AG31">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>11</v>
+        <v>2.41</v>
       </c>
       <c r="O34">
-        <v>5.15</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="Q34">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="U34">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3.77</v>
+        <v>2.88</v>
       </c>
       <c r="AA34">
+        <v>2.06</v>
+      </c>
+      <c r="AB34">
+        <v>1.7</v>
+      </c>
+      <c r="AC34">
+        <v>3.35</v>
+      </c>
+      <c r="AD34">
+        <v>1.25</v>
+      </c>
+      <c r="AE34">
+        <v>1.04</v>
+      </c>
+      <c r="AF34">
+        <v>1.81</v>
+      </c>
+      <c r="AG34">
         <v>1.9</v>
       </c>
-      <c r="AB34">
-        <v>1.9</v>
-      </c>
-      <c r="AC34">
-        <v>2.83</v>
-      </c>
-      <c r="AD34">
-        <v>1.33</v>
-      </c>
-      <c r="AE34">
-        <v>1.13</v>
-      </c>
-      <c r="AF34">
-        <v>2.4</v>
-      </c>
-      <c r="AG34">
-        <v>1.5</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>3.6</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-02 14:30:00</t>
+          <t>2026-09-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>3.96</v>
+        <v>4.8</v>
       </c>
       <c r="P36">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-02 14:30:00</t>
+          <t>2026-09-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G37">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>3.9</v>
+        <v>6.9</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="P38">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Q38">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-02 15:00:00</t>
+          <t>2026-09-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-02 15:00:00</t>
+          <t>2026-09-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,69 +6825,69 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="Q40">
-        <v>3.71</v>
+        <v>4.46</v>
       </c>
       <c r="R40">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T40">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V40">
         <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AB40">
+        <v>2.21</v>
+      </c>
+      <c r="AC40">
+        <v>2.41</v>
+      </c>
+      <c r="AD40">
+        <v>1.5</v>
+      </c>
+      <c r="AE40">
+        <v>1.23</v>
+      </c>
+      <c r="AF40">
+        <v>1.53</v>
+      </c>
+      <c r="AG40">
         <v>2.3</v>
       </c>
-      <c r="AC40">
-        <v>2.48</v>
-      </c>
-      <c r="AD40">
-        <v>1.49</v>
-      </c>
-      <c r="AE40">
-        <v>1.16</v>
-      </c>
-      <c r="AF40">
-        <v>1.47</v>
-      </c>
-      <c r="AG40">
-        <v>2.45</v>
-      </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:00</t>
+          <t>2026-09-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:00</t>
+          <t>2026-09-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q45">
-        <v>2.46</v>
+        <v>4.56</v>
       </c>
       <c r="R45">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U45">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V45">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
         <v>5</v>
       </c>
       <c r="AA45">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB45">
         <v>2.38</v>
       </c>
       <c r="AC45">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD45">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE45">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AG45">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AK45">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="O47">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P48">
+        <v>3.65</v>
+      </c>
+      <c r="Q48">
+        <v>2.29</v>
+      </c>
+      <c r="R48">
+        <v>2.48</v>
+      </c>
+      <c r="S48">
+        <v>1.21</v>
+      </c>
+      <c r="T48">
         <v>3.75</v>
       </c>
-      <c r="Q48">
-        <v>2.4</v>
-      </c>
-      <c r="R48">
-        <v>2.11</v>
-      </c>
-      <c r="S48">
-        <v>1.36</v>
-      </c>
-      <c r="T48">
-        <v>2.9</v>
-      </c>
       <c r="U48">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>3.62</v>
+        <v>5.75</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="AB48">
-        <v>2</v>
+        <v>2.61</v>
       </c>
       <c r="AC48">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD48">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF48">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG48">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-02 15:45:00</t>
+          <t>2026-09-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.77</v>
+        <v>3.65</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>4.51</v>
+        <v>1.95</v>
       </c>
       <c r="Q49">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB49">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC49">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-02 15:45:00</t>
+          <t>2026-09-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
         <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="V50">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="AA50">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AD50">
+        <v>1.41</v>
+      </c>
+      <c r="AE50">
+        <v>1.15</v>
+      </c>
+      <c r="AF50">
+        <v>1.65</v>
+      </c>
+      <c r="AG50">
+        <v>2.15</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.27</v>
       </c>
-      <c r="AE50">
-        <v>1.11</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
-      <c r="AG50">
-        <v>2</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.3</v>
-      </c>
       <c r="AK50">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O51">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q51">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="Z51">
-        <v>3.85</v>
+        <v>3.24</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC51">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AG51">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Q52">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="R52">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="U52">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB52">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="AD52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="O53">
+        <v>3.6</v>
+      </c>
+      <c r="P53">
         <v>3.5</v>
       </c>
-      <c r="P53">
-        <v>2.6</v>
-      </c>
       <c r="Q53">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="U53">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AA53">
+        <v>1.71</v>
+      </c>
+      <c r="AB53">
+        <v>2.08</v>
+      </c>
+      <c r="AC53">
+        <v>2.75</v>
+      </c>
+      <c r="AD53">
+        <v>1.39</v>
+      </c>
+      <c r="AE53">
+        <v>1.13</v>
+      </c>
+      <c r="AF53">
+        <v>1.61</v>
+      </c>
+      <c r="AG53">
+        <v>2.25</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.22</v>
+      </c>
+      <c r="AK53">
         <v>1.8</v>
-      </c>
-      <c r="AB53">
-        <v>2</v>
-      </c>
-      <c r="AC53">
-        <v>2.94</v>
-      </c>
-      <c r="AD53">
-        <v>1.31</v>
-      </c>
-      <c r="AE53">
-        <v>1.08</v>
-      </c>
-      <c r="AF53">
-        <v>1.62</v>
-      </c>
-      <c r="AG53">
-        <v>2.15</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.28</v>
-      </c>
-      <c r="AK53">
-        <v>1.46</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O54">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q54">
-        <v>1.52</v>
+        <v>3.1</v>
       </c>
       <c r="R54">
+        <v>2.08</v>
+      </c>
+      <c r="S54">
+        <v>1.36</v>
+      </c>
+      <c r="T54">
+        <v>2.9</v>
+      </c>
+      <c r="U54">
+        <v>2.62</v>
+      </c>
+      <c r="V54">
+        <v>1.43</v>
+      </c>
+      <c r="W54">
+        <v>1.08</v>
+      </c>
+      <c r="X54">
+        <v>1.02</v>
+      </c>
+      <c r="Y54">
+        <v>1.22</v>
+      </c>
+      <c r="Z54">
+        <v>3.7</v>
+      </c>
+      <c r="AA54">
+        <v>1.82</v>
+      </c>
+      <c r="AB54">
+        <v>1.9</v>
+      </c>
+      <c r="AC54">
         <v>3.1</v>
       </c>
-      <c r="S54">
-        <v>1.19</v>
-      </c>
-      <c r="T54">
-        <v>3.92</v>
-      </c>
-      <c r="U54">
-        <v>1.9</v>
-      </c>
-      <c r="V54">
-        <v>1.85</v>
-      </c>
-      <c r="W54">
-        <v>1.22</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.05</v>
-      </c>
-      <c r="Z54">
-        <v>6.69</v>
-      </c>
-      <c r="AA54">
-        <v>1.32</v>
-      </c>
-      <c r="AB54">
-        <v>3.05</v>
-      </c>
-      <c r="AC54">
-        <v>1.78</v>
-      </c>
       <c r="AD54">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AE54">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O55">
         <v>3.4</v>
       </c>
       <c r="P55">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q55">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="R55">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
+        <v>1.37</v>
+      </c>
+      <c r="T55">
+        <v>2.99</v>
+      </c>
+      <c r="U55">
+        <v>2.65</v>
+      </c>
+      <c r="V55">
         <v>1.42</v>
-      </c>
-      <c r="T55">
-        <v>2.59</v>
-      </c>
-      <c r="U55">
-        <v>2.74</v>
-      </c>
-      <c r="V55">
-        <v>1.36</v>
       </c>
       <c r="W55">
         <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z55">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA55">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AB55">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AD55">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE55">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG55">
         <v>2.1</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="O56">
-        <v>3.38</v>
+        <v>6.5</v>
       </c>
       <c r="P56">
-        <v>3.87</v>
+        <v>10</v>
       </c>
       <c r="Q56">
-        <v>2.67</v>
+        <v>1.58</v>
       </c>
       <c r="R56">
-        <v>2.19</v>
+        <v>3.11</v>
       </c>
       <c r="S56">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="T56">
-        <v>2.59</v>
+        <v>4.33</v>
       </c>
       <c r="U56">
-        <v>3.04</v>
+        <v>1.98</v>
       </c>
       <c r="V56">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="Z56">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA56">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="AB56">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC56">
-        <v>3.62</v>
+        <v>1.85</v>
       </c>
       <c r="AD56">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="AE56">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="AF56">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="O57">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="Q57">
-        <v>2.48</v>
+        <v>3.04</v>
       </c>
       <c r="R57">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U57">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="V57">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y57">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>4.1</v>
+        <v>3.29</v>
       </c>
       <c r="AA57">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AB57">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC57">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD57">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="Q58">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T58">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U58">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="V58">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="W58">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AB58">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>2.66</v>
+        <v>3.64</v>
       </c>
       <c r="AD58">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P59">
-        <v>5.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q59">
-        <v>1.97</v>
+        <v>2.73</v>
       </c>
       <c r="R59">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="S59">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="U59">
-        <v>2.91</v>
+        <v>2.36</v>
       </c>
       <c r="V59">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z59">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA59">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC59">
-        <v>3.54</v>
+        <v>2.7</v>
       </c>
       <c r="AD59">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF59">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="AG59">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>2.33</v>
+        <v>1.63</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-02 16:00:00</t>
+          <t>2026-09-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="O60">
         <v>3.4</v>
       </c>
       <c r="P60">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q60">
+        <v>2.74</v>
+      </c>
+      <c r="R60">
+        <v>2.3</v>
+      </c>
+      <c r="S60">
+        <v>1.32</v>
+      </c>
+      <c r="T60">
         <v>3.25</v>
       </c>
-      <c r="R60">
-        <v>2.1</v>
-      </c>
-      <c r="S60">
-        <v>1.36</v>
-      </c>
-      <c r="T60">
-        <v>2.77</v>
-      </c>
       <c r="U60">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="V60">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W60">
         <v>1.08</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="AA60">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AB60">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="AD60">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE60">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF60">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG60">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-02 16:00:00</t>
+          <t>2026-09-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>5.25</v>
+        <v>1.49</v>
       </c>
       <c r="O61">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="S61">
+        <v>1.4</v>
+      </c>
+      <c r="T61">
+        <v>2.62</v>
+      </c>
+      <c r="U61">
+        <v>2.9</v>
+      </c>
+      <c r="V61">
+        <v>1.33</v>
+      </c>
+      <c r="W61">
+        <v>1.05</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>1.31</v>
+      </c>
+      <c r="Z61">
+        <v>3</v>
+      </c>
+      <c r="AA61">
+        <v>2.05</v>
+      </c>
+      <c r="AB61">
+        <v>1.75</v>
+      </c>
+      <c r="AC61">
+        <v>3.38</v>
+      </c>
+      <c r="AD61">
         <v>1.25</v>
       </c>
-      <c r="T61">
-        <v>3.34</v>
-      </c>
-      <c r="U61">
-        <v>2.23</v>
-      </c>
-      <c r="V61">
-        <v>1.56</v>
-      </c>
-      <c r="W61">
-        <v>1.14</v>
-      </c>
-      <c r="X61">
-        <v>1.01</v>
-      </c>
-      <c r="Y61">
-        <v>1.13</v>
-      </c>
-      <c r="Z61">
-        <v>4.6</v>
-      </c>
-      <c r="AA61">
-        <v>1.59</v>
-      </c>
-      <c r="AB61">
-        <v>2.31</v>
-      </c>
-      <c r="AC61">
+      <c r="AE61">
+        <v>1.05</v>
+      </c>
+      <c r="AF61">
+        <v>2.1</v>
+      </c>
+      <c r="AG61">
+        <v>1.66</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.22</v>
+      </c>
+      <c r="AK61">
         <v>2.38</v>
-      </c>
-      <c r="AD61">
-        <v>1.47</v>
-      </c>
-      <c r="AE61">
-        <v>1.15</v>
-      </c>
-      <c r="AF61">
-        <v>1.6</v>
-      </c>
-      <c r="AG61">
-        <v>2.15</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.21</v>
-      </c>
-      <c r="AK61">
-        <v>1.17</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="O62">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q62">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="R62">
         <v>2.2</v>
       </c>
       <c r="S62">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T62">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="V62">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="AA62">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC62">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AD62">
         <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG62">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK62">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P63">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="Q63">
-        <v>2.41</v>
+        <v>5.1</v>
       </c>
       <c r="R63">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>2.63</v>
+        <v>3.55</v>
       </c>
       <c r="U63">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="W63">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="AA63">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB63">
-        <v>1.61</v>
+        <v>2.31</v>
       </c>
       <c r="AC63">
-        <v>4.1</v>
+        <v>2.48</v>
       </c>
       <c r="AD63">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE63">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="AK63">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-02 18:30:00</t>
+          <t>2026-09-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="O64">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>6.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q64">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S64">
         <v>1.34</v>
       </c>
       <c r="T64">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="U64">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V64">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
         <v>1</v>
       </c>
       <c r="Y64">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA64">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB64">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AC64">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF64">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG64">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-02 19:00:00</t>
+          <t>2026-09-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="O65">
-        <v>5.65</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="Q65">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="R65">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="U65">
-        <v>2.36</v>
+        <v>3.18</v>
       </c>
       <c r="V65">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="Z65">
-        <v>4.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC65">
-        <v>2.41</v>
+        <v>3.95</v>
       </c>
       <c r="AD65">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AG65">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-02 19:30:00</t>
+          <t>2026-09-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="O66">
+        <v>4.4</v>
+      </c>
+      <c r="P66">
+        <v>6.3</v>
+      </c>
+      <c r="Q66">
+        <v>2.12</v>
+      </c>
+      <c r="R66">
+        <v>2.25</v>
+      </c>
+      <c r="S66">
+        <v>1.34</v>
+      </c>
+      <c r="T66">
+        <v>2.91</v>
+      </c>
+      <c r="U66">
+        <v>2.5</v>
+      </c>
+      <c r="V66">
+        <v>1.44</v>
+      </c>
+      <c r="W66">
+        <v>1.1</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>1.23</v>
+      </c>
+      <c r="Z66">
         <v>4.1</v>
       </c>
-      <c r="P66">
-        <v>5.9</v>
-      </c>
-      <c r="Q66">
-        <v>2.03</v>
-      </c>
-      <c r="R66">
-        <v>2.29</v>
-      </c>
-      <c r="S66">
-        <v>1.25</v>
-      </c>
-      <c r="T66">
-        <v>3.3</v>
-      </c>
-      <c r="U66">
-        <v>2.38</v>
-      </c>
-      <c r="V66">
-        <v>1.53</v>
-      </c>
-      <c r="W66">
+      <c r="AA66">
+        <v>1.79</v>
+      </c>
+      <c r="AB66">
+        <v>1.97</v>
+      </c>
+      <c r="AC66">
+        <v>2.83</v>
+      </c>
+      <c r="AD66">
+        <v>1.4</v>
+      </c>
+      <c r="AE66">
         <v>1.09</v>
       </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.22</v>
-      </c>
-      <c r="Z66">
-        <v>4.15</v>
-      </c>
-      <c r="AA66">
-        <v>1.63</v>
-      </c>
-      <c r="AB66">
-        <v>2.14</v>
-      </c>
-      <c r="AC66">
-        <v>2.49</v>
-      </c>
-      <c r="AD66">
-        <v>1.42</v>
-      </c>
-      <c r="AE66">
-        <v>1.17</v>
-      </c>
       <c r="AF66">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK66">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-02 20:00:00</t>
+          <t>2026-09-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="O67">
-        <v>2.53</v>
+        <v>5.65</v>
       </c>
       <c r="P67">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="Q67">
-        <v>3.06</v>
+        <v>1.67</v>
       </c>
       <c r="R67">
-        <v>1.84</v>
+        <v>2.58</v>
       </c>
       <c r="S67">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="U67">
-        <v>4.05</v>
+        <v>2.36</v>
       </c>
       <c r="V67">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>2.14</v>
+        <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB67">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>6</v>
+        <v>2.41</v>
       </c>
       <c r="AD67">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AE67">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AG67">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AK67">
-        <v>1.58</v>
+        <v>3.75</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-02 20:00:00</t>
+          <t>2026-09-02 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G68">
@@ -11389,68 +11389,68 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N68">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P68">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q68">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="S68">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="U68">
-        <v>3.32</v>
+        <v>2.38</v>
       </c>
       <c r="V68">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>2.52</v>
+        <v>4.15</v>
       </c>
       <c r="AA68">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AB68">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="AC68">
-        <v>4.33</v>
+        <v>2.49</v>
       </c>
       <c r="AD68">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF68">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-02 21:00:00</t>
+          <t>2026-09-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11509,27 +11509,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G69">
@@ -11552,68 +11552,68 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N69">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="O69">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="P69">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q69">
-        <v>4.2</v>
+        <v>3.06</v>
       </c>
       <c r="R69">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S69">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="T69">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="U69">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="V69">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y69">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="Z69">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="AA69">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AB69">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AC69">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AD69">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE69">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF69">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG69">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AK69">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-09-02 21:00:00</t>
+          <t>2026-09-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G70">
@@ -11715,68 +11715,68 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q70">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="R70">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T70">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="U70">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="V70">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z70">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="AA70">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB70">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC70">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="AD70">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AE70">
         <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AG70">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>1.31</v>
+        <v>2.08</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11835,156 +11835,482 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>US Biskra</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>3.64</v>
+      </c>
+      <c r="O71">
+        <v>2.8</v>
+      </c>
+      <c r="P71">
+        <v>2.15</v>
+      </c>
+      <c r="Q71">
+        <v>4.2</v>
+      </c>
+      <c r="R71">
+        <v>1.91</v>
+      </c>
+      <c r="S71">
+        <v>1.59</v>
+      </c>
+      <c r="T71">
+        <v>2.3</v>
+      </c>
+      <c r="U71">
+        <v>3.72</v>
+      </c>
+      <c r="V71">
+        <v>1.2</v>
+      </c>
+      <c r="W71">
+        <v>1.04</v>
+      </c>
+      <c r="X71">
+        <v>1.06</v>
+      </c>
+      <c r="Y71">
+        <v>1.52</v>
+      </c>
+      <c r="Z71">
+        <v>2.39</v>
+      </c>
+      <c r="AA71">
+        <v>2.56</v>
+      </c>
+      <c r="AB71">
+        <v>1.5</v>
+      </c>
+      <c r="AC71">
+        <v>5.15</v>
+      </c>
+      <c r="AD71">
+        <v>1.1</v>
+      </c>
+      <c r="AE71">
+        <v>1.04</v>
+      </c>
+      <c r="AF71">
+        <v>2.15</v>
+      </c>
+      <c r="AG71">
+        <v>1.59</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.61</v>
+      </c>
+      <c r="AK71">
+        <v>1.25</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CSD Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N72">
+        <v>2.98</v>
+      </c>
+      <c r="O72">
+        <v>3.15</v>
+      </c>
+      <c r="P72">
+        <v>2.2</v>
+      </c>
+      <c r="Q72">
+        <v>3.85</v>
+      </c>
+      <c r="R72">
+        <v>1.97</v>
+      </c>
+      <c r="S72">
+        <v>1.4</v>
+      </c>
+      <c r="T72">
+        <v>2.7</v>
+      </c>
+      <c r="U72">
+        <v>2.96</v>
+      </c>
+      <c r="V72">
+        <v>1.32</v>
+      </c>
+      <c r="W72">
+        <v>1.05</v>
+      </c>
+      <c r="X72">
+        <v>1.06</v>
+      </c>
+      <c r="Y72">
+        <v>1.32</v>
+      </c>
+      <c r="Z72">
+        <v>2.88</v>
+      </c>
+      <c r="AA72">
+        <v>2.1</v>
+      </c>
+      <c r="AB72">
+        <v>1.7</v>
+      </c>
+      <c r="AC72">
+        <v>3.8</v>
+      </c>
+      <c r="AD72">
+        <v>1.25</v>
+      </c>
+      <c r="AE72">
+        <v>1.08</v>
+      </c>
+      <c r="AF72">
+        <v>1.8</v>
+      </c>
+      <c r="AG72">
+        <v>1.86</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>1.31</v>
+      </c>
+      <c r="AK72">
+        <v>1.32</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>-1</v>
+      </c>
+      <c r="AN72">
+        <v>-1</v>
+      </c>
+      <c r="AO72">
+        <v>-1</v>
+      </c>
+      <c r="AP72">
+        <v>-1</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Ñublense</t>
         </is>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N71">
+      <c r="N73">
         <v>2.25</v>
       </c>
-      <c r="O71">
+      <c r="O73">
         <v>3.4</v>
       </c>
-      <c r="P71">
+      <c r="P73">
         <v>2.89</v>
       </c>
-      <c r="Q71">
+      <c r="Q73">
         <v>2.88</v>
       </c>
-      <c r="R71">
+      <c r="R73">
         <v>2.2</v>
       </c>
-      <c r="S71">
+      <c r="S73">
         <v>1.3</v>
       </c>
-      <c r="T71">
+      <c r="T73">
         <v>2.95</v>
       </c>
-      <c r="U71">
+      <c r="U73">
         <v>2.45</v>
       </c>
-      <c r="V71">
+      <c r="V73">
         <v>1.4</v>
       </c>
-      <c r="W71">
+      <c r="W73">
         <v>1.1</v>
       </c>
-      <c r="X71">
+      <c r="X73">
         <v>1</v>
       </c>
-      <c r="Y71">
+      <c r="Y73">
         <v>1.2</v>
       </c>
-      <c r="Z71">
+      <c r="Z73">
         <v>3.7</v>
       </c>
-      <c r="AA71">
+      <c r="AA73">
         <v>1.8</v>
       </c>
-      <c r="AB71">
+      <c r="AB73">
         <v>2</v>
       </c>
-      <c r="AC71">
+      <c r="AC73">
         <v>2.78</v>
       </c>
-      <c r="AD71">
+      <c r="AD73">
         <v>1.34</v>
       </c>
-      <c r="AE71">
+      <c r="AE73">
         <v>1.1</v>
       </c>
-      <c r="AF71">
+      <c r="AF73">
         <v>1.6</v>
       </c>
-      <c r="AG71">
+      <c r="AG73">
         <v>2.1</v>
       </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
         <v>1.25</v>
       </c>
-      <c r="AK71">
+      <c r="AK73">
         <v>1.53</v>
       </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-1</v>
+      </c>
+      <c r="AN73">
+        <v>-1</v>
+      </c>
+      <c r="AO73">
+        <v>-1</v>
+      </c>
+      <c r="AP73">
+        <v>-1</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>2026-09-02 21:30:00</t>
         </is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2754,55 +2754,55 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O15">
         <v>2.62</v>
       </c>
       <c r="P15">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q15">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="R15">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="S15">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="T15">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U15">
         <v>4.5</v>
       </c>
       <c r="V15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z15">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AA15">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AB15">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC15">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -2811,7 +2811,7 @@
         <v>2.3</v>
       </c>
       <c r="AG15">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.03</v>
+      </c>
+      <c r="O31">
+        <v>2.93</v>
+      </c>
+      <c r="P31">
+        <v>3.5</v>
+      </c>
+      <c r="Q31">
+        <v>2.75</v>
+      </c>
+      <c r="R31">
         <v>2</v>
       </c>
-      <c r="O31">
-        <v>2.9</v>
-      </c>
-      <c r="P31">
+      <c r="S31">
+        <v>1.52</v>
+      </c>
+      <c r="T31">
+        <v>2.5</v>
+      </c>
+      <c r="U31">
         <v>3.6</v>
-      </c>
-      <c r="Q31">
-        <v>2.7</v>
-      </c>
-      <c r="R31">
-        <v>1.87</v>
-      </c>
-      <c r="S31">
-        <v>1.57</v>
-      </c>
-      <c r="T31">
-        <v>2.24</v>
-      </c>
-      <c r="U31">
-        <v>3.7</v>
       </c>
       <c r="V31">
         <v>1.22</v>
@@ -5392,13 +5392,13 @@
         <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z31">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AA31">
         <v>2.46</v>
@@ -5407,19 +5407,19 @@
         <v>1.48</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD31">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE31">
         <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG31">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q40">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
       <c r="R40">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="S40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U40">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6865,25 +6865,25 @@
         <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA40">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB40">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AC40">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AD40">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE40">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
         <v>2.3</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O41">
         <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q41">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U41">
         <v>2.69</v>
@@ -7022,10 +7022,10 @@
         <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
         <v>3.42</v>
@@ -7034,22 +7034,22 @@
         <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC41">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AD41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AK41">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G43">
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G44">
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="O45">
         <v>4</v>
       </c>
       <c r="P45">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q45">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="R45">
         <v>2.44</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U45">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="V45">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X45">
         <v>1.02</v>
@@ -7680,13 +7680,13 @@
         <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA45">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB45">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AC45">
         <v>2.35</v>
@@ -7695,13 +7695,13 @@
         <v>1.6</v>
       </c>
       <c r="AE45">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF45">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>1.2</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q47">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="R47">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W47">
         <v>1.14</v>
@@ -8003,47 +8003,47 @@
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
         <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AD47">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AE47">
+        <v>1.24</v>
+      </c>
+      <c r="AF47">
+        <v>1.41</v>
+      </c>
+      <c r="AG47">
+        <v>2.64</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.28</v>
       </c>
-      <c r="AF47">
-        <v>1.42</v>
-      </c>
-      <c r="AG47">
-        <v>2.66</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.31</v>
-      </c>
       <c r="AK47">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>2.05</v>
       </c>
       <c r="AB61">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC61">
         <v>3.38</v>
@@ -10303,10 +10303,10 @@
         <v>1.25</v>
       </c>
       <c r="AE61">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF61">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG61">
         <v>1.66</v>
@@ -10907,10 +10907,10 @@
         <v>1.78</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P65">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q65">
         <v>2.41</v>
@@ -10922,10 +10922,10 @@
         <v>1.44</v>
       </c>
       <c r="T65">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U65">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V65">
         <v>1.31</v>
@@ -10934,28 +10934,28 @@
         <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y65">
         <v>1.4</v>
       </c>
       <c r="Z65">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB65">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AD65">
         <v>1.2</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF65">
         <v>1.98</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O66">
         <v>4.4</v>
@@ -11076,55 +11076,55 @@
         <v>6.3</v>
       </c>
       <c r="Q66">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="R66">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S66">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T66">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
+        <v>1.11</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
+        <v>1.24</v>
+      </c>
+      <c r="Z66">
+        <v>4</v>
+      </c>
+      <c r="AA66">
+        <v>1.73</v>
+      </c>
+      <c r="AB66">
+        <v>1.98</v>
+      </c>
+      <c r="AC66">
+        <v>2.7</v>
+      </c>
+      <c r="AD66">
+        <v>1.36</v>
+      </c>
+      <c r="AE66">
         <v>1.1</v>
       </c>
-      <c r="X66">
-        <v>1</v>
-      </c>
-      <c r="Y66">
-        <v>1.23</v>
-      </c>
-      <c r="Z66">
-        <v>4.1</v>
-      </c>
-      <c r="AA66">
-        <v>1.79</v>
-      </c>
-      <c r="AB66">
-        <v>1.97</v>
-      </c>
-      <c r="AC66">
-        <v>2.83</v>
-      </c>
-      <c r="AD66">
-        <v>1.4</v>
-      </c>
-      <c r="AE66">
-        <v>1.09</v>
-      </c>
       <c r="AF66">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG66">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.13</v>
       </c>
       <c r="AK66">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,19 +11233,19 @@
         <v>1.28</v>
       </c>
       <c r="O67">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="P67">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q67">
         <v>1.67</v>
       </c>
       <c r="R67">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
         <v>3.4</v>
@@ -11254,40 +11254,40 @@
         <v>2.36</v>
       </c>
       <c r="V67">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W67">
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
         <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AC67">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AD67">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE67">
         <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG67">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK67">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O68">
         <v>4.1</v>
       </c>
       <c r="P68">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="Q68">
         <v>2.03</v>
@@ -11411,31 +11411,31 @@
         <v>1.25</v>
       </c>
       <c r="T68">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U68">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z68">
         <v>4.15</v>
       </c>
       <c r="AA68">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AB68">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AC68">
         <v>2.49</v>
@@ -11444,7 +11444,7 @@
         <v>1.42</v>
       </c>
       <c r="AE68">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
         <v>1.7</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="P69">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="Q69">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R69">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="S69">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T69">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U69">
         <v>4.05</v>
@@ -11595,13 +11595,13 @@
         <v>2.14</v>
       </c>
       <c r="AA69">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB69">
         <v>1.32</v>
       </c>
       <c r="AC69">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="AD69">
         <v>1.08</v>
@@ -11610,7 +11610,7 @@
         <v>1.01</v>
       </c>
       <c r="AF69">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AG69">
         <v>1.51</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="O72">
         <v>3.15</v>
@@ -12060,10 +12060,10 @@
         <v>1.97</v>
       </c>
       <c r="S72">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T72">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U72">
         <v>2.96</v>
@@ -12211,28 +12211,28 @@
         <v>2.25</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P73">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="Q73">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R73">
         <v>2.2</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T73">
         <v>2.95</v>
       </c>
       <c r="U73">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V73">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
         <v>1.1</v>
@@ -12241,10 +12241,10 @@
         <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA73">
         <v>1.8</v>
@@ -12256,16 +12256,16 @@
         <v>2.78</v>
       </c>
       <c r="AD73">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG73">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q4">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U4">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z4">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AC4">
         <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="O5">
-        <v>3.56</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q5">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>3.18</v>
+        <v>2.41</v>
       </c>
       <c r="U5">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
+        <v>1.42</v>
+      </c>
+      <c r="Z5">
+        <v>2.64</v>
+      </c>
+      <c r="AA5">
+        <v>2.3</v>
+      </c>
+      <c r="AB5">
+        <v>1.61</v>
+      </c>
+      <c r="AC5">
+        <v>4.43</v>
+      </c>
+      <c r="AD5">
         <v>1.21</v>
       </c>
-      <c r="Z5">
-        <v>3.62</v>
-      </c>
-      <c r="AA5">
-        <v>1.78</v>
-      </c>
-      <c r="AB5">
-        <v>2.01</v>
-      </c>
-      <c r="AC5">
-        <v>2.94</v>
-      </c>
-      <c r="AD5">
-        <v>1.38</v>
-      </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6">
+        <v>2.04</v>
+      </c>
+      <c r="S6">
+        <v>1.36</v>
+      </c>
+      <c r="T6">
+        <v>2.69</v>
+      </c>
+      <c r="U6">
+        <v>2.89</v>
+      </c>
+      <c r="V6">
+        <v>1.36</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.02</v>
+      </c>
+      <c r="Y6">
+        <v>1.33</v>
+      </c>
+      <c r="Z6">
+        <v>3.2</v>
+      </c>
+      <c r="AA6">
         <v>2</v>
       </c>
-      <c r="S6">
-        <v>1.5</v>
-      </c>
-      <c r="T6">
-        <v>2.41</v>
-      </c>
-      <c r="U6">
-        <v>3.3</v>
-      </c>
-      <c r="V6">
-        <v>1.29</v>
-      </c>
-      <c r="W6">
-        <v>1.01</v>
-      </c>
-      <c r="X6">
-        <v>1.04</v>
-      </c>
-      <c r="Y6">
-        <v>1.42</v>
-      </c>
-      <c r="Z6">
-        <v>2.64</v>
-      </c>
-      <c r="AA6">
-        <v>2.3</v>
-      </c>
       <c r="AB6">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>4.43</v>
+        <v>3.55</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="U7">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
         <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>3.79</v>
       </c>
       <c r="AA7">
+        <v>1.85</v>
+      </c>
+      <c r="AB7">
+        <v>1.95</v>
+      </c>
+      <c r="AC7">
+        <v>3.15</v>
+      </c>
+      <c r="AD7">
+        <v>1.31</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
+        <v>1.67</v>
+      </c>
+      <c r="AG7">
         <v>2</v>
       </c>
-      <c r="AB7">
-        <v>1.8</v>
-      </c>
-      <c r="AC7">
-        <v>3.55</v>
-      </c>
-      <c r="AD7">
-        <v>1.28</v>
-      </c>
-      <c r="AE7">
-        <v>1.06</v>
-      </c>
-      <c r="AF7">
-        <v>1.8</v>
-      </c>
-      <c r="AG7">
-        <v>1.79</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="R8">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>2.86</v>
+      </c>
+      <c r="V8">
+        <v>1.4</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.24</v>
+      </c>
+      <c r="Z8">
+        <v>3.38</v>
+      </c>
+      <c r="AA8">
+        <v>1.9</v>
+      </c>
+      <c r="AB8">
+        <v>1.91</v>
+      </c>
+      <c r="AC8">
         <v>2.94</v>
       </c>
-      <c r="U8">
-        <v>2.65</v>
-      </c>
-      <c r="V8">
-        <v>1.42</v>
-      </c>
-      <c r="W8">
-        <v>1.05</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1.26</v>
-      </c>
-      <c r="Z8">
-        <v>3.79</v>
-      </c>
-      <c r="AA8">
-        <v>1.85</v>
-      </c>
-      <c r="AB8">
-        <v>1.95</v>
-      </c>
-      <c r="AC8">
-        <v>3.15</v>
-      </c>
       <c r="AD8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
         <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.74</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R50">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="U50">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="Z50">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AC50">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD50">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG50">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P51">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q51">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="U51">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AB51">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U53">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W53">
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA53">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK53">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
+        <v>3.5</v>
+      </c>
+      <c r="Q54">
         <v>2.5</v>
       </c>
-      <c r="Q54">
-        <v>3.1</v>
-      </c>
       <c r="R54">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U54">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V54">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W54">
         <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
+        <v>1.21</v>
+      </c>
+      <c r="Z54">
+        <v>4.4</v>
+      </c>
+      <c r="AA54">
+        <v>1.71</v>
+      </c>
+      <c r="AB54">
+        <v>2.08</v>
+      </c>
+      <c r="AC54">
+        <v>2.75</v>
+      </c>
+      <c r="AD54">
+        <v>1.39</v>
+      </c>
+      <c r="AE54">
+        <v>1.13</v>
+      </c>
+      <c r="AF54">
+        <v>1.61</v>
+      </c>
+      <c r="AG54">
+        <v>2.25</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
         <v>1.22</v>
       </c>
-      <c r="Z54">
-        <v>3.7</v>
-      </c>
-      <c r="AA54">
-        <v>1.82</v>
-      </c>
-      <c r="AB54">
-        <v>1.9</v>
-      </c>
-      <c r="AC54">
-        <v>3.1</v>
-      </c>
-      <c r="AD54">
-        <v>1.33</v>
-      </c>
-      <c r="AE54">
-        <v>1.11</v>
-      </c>
-      <c r="AF54">
-        <v>1.62</v>
-      </c>
-      <c r="AG54">
-        <v>2.15</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.33</v>
-      </c>
       <c r="AK54">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O66">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q66">
         <v>2.09</v>
       </c>
       <c r="R66">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S66">
         <v>1.31</v>
       </c>
       <c r="T66">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U66">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V66">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W66">
         <v>1.11</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA66">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB66">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC66">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AD66">
         <v>1.36</v>
       </c>
       <c r="AE66">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF66">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.13</v>
       </c>
       <c r="AK66">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Q67">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R67">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11260,7 +11260,7 @@
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.15</v>
@@ -11269,7 +11269,7 @@
         <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB67">
         <v>2.18</v>
@@ -11281,7 +11281,7 @@
         <v>1.49</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF67">
         <v>2</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK67">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O69">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P69">
         <v>3.27</v>
@@ -11571,10 +11571,10 @@
         <v>1.78</v>
       </c>
       <c r="S69">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T69">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U69">
         <v>4.05</v>
@@ -11589,16 +11589,16 @@
         <v>1.08</v>
       </c>
       <c r="Y69">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z69">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AA69">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AB69">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC69">
         <v>6.35</v>
@@ -12220,7 +12220,7 @@
         <v>2.9</v>
       </c>
       <c r="R73">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S73">
         <v>1.34</v>
@@ -12235,22 +12235,22 @@
         <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z73">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB73">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC73">
         <v>2.78</v>
@@ -12262,10 +12262,10 @@
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG73">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2760,58 +2760,58 @@
         <v>2.62</v>
       </c>
       <c r="P15">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="R15">
         <v>1.66</v>
       </c>
       <c r="S15">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T15">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U15">
         <v>4.5</v>
       </c>
       <c r="V15">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
         <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z15">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AA15">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AB15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC15">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
       <c r="AD15">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG15">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AK15">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         <v>3.2</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q16">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="R16">
         <v>2.18</v>
@@ -2947,22 +2947,22 @@
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AA16">
         <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AD16">
         <v>1.35</v>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,40 +3089,40 @@
         <v>4</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W17">
         <v>0</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3134,10 +3134,10 @@
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
         <v>2.9</v>
@@ -3415,40 +3415,40 @@
         <v>2.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19">
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3460,10 +3460,10 @@
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4580,22 +4580,22 @@
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z26">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA26">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB26">
         <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD26">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE26">
         <v>1.02</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>2.87</v>
       </c>
       <c r="Q27">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
         <v>2.09</v>
@@ -4743,16 +4743,16 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AA27">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
         <v>2.97</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="O29">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="P29">
-        <v>2.57</v>
+        <v>2.37</v>
       </c>
       <c r="Q29">
         <v>3.82</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
         <v>3.5</v>
@@ -5211,37 +5211,37 @@
         <v>2.5</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.54</v>
+        <v>3.89</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC30">
         <v>2.85</v>
@@ -5250,7 +5250,7 @@
         <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
         <v>1.67</v>
@@ -5272,7 +5272,7 @@
         <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="P31">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="Q31">
         <v>2.75</v>
@@ -5377,10 +5377,10 @@
         <v>2</v>
       </c>
       <c r="S31">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U31">
         <v>3.6</v>
@@ -5395,19 +5395,19 @@
         <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z31">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AA31">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AB31">
         <v>1.48</v>
       </c>
       <c r="AC31">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD31">
         <v>1.12</v>
@@ -5419,7 +5419,7 @@
         <v>2.1</v>
       </c>
       <c r="AG31">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
         <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="R33">
         <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
         <v>2.82</v>
@@ -5712,40 +5712,40 @@
         <v>2.78</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AD33">
         <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK33">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="R34">
         <v>2</v>
@@ -5869,7 +5869,7 @@
         <v>1.42</v>
       </c>
       <c r="T34">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U34">
         <v>2.96</v>
@@ -5884,22 +5884,22 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA34">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AB34">
         <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q35">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="R35">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="S35">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T35">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="U35">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z35">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA35">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB35">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AC35">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG35">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK35">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="O36">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="P36">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Q36">
-        <v>9.15</v>
+        <v>9.4</v>
       </c>
       <c r="R36">
         <v>2.31</v>
@@ -6198,43 +6198,43 @@
         <v>2.85</v>
       </c>
       <c r="U36">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
         <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD36">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
         <v>2.25</v>
       </c>
       <c r="AG36">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -6844,22 +6844,22 @@
         <v>2.59</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="V40">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W40">
         <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.14</v>
@@ -6868,25 +6868,25 @@
         <v>4.4</v>
       </c>
       <c r="AA40">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB40">
         <v>2.24</v>
       </c>
       <c r="AC40">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AD40">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
         <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.55</v>
+      </c>
+      <c r="O41">
+        <v>3.3</v>
+      </c>
+      <c r="P41">
         <v>2.5</v>
       </c>
-      <c r="O41">
-        <v>3.2</v>
-      </c>
-      <c r="P41">
-        <v>2.45</v>
-      </c>
       <c r="Q41">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R41">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
         <v>1.36</v>
@@ -7022,22 +7022,22 @@
         <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
         <v>3.42</v>
       </c>
       <c r="AA41">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB41">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="AD41">
         <v>1.3</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
         <v>1.44</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="Q42">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="R42">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
         <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="V42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>4.83</v>
+        <v>4.65</v>
       </c>
       <c r="AA42">
+        <v>1.6</v>
+      </c>
+      <c r="AB42">
+        <v>2.3</v>
+      </c>
+      <c r="AC42">
+        <v>2.5</v>
+      </c>
+      <c r="AD42">
+        <v>1.51</v>
+      </c>
+      <c r="AE42">
+        <v>1.17</v>
+      </c>
+      <c r="AF42">
         <v>1.53</v>
       </c>
-      <c r="AB42">
-        <v>2.25</v>
-      </c>
-      <c r="AC42">
-        <v>2.48</v>
-      </c>
-      <c r="AD42">
-        <v>1.5</v>
-      </c>
-      <c r="AE42">
-        <v>1.22</v>
-      </c>
-      <c r="AF42">
-        <v>1.47</v>
-      </c>
       <c r="AG42">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G43">
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G44">
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8133,37 +8133,37 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P48">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q48">
         <v>2.29</v>
       </c>
       <c r="R48">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U48">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V48">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W48">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.11</v>
@@ -8172,25 +8172,25 @@
         <v>5.75</v>
       </c>
       <c r="AA48">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AB48">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AC48">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AD48">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AE48">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF48">
         <v>1.4</v>
       </c>
       <c r="AG48">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P49">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
+        <v>3.75</v>
+      </c>
+      <c r="P50">
         <v>3.6</v>
       </c>
-      <c r="P50">
-        <v>4.25</v>
-      </c>
       <c r="Q50">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="R50">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="U50">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="AA50">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB50">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>3.38</v>
+        <v>2.78</v>
       </c>
       <c r="AD50">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AG50">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R51">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="U51">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.9</v>
+        <v>2.99</v>
       </c>
       <c r="AA51">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="AC51">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD51">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O52">
         <v>3.35</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q52">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
+        <v>1.37</v>
+      </c>
+      <c r="T52">
+        <v>2.77</v>
+      </c>
+      <c r="U52">
+        <v>2.77</v>
+      </c>
+      <c r="V52">
         <v>1.4</v>
-      </c>
-      <c r="T52">
-        <v>2.66</v>
-      </c>
-      <c r="U52">
-        <v>2.88</v>
-      </c>
-      <c r="V52">
-        <v>1.36</v>
       </c>
       <c r="W52">
         <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="AA52">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD52">
+        <v>1.28</v>
+      </c>
+      <c r="AE52">
+        <v>1.07</v>
+      </c>
+      <c r="AF52">
+        <v>1.7</v>
+      </c>
+      <c r="AG52">
+        <v>2.04</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.31</v>
       </c>
-      <c r="AE52">
-        <v>1.06</v>
-      </c>
-      <c r="AF52">
-        <v>1.71</v>
-      </c>
-      <c r="AG52">
-        <v>2.05</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.33</v>
-      </c>
       <c r="AK52">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,61 +8948,61 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q53">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R53">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S53">
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U53">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V53">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC53">
         <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG53">
         <v>2.15</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK53">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O54">
+        <v>3.7</v>
+      </c>
+      <c r="P54">
         <v>3.6</v>
       </c>
-      <c r="P54">
-        <v>3.5</v>
-      </c>
       <c r="Q54">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R54">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U54">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
         <v>2.75</v>
       </c>
       <c r="AD54">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
         <v>1.13</v>
       </c>
       <c r="AF54">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O55">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P55">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q55">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S55">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
         <v>2.99</v>
       </c>
       <c r="U55">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V55">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z55">
         <v>3.62</v>
       </c>
       <c r="AA55">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB55">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC55">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE55">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG55">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O56">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="P56">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q56">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R56">
-        <v>3.11</v>
+        <v>2.71</v>
       </c>
       <c r="S56">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>4.33</v>
+        <v>3.66</v>
       </c>
       <c r="U56">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V56">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W56">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="AA56">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB56">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AC56">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD56">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE56">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF56">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK56">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P57">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="Q57">
         <v>3.04</v>
@@ -9621,16 +9621,16 @@
         <v>2.69</v>
       </c>
       <c r="U57">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V57">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y57">
         <v>1.28</v>
@@ -9639,13 +9639,13 @@
         <v>3.29</v>
       </c>
       <c r="AA57">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB57">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC57">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="AD57">
         <v>1.28</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,46 +9769,46 @@
         <v>3.35</v>
       </c>
       <c r="P58">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R58">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S58">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T58">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="U58">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="V58">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
         <v>1.05</v>
       </c>
-      <c r="X58">
-        <v>1.01</v>
-      </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA58">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
         <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD58">
         <v>1.27</v>
@@ -9817,10 +9817,10 @@
         <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9929,16 +9929,16 @@
         <v>2.21</v>
       </c>
       <c r="O59">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="Q59">
         <v>2.73</v>
       </c>
       <c r="R59">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="S59">
         <v>1.3</v>
@@ -9947,43 +9947,43 @@
         <v>3.22</v>
       </c>
       <c r="U59">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V59">
         <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z59">
         <v>4.1</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB59">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AD59">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG59">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="O60">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q60">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S60">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T60">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U60">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="V60">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
         <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA60">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB60">
         <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD60">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE60">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF60">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="O62">
         <v>3.5</v>
       </c>
       <c r="P62">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q62">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R62">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S62">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T62">
         <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="V62">
+        <v>1.46</v>
+      </c>
+      <c r="W62">
+        <v>1.07</v>
+      </c>
+      <c r="X62">
+        <v>1.02</v>
+      </c>
+      <c r="Y62">
+        <v>1.19</v>
+      </c>
+      <c r="Z62">
+        <v>3.82</v>
+      </c>
+      <c r="AA62">
+        <v>1.74</v>
+      </c>
+      <c r="AB62">
+        <v>2.11</v>
+      </c>
+      <c r="AC62">
+        <v>2.86</v>
+      </c>
+      <c r="AD62">
+        <v>1.42</v>
+      </c>
+      <c r="AE62">
+        <v>1.16</v>
+      </c>
+      <c r="AF62">
+        <v>1.58</v>
+      </c>
+      <c r="AG62">
+        <v>2.2</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.3</v>
+      </c>
+      <c r="AK62">
         <v>1.44</v>
-      </c>
-      <c r="W62">
-        <v>1.06</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.22</v>
-      </c>
-      <c r="Z62">
-        <v>4.11</v>
-      </c>
-      <c r="AA62">
-        <v>1.7</v>
-      </c>
-      <c r="AB62">
-        <v>1.99</v>
-      </c>
-      <c r="AC62">
-        <v>2.66</v>
-      </c>
-      <c r="AD62">
-        <v>1.4</v>
-      </c>
-      <c r="AE62">
-        <v>1.13</v>
-      </c>
-      <c r="AF62">
-        <v>1.65</v>
-      </c>
-      <c r="AG62">
-        <v>2.21</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.27</v>
-      </c>
-      <c r="AK62">
-        <v>1.42</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,43 +10578,43 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.8</v>
+        <v>5.16</v>
       </c>
       <c r="O63">
         <v>4.1</v>
       </c>
       <c r="P63">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q63">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T63">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V63">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W63">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA63">
         <v>1.6</v>
@@ -10626,16 +10626,16 @@
         <v>2.48</v>
       </c>
       <c r="AD63">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE63">
         <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>2.31</v>
+        <v>1.18</v>
       </c>
       <c r="AK63">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,37 +10741,37 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P64">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="Q64">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R64">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S64">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
         <v>2.62</v>
       </c>
       <c r="V64">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W64">
         <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
         <v>1.25</v>
@@ -10780,10 +10780,10 @@
         <v>3.62</v>
       </c>
       <c r="AA64">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB64">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC64">
         <v>2.91</v>
@@ -10795,10 +10795,10 @@
         <v>1.15</v>
       </c>
       <c r="AF64">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG64">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL64">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
         <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="U4">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AA4">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC4">
         <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="P5">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S5">
         <v>1.5</v>
@@ -1145,19 +1145,19 @@
         <v>2.41</v>
       </c>
       <c r="U5">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W5">
         <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z5">
         <v>2.64</v>
@@ -1169,19 +1169,19 @@
         <v>1.61</v>
       </c>
       <c r="AC5">
-        <v>4.43</v>
+        <v>4.15</v>
       </c>
       <c r="AD5">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE5">
         <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG5">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
         <v>1.91</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="R6">
         <v>2.04</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
         <v>2.69</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="V6">
         <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB6">
         <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG6">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,43 +1450,43 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>3.7</v>
+        <v>1.88</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.79</v>
+        <v>3.38</v>
       </c>
       <c r="AA7">
         <v>1.85</v>
@@ -1495,16 +1495,16 @@
         <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="AD7">
         <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>3.82</v>
       </c>
       <c r="Q8">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
         <v>2.15</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U8">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
         <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AA8">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB8">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
         <v>2.94</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.74</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="O9">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S9">
         <v>1.28</v>
       </c>
       <c r="T9">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
         <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC9">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE9">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
         <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK9">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="Q10">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="R10">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S10">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="T10">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U10">
         <v>3.4</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W10">
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Z10">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AA10">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB10">
         <v>1.5</v>
       </c>
       <c r="AC10">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD10">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG10">
         <v>1.62</v>
@@ -2012,7 +2012,7 @@
         <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
         <v>3.25</v>
@@ -2117,49 +2117,49 @@
         <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
         <v>2.59</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AB11">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="AD11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AK11">
         <v>1.22</v>
@@ -2271,16 +2271,16 @@
         <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R12">
         <v>2.12</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
         <v>2.94</v>
@@ -2289,37 +2289,37 @@
         <v>2.65</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
         <v>3.62</v>
       </c>
       <c r="AA12">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="AD12">
         <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
         <v>2.14</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,46 +2434,46 @@
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="R13">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="U13">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB13">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AD13">
         <v>1.28</v>
@@ -2482,10 +2482,10 @@
         <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="O28">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>6.17</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="R28">
         <v>2.7</v>
       </c>
       <c r="S28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T28">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W28">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4909,10 +4909,10 @@
         <v>1.07</v>
       </c>
       <c r="Z28">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="AA28">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AB28">
         <v>2.85</v>
@@ -4921,16 +4921,16 @@
         <v>1.92</v>
       </c>
       <c r="AD28">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE28">
         <v>1.28</v>
       </c>
       <c r="AF28">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG28">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK28">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P45">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q45">
-        <v>4.57</v>
+        <v>4.44</v>
       </c>
       <c r="R45">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="S45">
         <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="U45">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V45">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W45">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
         <v>1.02</v>
@@ -7680,28 +7680,28 @@
         <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AA45">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AC45">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AD45">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE45">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF45">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG45">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>1.57</v>
       </c>
       <c r="O46">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q46">
         <v>1.96</v>
@@ -7822,40 +7822,40 @@
         <v>2.7</v>
       </c>
       <c r="S46">
+        <v>1.14</v>
+      </c>
+      <c r="T46">
+        <v>4.8</v>
+      </c>
+      <c r="U46">
+        <v>1.91</v>
+      </c>
+      <c r="V46">
+        <v>1.8</v>
+      </c>
+      <c r="W46">
         <v>1.2</v>
-      </c>
-      <c r="T46">
-        <v>4.2</v>
-      </c>
-      <c r="U46">
-        <v>2</v>
-      </c>
-      <c r="V46">
-        <v>1.7</v>
-      </c>
-      <c r="W46">
-        <v>1.18</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA46">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AB46">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AC46">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AD46">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE46">
         <v>1.35</v>
@@ -7976,25 +7976,25 @@
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q47">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U47">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V47">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W47">
         <v>1.14</v>
@@ -8003,31 +8003,31 @@
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA47">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB47">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC47">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD47">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AE47">
         <v>1.24</v>
       </c>
       <c r="AF47">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="U50">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA50">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="AC50">
-        <v>2.78</v>
+        <v>3.38</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="O51">
+        <v>3.75</v>
+      </c>
+      <c r="P51">
         <v>3.6</v>
       </c>
-      <c r="P51">
-        <v>4.25</v>
-      </c>
       <c r="Q51">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="U51">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>2.99</v>
+        <v>4.05</v>
       </c>
       <c r="AA51">
+        <v>1.72</v>
+      </c>
+      <c r="AB51">
         <v>2.1</v>
       </c>
-      <c r="AB51">
-        <v>1.72</v>
-      </c>
       <c r="AC51">
-        <v>3.38</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,22 +8785,22 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q52">
         <v>2.9</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T52">
         <v>2.77</v>
@@ -8809,40 +8809,40 @@
         <v>2.77</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA52">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC52">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AD52">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P54">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="R54">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T54">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U54">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="V54">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.94</v>
+        <v>3.62</v>
       </c>
       <c r="AA54">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC54">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
         <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="O55">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q55">
-        <v>3.14</v>
+        <v>2.46</v>
       </c>
       <c r="R55">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S55">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T55">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U55">
-        <v>2.69</v>
+        <v>2.32</v>
       </c>
       <c r="V55">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W55">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="AA55">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB55">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD55">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
         <v>1.65</v>
       </c>
       <c r="AG55">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q58">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="R58">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S58">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="U58">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
         <v>1.03</v>
       </c>
-      <c r="X58">
-        <v>1.05</v>
-      </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AB58">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
-        <v>3.44</v>
+        <v>2.64</v>
       </c>
       <c r="AD58">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O59">
+        <v>3.35</v>
+      </c>
+      <c r="P59">
         <v>3.7</v>
       </c>
-      <c r="P59">
-        <v>2.82</v>
-      </c>
       <c r="Q59">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="R59">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S59">
+        <v>1.42</v>
+      </c>
+      <c r="T59">
+        <v>2.83</v>
+      </c>
+      <c r="U59">
+        <v>2.99</v>
+      </c>
+      <c r="V59">
+        <v>1.34</v>
+      </c>
+      <c r="W59">
+        <v>1.03</v>
+      </c>
+      <c r="X59">
+        <v>1.05</v>
+      </c>
+      <c r="Y59">
         <v>1.3</v>
       </c>
-      <c r="T59">
-        <v>3.22</v>
-      </c>
-      <c r="U59">
-        <v>2.47</v>
-      </c>
-      <c r="V59">
-        <v>1.5</v>
-      </c>
-      <c r="W59">
-        <v>1.07</v>
-      </c>
-      <c r="X59">
-        <v>1.03</v>
-      </c>
-      <c r="Y59">
-        <v>1.2</v>
-      </c>
       <c r="Z59">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA59">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD59">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -10267,49 +10267,49 @@
         <v>2.13</v>
       </c>
       <c r="S61">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T61">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U61">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V61">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W61">
         <v>1.05</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y61">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z61">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA61">
         <v>2.05</v>
       </c>
       <c r="AB61">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC61">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AD61">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE61">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AG61">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK61">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
         <v>2.45</v>
       </c>
       <c r="Q62">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R62">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S62">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T62">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U62">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="V62">
         <v>1.46</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA62">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AC62">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="AD62">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10913,22 +10913,22 @@
         <v>4</v>
       </c>
       <c r="Q65">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R65">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V65">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W65">
         <v>1.05</v>
@@ -10943,7 +10943,7 @@
         <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB65">
         <v>1.61</v>
@@ -10958,10 +10958,10 @@
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK65">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P66">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="Q66">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R66">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
         <v>1.31</v>
       </c>
       <c r="T66">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V66">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
         <v>1.11</v>
@@ -11100,16 +11100,16 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="AA66">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC66">
         <v>2.85</v>
@@ -11118,13 +11118,13 @@
         <v>1.36</v>
       </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF66">
         <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,61 +11230,61 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="O67">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="P67">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Q67">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R67">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U67">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V67">
         <v>1.55</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA67">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="AD67">
         <v>1.49</v>
       </c>
       <c r="AE67">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG67">
         <v>1.73</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK67">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="O68">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P68">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="Q68">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R68">
         <v>2.29</v>
@@ -11414,13 +11414,13 @@
         <v>3.15</v>
       </c>
       <c r="U68">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="V68">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W68">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
         <v>1.02</v>
@@ -11429,19 +11429,19 @@
         <v>1.16</v>
       </c>
       <c r="Z68">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA68">
         <v>1.56</v>
       </c>
       <c r="AB68">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC68">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD68">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE68">
         <v>1.14</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK68">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O69">
         <v>2.75</v>
       </c>
       <c r="P69">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q69">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R69">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="S69">
         <v>1.63</v>
@@ -11577,10 +11577,10 @@
         <v>2.13</v>
       </c>
       <c r="U69">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="V69">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W69">
         <v>1.03</v>
@@ -11589,16 +11589,16 @@
         <v>1.08</v>
       </c>
       <c r="Y69">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z69">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA69">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB69">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC69">
         <v>6.35</v>
@@ -11613,7 +11613,7 @@
         <v>2.14</v>
       </c>
       <c r="AG69">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O72">
         <v>3.15</v>
@@ -12054,34 +12054,34 @@
         <v>2.2</v>
       </c>
       <c r="Q72">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="R72">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S72">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T72">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U72">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V72">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W72">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z72">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA72">
         <v>2.1</v>
@@ -12090,10 +12090,10 @@
         <v>1.7</v>
       </c>
       <c r="AC72">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="AD72">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE72">
         <v>1.08</v>
@@ -12102,7 +12102,7 @@
         <v>1.8</v>
       </c>
       <c r="AG72">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.31</v>
       </c>
       <c r="AK72">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,10 +12211,10 @@
         <v>2.25</v>
       </c>
       <c r="O73">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q73">
         <v>2.9</v>
@@ -12238,34 +12238,34 @@
         <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
         <v>3.7</v>
       </c>
       <c r="AA73">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC73">
         <v>2.78</v>
       </c>
       <c r="AD73">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG73">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL73">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>1.85</v>
+      </c>
+      <c r="O6">
         <v>3.6</v>
       </c>
-      <c r="O6">
-        <v>3.2</v>
-      </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>3.82</v>
       </c>
       <c r="Q6">
-        <v>4.55</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="U6">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="AA6">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC6">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>1.19</v>
+        <v>1.78</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>3.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>4.55</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="U8">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AD8">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.78</v>
+        <v>1.19</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O58">
+        <v>3.35</v>
+      </c>
+      <c r="P58">
         <v>3.7</v>
       </c>
-      <c r="P58">
-        <v>2.82</v>
-      </c>
       <c r="Q58">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="R58">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S58">
+        <v>1.42</v>
+      </c>
+      <c r="T58">
+        <v>2.83</v>
+      </c>
+      <c r="U58">
+        <v>2.99</v>
+      </c>
+      <c r="V58">
+        <v>1.34</v>
+      </c>
+      <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
+        <v>1.05</v>
+      </c>
+      <c r="Y58">
         <v>1.3</v>
       </c>
-      <c r="T58">
-        <v>3.22</v>
-      </c>
-      <c r="U58">
-        <v>2.47</v>
-      </c>
-      <c r="V58">
-        <v>1.5</v>
-      </c>
-      <c r="W58">
-        <v>1.07</v>
-      </c>
-      <c r="X58">
-        <v>1.03</v>
-      </c>
-      <c r="Y58">
-        <v>1.2</v>
-      </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA58">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD58">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="O59">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q59">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="R59">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S59">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="U59">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="V59">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
+        <v>1.07</v>
+      </c>
+      <c r="X59">
         <v>1.03</v>
       </c>
-      <c r="X59">
-        <v>1.05</v>
-      </c>
       <c r="Y59">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z59">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="AA59">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AB59">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>3.44</v>
+        <v>2.64</v>
       </c>
       <c r="AD59">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG59">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL59">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,49 +1287,49 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
-        <v>3.82</v>
+        <v>1.88</v>
       </c>
       <c r="Q6">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R6">
         <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
         <v>2.89</v>
       </c>
       <c r="U6">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z6">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AA6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
         <v>2.94</v>
@@ -1341,10 +1341,10 @@
         <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,49 +1450,49 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.88</v>
+        <v>3.82</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
         <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
         <v>2.89</v>
       </c>
       <c r="U7">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC7">
         <v>2.94</v>
@@ -1504,10 +1504,10 @@
         <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>2.62</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q15">
         <v>3.82</v>
@@ -2769,13 +2769,13 @@
         <v>1.66</v>
       </c>
       <c r="S15">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="T15">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="U15">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="V15">
         <v>1.15</v>
@@ -2787,28 +2787,28 @@
         <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z15">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AA15">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AB15">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC15">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AD15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG15">
         <v>1.53</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O16">
+        <v>3.4</v>
+      </c>
+      <c r="P16">
+        <v>2.05</v>
+      </c>
+      <c r="Q16">
         <v>3.6</v>
       </c>
-      <c r="P16">
-        <v>1.97</v>
-      </c>
-      <c r="Q16">
-        <v>3.96</v>
-      </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U16">
         <v>2.53</v>
@@ -2947,25 +2947,25 @@
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA16">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC16">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD16">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.23</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
         <v>2.7</v>
       </c>
       <c r="P18">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
+        <v>2.6</v>
+      </c>
+      <c r="O19">
+        <v>2.95</v>
+      </c>
+      <c r="P19">
         <v>2.65</v>
-      </c>
-      <c r="O19">
-        <v>2.9</v>
-      </c>
-      <c r="P19">
-        <v>2.5</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
       </c>
       <c r="R19">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="S19">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T19">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U19">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V19">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y19">
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AA19">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AB19">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK19">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>2.37</v>
       </c>
       <c r="Q29">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="R29">
         <v>1.89</v>
@@ -5087,13 +5087,13 @@
         <v>1.11</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
         <v>2.09</v>
       </c>
       <c r="AG29">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AK29">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="O31">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P31">
-        <v>3.86</v>
+        <v>2.55</v>
       </c>
       <c r="Q31">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="S31">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="T31">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="U31">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="V31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W31">
         <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y31">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="Z31">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AA31">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AB31">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AC31">
-        <v>4.7</v>
+        <v>5.92</v>
       </c>
       <c r="AD31">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AG31">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AK31">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="P32">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
         <v>1.35</v>
@@ -5712,7 +5712,7 @@
         <v>2.78</v>
       </c>
       <c r="V33">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
         <v>1.04</v>
@@ -5721,10 +5721,10 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
         <v>1.95</v>
@@ -5733,19 +5733,19 @@
         <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
         <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
         <v>1.47</v>
@@ -5875,28 +5875,28 @@
         <v>2.96</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
         <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA34">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC34">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD34">
         <v>1.22</v>
@@ -5905,10 +5905,10 @@
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="O45">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P45">
-        <v>1.72</v>
+        <v>4.33</v>
       </c>
       <c r="Q45">
-        <v>4.44</v>
+        <v>1.96</v>
       </c>
       <c r="R45">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T45">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="U45">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="V45">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>5.15</v>
+        <v>7.5</v>
       </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AB45">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC45">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AD45">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AE45">
+        <v>1.35</v>
+      </c>
+      <c r="AF45">
+        <v>1.42</v>
+      </c>
+      <c r="AG45">
+        <v>2.69</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.21</v>
       </c>
-      <c r="AF45">
-        <v>1.47</v>
-      </c>
-      <c r="AG45">
-        <v>2.47</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.2</v>
-      </c>
       <c r="AK45">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="O46">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P46">
-        <v>4.33</v>
+        <v>1.72</v>
       </c>
       <c r="Q46">
-        <v>1.96</v>
+        <v>4.44</v>
       </c>
       <c r="R46">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="S46">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="U46">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="V46">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.1</v>
+      </c>
+      <c r="Z46">
+        <v>5.15</v>
+      </c>
+      <c r="AA46">
+        <v>1.44</v>
+      </c>
+      <c r="AB46">
+        <v>2.5</v>
+      </c>
+      <c r="AC46">
+        <v>2.23</v>
+      </c>
+      <c r="AD46">
+        <v>1.63</v>
+      </c>
+      <c r="AE46">
+        <v>1.21</v>
+      </c>
+      <c r="AF46">
+        <v>1.47</v>
+      </c>
+      <c r="AG46">
+        <v>2.47</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.2</v>
       </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.08</v>
-      </c>
-      <c r="Z46">
-        <v>7.5</v>
-      </c>
-      <c r="AA46">
-        <v>1.35</v>
-      </c>
-      <c r="AB46">
-        <v>2.9</v>
-      </c>
-      <c r="AC46">
-        <v>1.84</v>
-      </c>
-      <c r="AD46">
-        <v>1.82</v>
-      </c>
-      <c r="AE46">
-        <v>1.35</v>
-      </c>
-      <c r="AF46">
-        <v>1.42</v>
-      </c>
-      <c r="AG46">
-        <v>2.69</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.21</v>
-      </c>
       <c r="AK46">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="O54">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
-        <v>3.14</v>
+        <v>2.46</v>
       </c>
       <c r="R54">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S54">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U54">
-        <v>2.69</v>
+        <v>2.32</v>
       </c>
       <c r="V54">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="AA54">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
         <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P55">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q55">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="R55">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S55">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U55">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z55">
-        <v>3.94</v>
+        <v>3.62</v>
       </c>
       <c r="AA55">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB55">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC55">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE55">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF55">
         <v>1.65</v>
       </c>
       <c r="AG55">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q58">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="R58">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S58">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="U58">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
         <v>1.03</v>
       </c>
-      <c r="X58">
-        <v>1.05</v>
-      </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AB58">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
-        <v>3.44</v>
+        <v>2.64</v>
       </c>
       <c r="AD58">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O59">
+        <v>3.35</v>
+      </c>
+      <c r="P59">
         <v>3.7</v>
       </c>
-      <c r="P59">
-        <v>2.82</v>
-      </c>
       <c r="Q59">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="R59">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S59">
+        <v>1.42</v>
+      </c>
+      <c r="T59">
+        <v>2.83</v>
+      </c>
+      <c r="U59">
+        <v>2.99</v>
+      </c>
+      <c r="V59">
+        <v>1.34</v>
+      </c>
+      <c r="W59">
+        <v>1.03</v>
+      </c>
+      <c r="X59">
+        <v>1.05</v>
+      </c>
+      <c r="Y59">
         <v>1.3</v>
       </c>
-      <c r="T59">
-        <v>3.22</v>
-      </c>
-      <c r="U59">
-        <v>2.47</v>
-      </c>
-      <c r="V59">
-        <v>1.5</v>
-      </c>
-      <c r="W59">
-        <v>1.07</v>
-      </c>
-      <c r="X59">
-        <v>1.03</v>
-      </c>
-      <c r="Y59">
-        <v>1.2</v>
-      </c>
       <c r="Z59">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA59">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD59">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL59">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
         <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q4">
         <v>3.9</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
         <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
         <v>1.42</v>
@@ -994,22 +994,22 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z4">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
@@ -1018,7 +1018,7 @@
         <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R5">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T5">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U5">
         <v>3.34</v>
@@ -1154,7 +1154,7 @@
         <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.38</v>
@@ -1166,22 +1166,22 @@
         <v>2.3</v>
       </c>
       <c r="AB5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD5">
         <v>1.16</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK5">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R6">
         <v>2.15</v>
@@ -1308,7 +1308,7 @@
         <v>2.89</v>
       </c>
       <c r="U6">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="V6">
         <v>1.41</v>
@@ -1326,10 +1326,10 @@
         <v>3.38</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
         <v>2.94</v>
@@ -1341,7 +1341,7 @@
         <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>3.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
+        <v>2.69</v>
+      </c>
+      <c r="U7">
         <v>2.89</v>
       </c>
-      <c r="U7">
-        <v>2.75</v>
-      </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="Z7">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="AA7">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AB7">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC7">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="AD7">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q8">
-        <v>4.55</v>
+        <v>2.49</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
+        <v>1.36</v>
+      </c>
+      <c r="T8">
+        <v>2.89</v>
+      </c>
+      <c r="U8">
+        <v>2.69</v>
+      </c>
+      <c r="V8">
         <v>1.41</v>
       </c>
-      <c r="T8">
-        <v>2.69</v>
-      </c>
-      <c r="U8">
-        <v>3.01</v>
-      </c>
-      <c r="V8">
-        <v>1.36</v>
-      </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="AA8">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AG8">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q9">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA9">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD9">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
+        <v>1.67</v>
+      </c>
+      <c r="AG9">
+        <v>2.08</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.29</v>
+      </c>
+      <c r="AK9">
         <v>1.68</v>
-      </c>
-      <c r="AG9">
-        <v>2.06</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.16</v>
-      </c>
-      <c r="AK9">
-        <v>2.45</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>1.52</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>2.03</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>4.81</v>
+        <v>1.97</v>
       </c>
       <c r="R10">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="S10">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="T10">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="U10">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="V10">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
+        <v>1.09</v>
+      </c>
+      <c r="X10">
         <v>1.01</v>
       </c>
-      <c r="X10">
-        <v>1.08</v>
-      </c>
       <c r="Y10">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>2.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA10">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB10">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="AD10">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF10">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P11">
         <v>2.05</v>
       </c>
       <c r="Q11">
-        <v>3.86</v>
+        <v>4.65</v>
       </c>
       <c r="R11">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="U11">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="AA11">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC11">
-        <v>3.38</v>
+        <v>4.7</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AG11">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="AK11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
+        <v>1.41</v>
+      </c>
+      <c r="T12">
+        <v>2.69</v>
+      </c>
+      <c r="U12">
+        <v>2.94</v>
+      </c>
+      <c r="V12">
         <v>1.35</v>
       </c>
-      <c r="T12">
-        <v>2.94</v>
-      </c>
-      <c r="U12">
-        <v>2.65</v>
-      </c>
-      <c r="V12">
-        <v>1.45</v>
-      </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.62</v>
+        <v>3.12</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
-        <v>2.89</v>
+        <v>3.38</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>3.5</v>
+      </c>
+      <c r="P13">
         <v>2.1</v>
       </c>
-      <c r="O13">
-        <v>3.2</v>
-      </c>
-      <c r="P13">
-        <v>3</v>
-      </c>
       <c r="Q13">
-        <v>2.72</v>
+        <v>3.74</v>
       </c>
       <c r="R13">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z13">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="AA13">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="AD13">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG13">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q26">
         <v>2.41</v>
@@ -4568,31 +4568,31 @@
         <v>2.44</v>
       </c>
       <c r="U26">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="V26">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z26">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA26">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB26">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC26">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD26">
         <v>1.16</v>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,37 +4716,37 @@
         <v>3.2</v>
       </c>
       <c r="P27">
+        <v>2.8</v>
+      </c>
+      <c r="Q27">
         <v>2.87</v>
       </c>
-      <c r="Q27">
-        <v>2.9</v>
-      </c>
       <c r="R27">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
+        <v>1.36</v>
+      </c>
+      <c r="T27">
+        <v>2.85</v>
+      </c>
+      <c r="U27">
+        <v>2.73</v>
+      </c>
+      <c r="V27">
         <v>1.39</v>
       </c>
-      <c r="T27">
-        <v>2.7</v>
-      </c>
-      <c r="U27">
-        <v>2.69</v>
-      </c>
-      <c r="V27">
-        <v>1.4</v>
-      </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
         <v>1.95</v>
@@ -4755,19 +4755,19 @@
         <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
         <v>1.58</v>
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="U30">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W30">
         <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
+        <v>1.22</v>
+      </c>
+      <c r="Z30">
+        <v>4.1</v>
+      </c>
+      <c r="AA30">
+        <v>1.83</v>
+      </c>
+      <c r="AB30">
+        <v>2.01</v>
+      </c>
+      <c r="AC30">
+        <v>2.88</v>
+      </c>
+      <c r="AD30">
+        <v>1.4</v>
+      </c>
+      <c r="AE30">
+        <v>1.1</v>
+      </c>
+      <c r="AF30">
+        <v>1.66</v>
+      </c>
+      <c r="AG30">
+        <v>2.09</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.25</v>
       </c>
-      <c r="Z30">
-        <v>3.89</v>
-      </c>
-      <c r="AA30">
-        <v>1.8</v>
-      </c>
-      <c r="AB30">
-        <v>2</v>
-      </c>
-      <c r="AC30">
-        <v>2.85</v>
-      </c>
-      <c r="AD30">
-        <v>1.33</v>
-      </c>
-      <c r="AE30">
-        <v>1.14</v>
-      </c>
-      <c r="AF30">
-        <v>1.67</v>
-      </c>
-      <c r="AG30">
-        <v>2.08</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.26</v>
-      </c>
       <c r="AK30">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.4</v>
       </c>
       <c r="O35">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P35">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q35">
         <v>1.87</v>
@@ -6035,19 +6035,19 @@
         <v>3.44</v>
       </c>
       <c r="U35">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W35">
         <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
         <v>4.65</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="O36">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="P36">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q36">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="R36">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6201,7 +6201,7 @@
         <v>2.66</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W36">
         <v>1.06</v>
@@ -6219,10 +6219,10 @@
         <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="AD36">
         <v>1.31</v>
@@ -6231,10 +6231,10 @@
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AG36">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>4.6</v>
+      </c>
+      <c r="O40">
         <v>4.2</v>
       </c>
-      <c r="O40">
-        <v>3.9</v>
-      </c>
       <c r="P40">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Q40">
-        <v>4.33</v>
+        <v>5.18</v>
       </c>
       <c r="R40">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="V40">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z40">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA40">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AB40">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AC40">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AD40">
+        <v>1.59</v>
+      </c>
+      <c r="AE40">
+        <v>1.21</v>
+      </c>
+      <c r="AF40">
         <v>1.53</v>
       </c>
-      <c r="AE40">
-        <v>1.2</v>
-      </c>
-      <c r="AF40">
-        <v>1.57</v>
-      </c>
       <c r="AG40">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q41">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="R41">
         <v>2.1</v>
@@ -7022,7 +7022,7 @@
         <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.23</v>
@@ -7065,7 +7065,7 @@
         <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,49 +7155,49 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O42">
         <v>3.4</v>
       </c>
       <c r="P42">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q42">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="R42">
         <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W42">
         <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB42">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC42">
         <v>2.5</v>
@@ -7206,13 +7206,13 @@
         <v>1.51</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG42">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7481,28 +7481,28 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="R44">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S44">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T44">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U44">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V44">
         <v>1.26</v>
@@ -7511,7 +7511,7 @@
         <v>1.02</v>
       </c>
       <c r="X44">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
         <v>1.42</v>
@@ -7520,7 +7520,7 @@
         <v>2.49</v>
       </c>
       <c r="AA44">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AB44">
         <v>1.52</v>
@@ -7529,16 +7529,16 @@
         <v>5</v>
       </c>
       <c r="AD44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE44">
         <v>1.01</v>
       </c>
       <c r="AF44">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG44">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,61 +7647,61 @@
         <v>1.57</v>
       </c>
       <c r="O45">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P45">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q45">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R45">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="S45">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="U45">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V45">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z45">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA45">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB45">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC45">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AD45">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AE45">
         <v>1.35</v>
       </c>
       <c r="AF45">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q46">
-        <v>4.44</v>
+        <v>4.51</v>
       </c>
       <c r="R46">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T46">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U46">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="V46">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB46">
         <v>2.5</v>
       </c>
       <c r="AC46">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AD46">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE46">
+        <v>1.23</v>
+      </c>
+      <c r="AF46">
+        <v>1.46</v>
+      </c>
+      <c r="AG46">
+        <v>2.53</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.21</v>
       </c>
-      <c r="AF46">
-        <v>1.47</v>
-      </c>
-      <c r="AG46">
-        <v>2.47</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.2</v>
-      </c>
       <c r="AK46">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7976,25 +7976,25 @@
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q47">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="R47">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
         <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U47">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V47">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="W47">
         <v>1.14</v>
@@ -8006,28 +8006,28 @@
         <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA47">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB47">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AC47">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AD47">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE47">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG47">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK47">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,58 +8133,58 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O48">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P48">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="Q48">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="R48">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T48">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V48">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z48">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA48">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB48">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AC48">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD48">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF48">
         <v>1.4</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O49">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="P49">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
+        <v>3.75</v>
+      </c>
+      <c r="P50">
         <v>3.6</v>
       </c>
-      <c r="P50">
-        <v>4.6</v>
-      </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="R50">
+        <v>2.31</v>
+      </c>
+      <c r="S50">
+        <v>1.28</v>
+      </c>
+      <c r="T50">
+        <v>3.3</v>
+      </c>
+      <c r="U50">
+        <v>2.44</v>
+      </c>
+      <c r="V50">
+        <v>1.49</v>
+      </c>
+      <c r="W50">
+        <v>1.08</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.17</v>
+      </c>
+      <c r="Z50">
+        <v>4.05</v>
+      </c>
+      <c r="AA50">
+        <v>1.72</v>
+      </c>
+      <c r="AB50">
         <v>2.1</v>
       </c>
-      <c r="S50">
-        <v>1.4</v>
-      </c>
-      <c r="T50">
-        <v>2.69</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
-      <c r="V50">
-        <v>1.36</v>
-      </c>
-      <c r="W50">
-        <v>1.05</v>
-      </c>
-      <c r="X50">
-        <v>1.06</v>
-      </c>
-      <c r="Y50">
-        <v>1.3</v>
-      </c>
-      <c r="Z50">
-        <v>3.1</v>
-      </c>
-      <c r="AA50">
-        <v>2.1</v>
-      </c>
-      <c r="AB50">
-        <v>1.73</v>
-      </c>
       <c r="AC50">
-        <v>3.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG50">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O51">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q51">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="U51">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="Z51">
-        <v>4.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA51">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>3.38</v>
       </c>
       <c r="AD51">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AG51">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="Q52">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S52">
         <v>1.39</v>
@@ -8809,40 +8809,40 @@
         <v>2.77</v>
       </c>
       <c r="V52">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W52">
         <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA52">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC52">
         <v>3.12</v>
       </c>
       <c r="AD52">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.31</v>
       </c>
       <c r="AK52">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q53">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="R53">
         <v>2.1</v>
@@ -8984,7 +8984,7 @@
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA53">
         <v>1.8</v>
@@ -8993,7 +8993,7 @@
         <v>2</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD53">
         <v>1.35</v>
@@ -9005,7 +9005,7 @@
         <v>1.61</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q54">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="R54">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T54">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U54">
-        <v>2.32</v>
+        <v>2.65</v>
       </c>
       <c r="V54">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z54">
-        <v>3.94</v>
+        <v>3.62</v>
       </c>
       <c r="AA54">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC54">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AD54">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="O55">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q55">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="R55">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U55">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="V55">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W55">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="AA55">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB55">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="AD55">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG55">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="O56">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="P56">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Q56">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R56">
         <v>2.71</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T56">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U56">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="V56">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W56">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z56">
-        <v>6.33</v>
+        <v>5.65</v>
       </c>
       <c r="AA56">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC56">
         <v>1.94</v>
       </c>
       <c r="AD56">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AE56">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF56">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG56">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.11</v>
       </c>
       <c r="AK56">
-        <v>3.98</v>
+        <v>3.78</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O57">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="Q57">
         <v>3.04</v>
@@ -9636,28 +9636,28 @@
         <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="AA57">
         <v>2.03</v>
       </c>
       <c r="AB57">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC57">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="AD57">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE57">
         <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG57">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK57">
         <v>1.54</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="Q58">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R58">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="S58">
         <v>1.3</v>
@@ -9787,25 +9787,25 @@
         <v>2.47</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
         <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
         <v>4.1</v>
       </c>
       <c r="AA58">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC58">
         <v>2.64</v>
@@ -9814,13 +9814,13 @@
         <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG58">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK58">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O59">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
         <v>3.7</v>
@@ -9941,22 +9941,22 @@
         <v>2.03</v>
       </c>
       <c r="S59">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T59">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="U59">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="V59">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W59">
         <v>1.03</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.3</v>
@@ -9965,25 +9965,25 @@
         <v>2.99</v>
       </c>
       <c r="AA59">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB59">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC59">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AD59">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE59">
         <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,19 +10098,19 @@
         <v>2.9</v>
       </c>
       <c r="Q60">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R60">
         <v>2.15</v>
       </c>
       <c r="S60">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T60">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="U60">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="V60">
         <v>1.46</v>
@@ -10122,22 +10122,22 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z60">
         <v>3.96</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB60">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC60">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AD60">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE60">
         <v>1.1</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -10430,7 +10430,7 @@
         <v>2.25</v>
       </c>
       <c r="S62">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T62">
         <v>3.1</v>
@@ -10442,7 +10442,7 @@
         <v>1.46</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X62">
         <v>1.03</v>
@@ -10451,25 +10451,25 @@
         <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA62">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB62">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC62">
         <v>2.95</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG62">
         <v>2.23</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
         <v>1.41</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>5.16</v>
+        <v>4.8</v>
       </c>
       <c r="O63">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P63">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Q63">
         <v>5.3</v>
@@ -10596,7 +10596,7 @@
         <v>1.28</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U63">
         <v>2.34</v>
@@ -10614,25 +10614,25 @@
         <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA63">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB63">
         <v>2.31</v>
       </c>
       <c r="AC63">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD63">
         <v>1.47</v>
       </c>
       <c r="AE63">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF63">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
         <v>2.18</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,28 +10741,28 @@
         </is>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O64">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P64">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="Q64">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="R64">
         <v>2.19</v>
       </c>
       <c r="S64">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U64">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V64">
         <v>1.45</v>
@@ -10771,34 +10771,34 @@
         <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z64">
         <v>3.62</v>
       </c>
       <c r="AA64">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB64">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC64">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="AD64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE64">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF64">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG64">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL64">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="Q6">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U6">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AA6">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>4.6</v>
+        <v>2.49</v>
       </c>
       <c r="R7">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S7">
+        <v>1.36</v>
+      </c>
+      <c r="T7">
+        <v>2.89</v>
+      </c>
+      <c r="U7">
+        <v>2.69</v>
+      </c>
+      <c r="V7">
         <v>1.41</v>
       </c>
-      <c r="T7">
-        <v>2.69</v>
-      </c>
-      <c r="U7">
-        <v>2.89</v>
-      </c>
-      <c r="V7">
-        <v>1.36</v>
-      </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.95</v>
+        <v>3.13</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
-        <v>2.49</v>
+        <v>4.4</v>
       </c>
       <c r="R8">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.36</v>
@@ -1634,43 +1634,43 @@
         <v>2.89</v>
       </c>
       <c r="U8">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="V8">
         <v>1.41</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z8">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AA8">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC8">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="AD8">
         <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="U9">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z9">
-        <v>3.54</v>
+        <v>2.95</v>
       </c>
       <c r="AA9">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC9">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>2.62</v>
       </c>
       <c r="P15">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="R15">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S15">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="T15">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="U15">
         <v>4.25</v>
@@ -2784,7 +2784,7 @@
         <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y15">
         <v>1.65</v>
@@ -2793,16 +2793,16 @@
         <v>2.11</v>
       </c>
       <c r="AA15">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB15">
         <v>1.36</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AD15">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AK15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="Q26">
+        <v>2.49</v>
+      </c>
+      <c r="R26">
+        <v>1.95</v>
+      </c>
+      <c r="S26">
+        <v>1.47</v>
+      </c>
+      <c r="T26">
         <v>2.41</v>
-      </c>
-      <c r="R26">
-        <v>1.97</v>
-      </c>
-      <c r="S26">
-        <v>1.44</v>
-      </c>
-      <c r="T26">
-        <v>2.44</v>
       </c>
       <c r="U26">
         <v>3.18</v>
@@ -4574,25 +4574,25 @@
         <v>1.28</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA26">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB26">
         <v>1.58</v>
       </c>
       <c r="AC26">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD26">
         <v>1.16</v>
@@ -4601,10 +4601,10 @@
         <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q28">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R28">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
         <v>1.19</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U28">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W28">
         <v>1.14</v>
@@ -4912,25 +4912,25 @@
         <v>5.9</v>
       </c>
       <c r="AA28">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB28">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC28">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AD28">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF28">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG28">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.16</v>
       </c>
       <c r="AK28">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -5232,22 +5232,22 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA30">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB30">
         <v>2.01</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE30">
         <v>1.1</v>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.99</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P31">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q31">
-        <v>3.75</v>
+        <v>2.77</v>
       </c>
       <c r="R31">
+        <v>2</v>
+      </c>
+      <c r="S31">
+        <v>1.56</v>
+      </c>
+      <c r="T31">
+        <v>2.26</v>
+      </c>
+      <c r="U31">
+        <v>3.6</v>
+      </c>
+      <c r="V31">
+        <v>1.22</v>
+      </c>
+      <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
+        <v>1.05</v>
+      </c>
+      <c r="Y31">
+        <v>1.5</v>
+      </c>
+      <c r="Z31">
+        <v>2.46</v>
+      </c>
+      <c r="AA31">
+        <v>2.5</v>
+      </c>
+      <c r="AB31">
+        <v>1.51</v>
+      </c>
+      <c r="AC31">
+        <v>4.75</v>
+      </c>
+      <c r="AD31">
+        <v>1.12</v>
+      </c>
+      <c r="AE31">
+        <v>1.02</v>
+      </c>
+      <c r="AF31">
+        <v>2.1</v>
+      </c>
+      <c r="AG31">
+        <v>1.64</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.31</v>
+      </c>
+      <c r="AK31">
         <v>1.67</v>
-      </c>
-      <c r="S31">
-        <v>1.71</v>
-      </c>
-      <c r="T31">
-        <v>2.01</v>
-      </c>
-      <c r="U31">
-        <v>3.92</v>
-      </c>
-      <c r="V31">
-        <v>1.18</v>
-      </c>
-      <c r="W31">
-        <v>1.02</v>
-      </c>
-      <c r="X31">
-        <v>1.11</v>
-      </c>
-      <c r="Y31">
-        <v>1.61</v>
-      </c>
-      <c r="Z31">
-        <v>2.28</v>
-      </c>
-      <c r="AA31">
-        <v>3</v>
-      </c>
-      <c r="AB31">
-        <v>1.36</v>
-      </c>
-      <c r="AC31">
-        <v>5.92</v>
-      </c>
-      <c r="AD31">
-        <v>1.09</v>
-      </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
-      <c r="AF31">
-        <v>2.19</v>
-      </c>
-      <c r="AG31">
-        <v>1.59</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.41</v>
-      </c>
-      <c r="AK31">
-        <v>1.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="O32">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="P32">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q32">
-        <v>2.77</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="S32">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="T32">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="U32">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="V32">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W32">
+        <v>1.02</v>
+      </c>
+      <c r="X32">
+        <v>1.11</v>
+      </c>
+      <c r="Y32">
+        <v>1.61</v>
+      </c>
+      <c r="Z32">
+        <v>2.28</v>
+      </c>
+      <c r="AA32">
+        <v>3</v>
+      </c>
+      <c r="AB32">
+        <v>1.36</v>
+      </c>
+      <c r="AC32">
+        <v>5.92</v>
+      </c>
+      <c r="AD32">
+        <v>1.09</v>
+      </c>
+      <c r="AE32">
         <v>1.03</v>
       </c>
-      <c r="X32">
-        <v>1.05</v>
-      </c>
-      <c r="Y32">
-        <v>1.5</v>
-      </c>
-      <c r="Z32">
-        <v>2.46</v>
-      </c>
-      <c r="AA32">
-        <v>2.5</v>
-      </c>
-      <c r="AB32">
-        <v>1.51</v>
-      </c>
-      <c r="AC32">
-        <v>4.75</v>
-      </c>
-      <c r="AD32">
-        <v>1.12</v>
-      </c>
-      <c r="AE32">
-        <v>1.02</v>
-      </c>
       <c r="AF32">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AG32">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -7318,43 +7318,43 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O43">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
-        <v>7.08</v>
+        <v>5.2</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA43">
         <v>1.95</v>
@@ -7363,19 +7363,19 @@
         <v>1.85</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,22 +7490,22 @@
         <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>4.8</v>
+        <v>4.52</v>
       </c>
       <c r="R44">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S44">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T44">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U44">
         <v>3.25</v>
       </c>
       <c r="V44">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W44">
         <v>1.02</v>
@@ -7514,31 +7514,31 @@
         <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z44">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA44">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB44">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC44">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="AD44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE44">
         <v>1.01</v>
       </c>
       <c r="AF44">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG44">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK44">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O45">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P45">
-        <v>4.2</v>
+        <v>4.82</v>
       </c>
       <c r="Q45">
         <v>2.06</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
         <v>2.28</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
         <v>1.67</v>
       </c>
       <c r="Q46">
-        <v>4.51</v>
+        <v>4.56</v>
       </c>
       <c r="R46">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
         <v>1.21</v>
@@ -7828,13 +7828,13 @@
         <v>3.75</v>
       </c>
       <c r="U46">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V46">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,28 +7843,28 @@
         <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA46">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC46">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AD46">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF46">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG46">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="Q47">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="R47">
         <v>2.22</v>
       </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T47">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U47">
         <v>2.18</v>
@@ -8012,7 +8012,7 @@
         <v>1.46</v>
       </c>
       <c r="AB47">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AC47">
         <v>2.19</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="P48">
         <v>3.74</v>
@@ -8172,10 +8172,10 @@
         <v>5.3</v>
       </c>
       <c r="AA48">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB48">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AC48">
         <v>2.1</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q50">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U50">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="Z50">
-        <v>4.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA50">
+        <v>2.1</v>
+      </c>
+      <c r="AB50">
         <v>1.72</v>
       </c>
-      <c r="AB50">
-        <v>2.1</v>
-      </c>
       <c r="AC50">
-        <v>2.55</v>
+        <v>3.38</v>
       </c>
       <c r="AD50">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AG50">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK50">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O51">
+        <v>3.75</v>
+      </c>
+      <c r="P51">
         <v>3.6</v>
       </c>
-      <c r="P51">
-        <v>4.4</v>
-      </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>2.99</v>
+        <v>4.05</v>
       </c>
       <c r="AA51">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AB51">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>3.38</v>
+        <v>2.61</v>
       </c>
       <c r="AD51">
+        <v>1.39</v>
+      </c>
+      <c r="AE51">
+        <v>1.12</v>
+      </c>
+      <c r="AF51">
+        <v>1.59</v>
+      </c>
+      <c r="AG51">
+        <v>2.21</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.24</v>
       </c>
-      <c r="AE51">
-        <v>1.05</v>
-      </c>
-      <c r="AF51">
-        <v>1.88</v>
-      </c>
-      <c r="AG51">
-        <v>1.8</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
-      </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
         <v>3.29</v>
@@ -8809,7 +8809,7 @@
         <v>2.77</v>
       </c>
       <c r="V52">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W52">
         <v>1.04</v>
@@ -8824,10 +8824,10 @@
         <v>3.3</v>
       </c>
       <c r="AA52">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
         <v>3.12</v>
@@ -8858,7 +8858,7 @@
         <v>1.31</v>
       </c>
       <c r="AK52">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="R54">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U54">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="V54">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="AA54">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG54">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK54">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q55">
-        <v>2.48</v>
+        <v>3.14</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U55">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="V55">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W55">
+        <v>1.05</v>
+      </c>
+      <c r="X55">
+        <v>1.03</v>
+      </c>
+      <c r="Y55">
+        <v>1.21</v>
+      </c>
+      <c r="Z55">
+        <v>3.62</v>
+      </c>
+      <c r="AA55">
+        <v>1.9</v>
+      </c>
+      <c r="AB55">
+        <v>1.9</v>
+      </c>
+      <c r="AC55">
+        <v>2.94</v>
+      </c>
+      <c r="AD55">
+        <v>1.31</v>
+      </c>
+      <c r="AE55">
         <v>1.08</v>
       </c>
-      <c r="X55">
-        <v>1</v>
-      </c>
-      <c r="Y55">
-        <v>1.18</v>
-      </c>
-      <c r="Z55">
-        <v>3.94</v>
-      </c>
-      <c r="AA55">
-        <v>1.72</v>
-      </c>
-      <c r="AB55">
-        <v>2.1</v>
-      </c>
-      <c r="AC55">
-        <v>2.54</v>
-      </c>
-      <c r="AD55">
-        <v>1.41</v>
-      </c>
-      <c r="AE55">
-        <v>1.13</v>
-      </c>
       <c r="AF55">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG55">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>3.32</v>
       </c>
       <c r="AA57">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB57">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC57">
         <v>3.38</v>
@@ -9654,10 +9654,10 @@
         <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AK57">
         <v>1.54</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="O58">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q58">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="R58">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="S58">
+        <v>1.43</v>
+      </c>
+      <c r="T58">
+        <v>2.62</v>
+      </c>
+      <c r="U58">
+        <v>2.99</v>
+      </c>
+      <c r="V58">
+        <v>1.34</v>
+      </c>
+      <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
+        <v>1.02</v>
+      </c>
+      <c r="Y58">
         <v>1.3</v>
       </c>
-      <c r="T58">
-        <v>3.22</v>
-      </c>
-      <c r="U58">
-        <v>2.47</v>
-      </c>
-      <c r="V58">
-        <v>1.48</v>
-      </c>
-      <c r="W58">
-        <v>1.07</v>
-      </c>
-      <c r="X58">
-        <v>1.01</v>
-      </c>
-      <c r="Y58">
-        <v>1.16</v>
-      </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA58">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD58">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q59">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="R59">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S59">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="U59">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="V59">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W59">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="AA59">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>3.52</v>
+        <v>2.64</v>
       </c>
       <c r="AD59">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AG59">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P60">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="Q60">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R60">
         <v>2.15</v>
@@ -10122,7 +10122,7 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
         <v>3.96</v>
@@ -10131,7 +10131,7 @@
         <v>1.72</v>
       </c>
       <c r="AB60">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC60">
         <v>2.68</v>
@@ -10162,7 +10162,7 @@
         <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,43 +10252,43 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="O61">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P61">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R61">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S61">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T61">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U61">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V61">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
         <v>1.3</v>
       </c>
       <c r="Z61">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="AA61">
         <v>2.05</v>
@@ -10297,19 +10297,19 @@
         <v>1.75</v>
       </c>
       <c r="AC61">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="AD61">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG61">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>2.5</v>
       </c>
       <c r="Q62">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="R62">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S62">
         <v>1.32</v>
@@ -10448,19 +10448,19 @@
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA62">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
         <v>1.36</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK62">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10750,22 +10750,22 @@
         <v>3.4</v>
       </c>
       <c r="Q64">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="R64">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S64">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T64">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U64">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="V64">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
         <v>1.07</v>
@@ -10774,31 +10774,31 @@
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z64">
         <v>3.62</v>
       </c>
       <c r="AA64">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB64">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC64">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AD64">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE64">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF64">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG64">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
         <v>3.25</v>
@@ -10913,55 +10913,55 @@
         <v>4</v>
       </c>
       <c r="Q65">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R65">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U65">
-        <v>3.18</v>
+        <v>2.42</v>
       </c>
       <c r="V65">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z65">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AA65">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB65">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC65">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AD65">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF65">
         <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="O66">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="P66">
-        <v>5.45</v>
+        <v>6.3</v>
       </c>
       <c r="Q66">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S66">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U66">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V66">
         <v>1.44</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.93</v>
+        <v>3.7</v>
       </c>
       <c r="AA66">
         <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC66">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AD66">
         <v>1.36</v>
       </c>
       <c r="AE66">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF66">
         <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK66">
         <v>2.25</v>
@@ -11233,61 +11233,61 @@
         <v>1.22</v>
       </c>
       <c r="O67">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="P67">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q67">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="R67">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T67">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
         <v>2.34</v>
       </c>
       <c r="V67">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W67">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AA67">
         <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC67">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AD67">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE67">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
         <v>2.1</v>
       </c>
       <c r="AG67">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK67">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,58 +11393,58 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="O68">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="P68">
-        <v>5.9</v>
+        <v>4.65</v>
       </c>
       <c r="Q68">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="R68">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T68">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U68">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="V68">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
+        <v>1.23</v>
+      </c>
+      <c r="Z68">
+        <v>4.05</v>
+      </c>
+      <c r="AA68">
+        <v>1.64</v>
+      </c>
+      <c r="AB68">
+        <v>2.12</v>
+      </c>
+      <c r="AC68">
+        <v>2.52</v>
+      </c>
+      <c r="AD68">
+        <v>1.41</v>
+      </c>
+      <c r="AE68">
         <v>1.16</v>
-      </c>
-      <c r="Z68">
-        <v>4.5</v>
-      </c>
-      <c r="AA68">
-        <v>1.56</v>
-      </c>
-      <c r="AB68">
-        <v>2.2</v>
-      </c>
-      <c r="AC68">
-        <v>2.55</v>
-      </c>
-      <c r="AD68">
-        <v>1.48</v>
-      </c>
-      <c r="AE68">
-        <v>1.14</v>
       </c>
       <c r="AF68">
         <v>1.7</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O69">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="P69">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q69">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R69">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="S69">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T69">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U69">
         <v>4</v>
       </c>
       <c r="V69">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W69">
         <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y69">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z69">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AA69">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB69">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC69">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="AD69">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG69">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK69">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O72">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q72">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="R72">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S72">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T72">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U72">
         <v>2.91</v>
@@ -12072,22 +12072,22 @@
         <v>1.33</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z72">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AA72">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB72">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC72">
         <v>3.46</v>
@@ -12096,7 +12096,7 @@
         <v>1.24</v>
       </c>
       <c r="AE72">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF72">
         <v>1.8</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,7 +12217,7 @@
         <v>2.7</v>
       </c>
       <c r="Q73">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="R73">
         <v>2.13</v>
@@ -12232,40 +12232,40 @@
         <v>2.59</v>
       </c>
       <c r="V73">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W73">
         <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z73">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB73">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC73">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AD73">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG73">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL73">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="P2">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>2.25</v>
+        <v>3.06</v>
       </c>
       <c r="R2">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AG2">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="O3">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q3">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AG3">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>3.89</v>
+        <v>3.02</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="R21">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S21">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="U21">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA21">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC21">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>3.02</v>
+        <v>3.89</v>
       </c>
       <c r="Q22">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S22">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="U22">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W22">
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC22">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.45</v>
+        <v>3.65</v>
       </c>
       <c r="O43">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>5.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q43">
-        <v>1.97</v>
+        <v>4.52</v>
       </c>
       <c r="R43">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="T43">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="U43">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W43">
+        <v>1.02</v>
+      </c>
+      <c r="X43">
         <v>1.06</v>
       </c>
-      <c r="X43">
+      <c r="Y43">
+        <v>1.38</v>
+      </c>
+      <c r="Z43">
+        <v>2.62</v>
+      </c>
+      <c r="AA43">
+        <v>2.35</v>
+      </c>
+      <c r="AB43">
+        <v>1.57</v>
+      </c>
+      <c r="AC43">
+        <v>3.13</v>
+      </c>
+      <c r="AD43">
+        <v>1.17</v>
+      </c>
+      <c r="AE43">
         <v>1.01</v>
       </c>
-      <c r="Y43">
-        <v>1.25</v>
-      </c>
-      <c r="Z43">
-        <v>3.28</v>
-      </c>
-      <c r="AA43">
+      <c r="AF43">
         <v>1.95</v>
       </c>
-      <c r="AB43">
-        <v>1.85</v>
-      </c>
-      <c r="AC43">
-        <v>3.2</v>
-      </c>
-      <c r="AD43">
-        <v>1.26</v>
-      </c>
-      <c r="AE43">
-        <v>1.06</v>
-      </c>
-      <c r="AF43">
-        <v>2.05</v>
-      </c>
       <c r="AG43">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
-        <v>2.57</v>
+        <v>1.22</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.65</v>
+        <v>1.45</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="P44">
+        <v>5.2</v>
+      </c>
+      <c r="Q44">
+        <v>1.97</v>
+      </c>
+      <c r="R44">
+        <v>2.21</v>
+      </c>
+      <c r="S44">
+        <v>1.35</v>
+      </c>
+      <c r="T44">
+        <v>2.82</v>
+      </c>
+      <c r="U44">
+        <v>2.78</v>
+      </c>
+      <c r="V44">
+        <v>1.36</v>
+      </c>
+      <c r="W44">
+        <v>1.06</v>
+      </c>
+      <c r="X44">
+        <v>1.01</v>
+      </c>
+      <c r="Y44">
+        <v>1.25</v>
+      </c>
+      <c r="Z44">
+        <v>3.28</v>
+      </c>
+      <c r="AA44">
         <v>1.95</v>
       </c>
-      <c r="Q44">
-        <v>4.52</v>
-      </c>
-      <c r="R44">
-        <v>1.92</v>
-      </c>
-      <c r="S44">
-        <v>1.48</v>
-      </c>
-      <c r="T44">
-        <v>2.38</v>
-      </c>
-      <c r="U44">
-        <v>3.25</v>
-      </c>
-      <c r="V44">
-        <v>1.28</v>
-      </c>
-      <c r="W44">
-        <v>1.02</v>
-      </c>
-      <c r="X44">
+      <c r="AB44">
+        <v>1.85</v>
+      </c>
+      <c r="AC44">
+        <v>3.2</v>
+      </c>
+      <c r="AD44">
+        <v>1.26</v>
+      </c>
+      <c r="AE44">
         <v>1.06</v>
       </c>
-      <c r="Y44">
-        <v>1.38</v>
-      </c>
-      <c r="Z44">
-        <v>2.62</v>
-      </c>
-      <c r="AA44">
-        <v>2.35</v>
-      </c>
-      <c r="AB44">
-        <v>1.57</v>
-      </c>
-      <c r="AC44">
-        <v>3.13</v>
-      </c>
-      <c r="AD44">
-        <v>1.17</v>
-      </c>
-      <c r="AE44">
-        <v>1.01</v>
-      </c>
       <c r="AF44">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG44">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>1.22</v>
+        <v>2.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.6</v>
+        <v>4.18</v>
       </c>
       <c r="O45">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="P45">
-        <v>4.82</v>
+        <v>1.67</v>
       </c>
       <c r="Q45">
-        <v>2.06</v>
+        <v>4.56</v>
       </c>
       <c r="R45">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S45">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T45">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="U45">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="W45">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>6.05</v>
+        <v>5.55</v>
       </c>
       <c r="AA45">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AB45">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC45">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AD45">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AE45">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AF45">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG45">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.18</v>
+        <v>1.6</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>1.67</v>
+        <v>4.82</v>
       </c>
       <c r="Q46">
-        <v>4.56</v>
+        <v>2.06</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S46">
+        <v>1.2</v>
+      </c>
+      <c r="T46">
+        <v>3.88</v>
+      </c>
+      <c r="U46">
+        <v>1.94</v>
+      </c>
+      <c r="V46">
+        <v>1.81</v>
+      </c>
+      <c r="W46">
         <v>1.21</v>
       </c>
-      <c r="T46">
-        <v>3.75</v>
-      </c>
-      <c r="U46">
-        <v>2.1</v>
-      </c>
-      <c r="V46">
-        <v>1.69</v>
-      </c>
-      <c r="W46">
-        <v>1.15</v>
-      </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z46">
-        <v>5.55</v>
+        <v>6.05</v>
       </c>
       <c r="AA46">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AB46">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC46">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AD46">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE46">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AF46">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
+        <v>3.75</v>
+      </c>
+      <c r="P50">
         <v>3.6</v>
       </c>
-      <c r="P50">
-        <v>4.4</v>
-      </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R50">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T50">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>2.99</v>
+        <v>4.05</v>
       </c>
       <c r="AA50">
+        <v>1.72</v>
+      </c>
+      <c r="AB50">
         <v>2.1</v>
       </c>
-      <c r="AB50">
-        <v>1.72</v>
-      </c>
       <c r="AC50">
-        <v>3.38</v>
+        <v>2.61</v>
       </c>
       <c r="AD50">
+        <v>1.39</v>
+      </c>
+      <c r="AE50">
+        <v>1.12</v>
+      </c>
+      <c r="AF50">
+        <v>1.59</v>
+      </c>
+      <c r="AG50">
+        <v>2.21</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.24</v>
       </c>
-      <c r="AE50">
-        <v>1.05</v>
-      </c>
-      <c r="AF50">
-        <v>1.88</v>
-      </c>
-      <c r="AG50">
-        <v>1.8</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.27</v>
-      </c>
       <c r="AK50">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O51">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q51">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.94</v>
       </c>
       <c r="V51">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="Z51">
-        <v>4.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA51">
+        <v>2.1</v>
+      </c>
+      <c r="AB51">
         <v>1.72</v>
       </c>
-      <c r="AB51">
-        <v>2.1</v>
-      </c>
       <c r="AC51">
-        <v>2.61</v>
+        <v>3.38</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AG51">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q58">
+        <v>2.73</v>
+      </c>
+      <c r="R58">
+        <v>2.23</v>
+      </c>
+      <c r="S58">
+        <v>1.3</v>
+      </c>
+      <c r="T58">
+        <v>3.22</v>
+      </c>
+      <c r="U58">
+        <v>2.47</v>
+      </c>
+      <c r="V58">
+        <v>1.48</v>
+      </c>
+      <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.16</v>
+      </c>
+      <c r="Z58">
+        <v>4.1</v>
+      </c>
+      <c r="AA58">
+        <v>1.7</v>
+      </c>
+      <c r="AB58">
+        <v>2.1</v>
+      </c>
+      <c r="AC58">
         <v>2.64</v>
       </c>
-      <c r="R58">
-        <v>2.01</v>
-      </c>
-      <c r="S58">
-        <v>1.43</v>
-      </c>
-      <c r="T58">
-        <v>2.62</v>
-      </c>
-      <c r="U58">
-        <v>2.99</v>
-      </c>
-      <c r="V58">
-        <v>1.34</v>
-      </c>
-      <c r="W58">
-        <v>1.03</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.3</v>
-      </c>
-      <c r="Z58">
-        <v>2.99</v>
-      </c>
-      <c r="AA58">
-        <v>2.05</v>
-      </c>
-      <c r="AB58">
-        <v>1.75</v>
-      </c>
-      <c r="AC58">
-        <v>3.44</v>
-      </c>
       <c r="AD58">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG58">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK58">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P59">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q59">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="R59">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="S59">
+        <v>1.43</v>
+      </c>
+      <c r="T59">
+        <v>2.62</v>
+      </c>
+      <c r="U59">
+        <v>2.99</v>
+      </c>
+      <c r="V59">
+        <v>1.34</v>
+      </c>
+      <c r="W59">
+        <v>1.03</v>
+      </c>
+      <c r="X59">
+        <v>1.02</v>
+      </c>
+      <c r="Y59">
         <v>1.3</v>
       </c>
-      <c r="T59">
-        <v>3.22</v>
-      </c>
-      <c r="U59">
-        <v>2.47</v>
-      </c>
-      <c r="V59">
-        <v>1.48</v>
-      </c>
-      <c r="W59">
-        <v>1.07</v>
-      </c>
-      <c r="X59">
-        <v>1.01</v>
-      </c>
-      <c r="Y59">
-        <v>1.16</v>
-      </c>
       <c r="Z59">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD59">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG59">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK59">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="O61">
         <v>3.9</v>
       </c>
       <c r="P61">
-        <v>6.4</v>
+        <v>5.77</v>
       </c>
       <c r="Q61">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R61">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S61">
         <v>1.4</v>
@@ -10288,13 +10288,13 @@
         <v>1.3</v>
       </c>
       <c r="Z61">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="AA61">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC61">
         <v>3.38</v>
@@ -10303,7 +10303,7 @@
         <v>1.25</v>
       </c>
       <c r="AE61">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
         <v>2.1</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O65">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P65">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="Q65">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R65">
         <v>1.98</v>
@@ -10925,10 +10925,10 @@
         <v>2.5</v>
       </c>
       <c r="U65">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="V65">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W65">
         <v>1.03</v>
@@ -10943,13 +10943,13 @@
         <v>2.86</v>
       </c>
       <c r="AA65">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AB65">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AD65">
         <v>1.19</v>
@@ -10958,10 +10958,10 @@
         <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG65">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O66">
-        <v>4.4</v>
+        <v>3.93</v>
       </c>
       <c r="P66">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q66">
         <v>2.11</v>
@@ -11112,7 +11112,7 @@
         <v>1.96</v>
       </c>
       <c r="AC66">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AD66">
         <v>1.36</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="O67">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P67">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Q67">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R67">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="S67">
         <v>1.24</v>
@@ -11251,13 +11251,13 @@
         <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V67">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1.01</v>
@@ -11269,10 +11269,10 @@
         <v>4.7</v>
       </c>
       <c r="AA67">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB67">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AC67">
         <v>2.34</v>
@@ -11556,16 +11556,16 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O69">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="P69">
-        <v>3.27</v>
+        <v>3.62</v>
       </c>
       <c r="Q69">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R69">
         <v>1.78</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK69">
         <v>1.61</v>
@@ -12045,10 +12045,10 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P72">
         <v>2.1</v>
@@ -12214,7 +12214,7 @@
         <v>3.3</v>
       </c>
       <c r="P73">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q73">
         <v>2.86</v>
@@ -12250,7 +12250,7 @@
         <v>1.77</v>
       </c>
       <c r="AB73">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC73">
         <v>2.9</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q15">
         <v>3.84</v>
       </c>
       <c r="R15">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="S15">
         <v>1.75</v>
@@ -2784,28 +2784,28 @@
         <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z15">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AA15">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AB15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC15">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AD15">
         <v>1.06</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
         <v>2.32</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>2.7</v>
       </c>
       <c r="O18">
+        <v>2.6</v>
+      </c>
+      <c r="P18">
         <v>2.7</v>
-      </c>
-      <c r="P18">
-        <v>2.62</v>
       </c>
       <c r="Q18">
         <v>4.14</v>
@@ -3300,7 +3300,7 @@
         <v>2.5</v>
       </c>
       <c r="AG18">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>2.6</v>
       </c>
       <c r="O19">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P19">
         <v>2.65</v>
@@ -3445,7 +3445,7 @@
         <v>2.29</v>
       </c>
       <c r="AA19">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB19">
         <v>1.39</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O29">
         <v>2.9</v>
@@ -5048,7 +5048,7 @@
         <v>3.88</v>
       </c>
       <c r="R29">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
         <v>1.53</v>
@@ -5057,10 +5057,10 @@
         <v>2.33</v>
       </c>
       <c r="U29">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="V29">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
         <v>1.01</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AK29">
         <v>1.32</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
+        <v>3.25</v>
+      </c>
+      <c r="O31">
+        <v>2.6</v>
+      </c>
+      <c r="P31">
+        <v>2.45</v>
+      </c>
+      <c r="Q31">
+        <v>4.4</v>
+      </c>
+      <c r="R31">
+        <v>1.66</v>
+      </c>
+      <c r="S31">
+        <v>1.57</v>
+      </c>
+      <c r="T31">
+        <v>1.99</v>
+      </c>
+      <c r="U31">
+        <v>4</v>
+      </c>
+      <c r="V31">
+        <v>1.2</v>
+      </c>
+      <c r="W31">
+        <v>1.01</v>
+      </c>
+      <c r="X31">
+        <v>1.13</v>
+      </c>
+      <c r="Y31">
+        <v>1.57</v>
+      </c>
+      <c r="Z31">
         <v>2</v>
       </c>
-      <c r="O31">
-        <v>2.9</v>
-      </c>
-      <c r="P31">
-        <v>3.6</v>
-      </c>
-      <c r="Q31">
-        <v>2.77</v>
-      </c>
-      <c r="R31">
-        <v>2</v>
-      </c>
-      <c r="S31">
-        <v>1.56</v>
-      </c>
-      <c r="T31">
-        <v>2.26</v>
-      </c>
-      <c r="U31">
-        <v>3.6</v>
-      </c>
-      <c r="V31">
-        <v>1.22</v>
-      </c>
-      <c r="W31">
+      <c r="AA31">
+        <v>2.88</v>
+      </c>
+      <c r="AB31">
+        <v>1.4</v>
+      </c>
+      <c r="AC31">
+        <v>6</v>
+      </c>
+      <c r="AD31">
+        <v>1.13</v>
+      </c>
+      <c r="AE31">
         <v>1.03</v>
       </c>
-      <c r="X31">
-        <v>1.05</v>
-      </c>
-      <c r="Y31">
-        <v>1.5</v>
-      </c>
-      <c r="Z31">
-        <v>2.46</v>
-      </c>
-      <c r="AA31">
-        <v>2.5</v>
-      </c>
-      <c r="AB31">
-        <v>1.51</v>
-      </c>
-      <c r="AC31">
-        <v>4.75</v>
-      </c>
-      <c r="AD31">
-        <v>1.12</v>
-      </c>
-      <c r="AE31">
-        <v>1.02</v>
-      </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG31">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.99</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P32">
+        <v>3.6</v>
+      </c>
+      <c r="Q32">
+        <v>2.7</v>
+      </c>
+      <c r="R32">
+        <v>2.02</v>
+      </c>
+      <c r="S32">
+        <v>1.56</v>
+      </c>
+      <c r="T32">
+        <v>2.5</v>
+      </c>
+      <c r="U32">
+        <v>3.3</v>
+      </c>
+      <c r="V32">
+        <v>1.22</v>
+      </c>
+      <c r="W32">
+        <v>1.05</v>
+      </c>
+      <c r="X32">
+        <v>1.07</v>
+      </c>
+      <c r="Y32">
+        <v>1.5</v>
+      </c>
+      <c r="Z32">
+        <v>2.63</v>
+      </c>
+      <c r="AA32">
         <v>2.55</v>
       </c>
-      <c r="Q32">
-        <v>3.75</v>
-      </c>
-      <c r="R32">
-        <v>1.67</v>
-      </c>
-      <c r="S32">
-        <v>1.71</v>
-      </c>
-      <c r="T32">
-        <v>2.01</v>
-      </c>
-      <c r="U32">
-        <v>3.92</v>
-      </c>
-      <c r="V32">
-        <v>1.18</v>
-      </c>
-      <c r="W32">
+      <c r="AB32">
+        <v>1.5</v>
+      </c>
+      <c r="AC32">
+        <v>4.75</v>
+      </c>
+      <c r="AD32">
+        <v>1.17</v>
+      </c>
+      <c r="AE32">
         <v>1.02</v>
       </c>
-      <c r="X32">
-        <v>1.11</v>
-      </c>
-      <c r="Y32">
-        <v>1.61</v>
-      </c>
-      <c r="Z32">
-        <v>2.28</v>
-      </c>
-      <c r="AA32">
-        <v>3</v>
-      </c>
-      <c r="AB32">
-        <v>1.36</v>
-      </c>
-      <c r="AC32">
-        <v>5.92</v>
-      </c>
-      <c r="AD32">
-        <v>1.09</v>
-      </c>
-      <c r="AE32">
-        <v>1.03</v>
-      </c>
       <c r="AF32">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AG32">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q38">
-        <v>6.84</v>
+        <v>6.25</v>
       </c>
       <c r="R38">
         <v>2.09</v>
@@ -6548,7 +6548,7 @@
         <v>1.69</v>
       </c>
       <c r="AC38">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD38">
         <v>1.22</v>
@@ -6557,7 +6557,7 @@
         <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG38">
         <v>1.61</v>
@@ -6825,68 +6825,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="P40">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q40">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
         <v>4</v>
       </c>
       <c r="U40">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V40">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W40">
         <v>1.16</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.12</v>
       </c>
       <c r="Z40">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA40">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AB40">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC40">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD40">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="O58">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q58">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="R58">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="S58">
+        <v>1.43</v>
+      </c>
+      <c r="T58">
+        <v>2.62</v>
+      </c>
+      <c r="U58">
+        <v>2.99</v>
+      </c>
+      <c r="V58">
+        <v>1.34</v>
+      </c>
+      <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
+        <v>1.02</v>
+      </c>
+      <c r="Y58">
         <v>1.3</v>
       </c>
-      <c r="T58">
-        <v>3.22</v>
-      </c>
-      <c r="U58">
-        <v>2.47</v>
-      </c>
-      <c r="V58">
-        <v>1.48</v>
-      </c>
-      <c r="W58">
-        <v>1.07</v>
-      </c>
-      <c r="X58">
-        <v>1.01</v>
-      </c>
-      <c r="Y58">
-        <v>1.16</v>
-      </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA58">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="AD58">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="O59">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q59">
+        <v>2.73</v>
+      </c>
+      <c r="R59">
+        <v>2.23</v>
+      </c>
+      <c r="S59">
+        <v>1.3</v>
+      </c>
+      <c r="T59">
+        <v>3.22</v>
+      </c>
+      <c r="U59">
+        <v>2.47</v>
+      </c>
+      <c r="V59">
+        <v>1.48</v>
+      </c>
+      <c r="W59">
+        <v>1.07</v>
+      </c>
+      <c r="X59">
+        <v>1.01</v>
+      </c>
+      <c r="Y59">
+        <v>1.16</v>
+      </c>
+      <c r="Z59">
+        <v>4.1</v>
+      </c>
+      <c r="AA59">
+        <v>1.7</v>
+      </c>
+      <c r="AB59">
+        <v>2.1</v>
+      </c>
+      <c r="AC59">
         <v>2.64</v>
       </c>
-      <c r="R59">
-        <v>2.01</v>
-      </c>
-      <c r="S59">
-        <v>1.43</v>
-      </c>
-      <c r="T59">
-        <v>2.62</v>
-      </c>
-      <c r="U59">
-        <v>2.99</v>
-      </c>
-      <c r="V59">
-        <v>1.34</v>
-      </c>
-      <c r="W59">
-        <v>1.03</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.3</v>
-      </c>
-      <c r="Z59">
-        <v>2.99</v>
-      </c>
-      <c r="AA59">
-        <v>2.05</v>
-      </c>
-      <c r="AB59">
-        <v>1.75</v>
-      </c>
-      <c r="AC59">
-        <v>3.44</v>
-      </c>
       <c r="AD59">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG59">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AL59">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="O2">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD2">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AG2">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="P3">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>2.25</v>
+        <v>3.06</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
         <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V4">
         <v>1.42</v>
@@ -994,22 +994,22 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
         <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
@@ -1018,7 +1018,7 @@
         <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O5">
+        <v>3.05</v>
+      </c>
+      <c r="P5">
+        <v>2.95</v>
+      </c>
+      <c r="Q5">
         <v>3</v>
       </c>
-      <c r="P5">
-        <v>2.8</v>
-      </c>
-      <c r="Q5">
-        <v>3.12</v>
-      </c>
       <c r="R5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T5">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U5">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V5">
         <v>1.28</v>
@@ -1157,19 +1157,19 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z5">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC5">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD5">
         <v>1.16</v>
@@ -1178,7 +1178,7 @@
         <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG5">
         <v>1.77</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,58 +1287,58 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q6">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U6">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC6">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
         <v>1.67</v>
@@ -1360,7 +1360,7 @@
         <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>2.49</v>
+        <v>4.4</v>
       </c>
       <c r="R7">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
         <v>2.89</v>
       </c>
       <c r="U7">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC7">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AD7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U8">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AD8">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q9">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R9">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
         <v>1.41</v>
@@ -1809,19 +1809,19 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD9">
         <v>1.25</v>
@@ -1849,7 +1849,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T10">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U10">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1975,28 +1975,28 @@
         <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA10">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB10">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC10">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AD10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
         <v>1.16</v>
       </c>
       <c r="AF10">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,49 +2102,49 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q11">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="R11">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="T11">
         <v>2.29</v>
       </c>
       <c r="U11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V11">
         <v>1.24</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z11">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AA11">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AB11">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC11">
         <v>4.7</v>
@@ -2153,13 +2153,13 @@
         <v>1.12</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF11">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>3.2</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q12">
         <v>4.25</v>
@@ -2307,13 +2307,13 @@
         <v>2</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.38</v>
+        <v>3.69</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
@@ -2322,7 +2322,7 @@
         <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q13">
         <v>3.74</v>
       </c>
       <c r="R13">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U13">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
         <v>1.05</v>
@@ -2461,31 +2461,31 @@
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB13">
         <v>2</v>
       </c>
       <c r="AC13">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="AD13">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O14">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P16">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q16">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S16">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U16">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2950,31 +2950,31 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC16">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.3</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="P20">
-        <v>4.37</v>
+        <v>3.73</v>
       </c>
       <c r="Q20">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="R20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="T20">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="U20">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z20">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA20">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB20">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AD20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE20">
         <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AG20">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="Q21">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="R21">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U21">
         <v>2.88</v>
@@ -3762,7 +3762,7 @@
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
         <v>1.28</v>
@@ -3771,41 +3771,41 @@
         <v>3.08</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB21">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
         <v>3.42</v>
       </c>
       <c r="AD21">
+        <v>1.25</v>
+      </c>
+      <c r="AE21">
+        <v>1.06</v>
+      </c>
+      <c r="AF21">
+        <v>1.82</v>
+      </c>
+      <c r="AG21">
+        <v>1.85</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.23</v>
       </c>
-      <c r="AE21">
-        <v>1.05</v>
-      </c>
-      <c r="AF21">
-        <v>1.76</v>
-      </c>
-      <c r="AG21">
-        <v>1.91</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.25</v>
-      </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O22">
         <v>3.25</v>
       </c>
       <c r="P22">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
       </c>
       <c r="R22">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U22">
         <v>2.97</v>
@@ -3925,7 +3925,7 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
         <v>1.3</v>
@@ -3940,7 +3940,7 @@
         <v>1.68</v>
       </c>
       <c r="AC22">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
         <v>1.21</v>
@@ -3952,7 +3952,7 @@
         <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P23">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
+        <v>3.15</v>
+      </c>
+      <c r="P24">
+        <v>2.95</v>
+      </c>
+      <c r="Q24">
+        <v>2.85</v>
+      </c>
+      <c r="R24">
+        <v>1.99</v>
+      </c>
+      <c r="S24">
+        <v>1.4</v>
+      </c>
+      <c r="T24">
+        <v>2.6</v>
+      </c>
+      <c r="U24">
         <v>3.2</v>
       </c>
-      <c r="P24">
-        <v>2.47</v>
-      </c>
-      <c r="Q24">
-        <v>3.22</v>
-      </c>
-      <c r="R24">
-        <v>2.01</v>
-      </c>
-      <c r="S24">
-        <v>1.39</v>
-      </c>
-      <c r="T24">
-        <v>2.63</v>
-      </c>
-      <c r="U24">
-        <v>2.97</v>
-      </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
         <v>1.04</v>
@@ -4254,31 +4254,31 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
         <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC24">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AD24">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG24">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="Q25">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="R25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.38</v>
@@ -4405,10 +4405,10 @@
         <v>2.67</v>
       </c>
       <c r="U25">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
         <v>1.05</v>
@@ -4417,31 +4417,31 @@
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA25">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB25">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC25">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O26">
         <v>3.2</v>
@@ -4556,7 +4556,7 @@
         <v>4</v>
       </c>
       <c r="Q26">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R26">
         <v>1.95</v>
@@ -4574,7 +4574,7 @@
         <v>1.28</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
         <v>1.05</v>
@@ -4589,13 +4589,13 @@
         <v>2.25</v>
       </c>
       <c r="AB26">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC26">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE26">
         <v>1.02</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,13 +4716,13 @@
         <v>3.2</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="Q27">
         <v>2.87</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
         <v>1.36</v>
@@ -4731,7 +4731,7 @@
         <v>2.85</v>
       </c>
       <c r="U27">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
         <v>1.39</v>
@@ -4743,31 +4743,31 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC27">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O30">
+        <v>3.28</v>
+      </c>
+      <c r="P30">
         <v>3.4</v>
       </c>
-      <c r="P30">
-        <v>3.5</v>
-      </c>
       <c r="Q30">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R30">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="U30">
         <v>2.56</v>
@@ -5229,28 +5229,28 @@
         <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA30">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AC30">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="AD30">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
         <v>1.66</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q31">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="S31">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T31">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y31">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AA31">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AB31">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AD31">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG31">
         <v>1.65</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AK31">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,61 +5525,61 @@
         </is>
       </c>
       <c r="N32">
+        <v>3.25</v>
+      </c>
+      <c r="O32">
+        <v>2.6</v>
+      </c>
+      <c r="P32">
+        <v>2.45</v>
+      </c>
+      <c r="Q32">
+        <v>4.4</v>
+      </c>
+      <c r="R32">
+        <v>1.66</v>
+      </c>
+      <c r="S32">
+        <v>1.57</v>
+      </c>
+      <c r="T32">
+        <v>1.99</v>
+      </c>
+      <c r="U32">
+        <v>4</v>
+      </c>
+      <c r="V32">
+        <v>1.2</v>
+      </c>
+      <c r="W32">
+        <v>1.01</v>
+      </c>
+      <c r="X32">
+        <v>1.13</v>
+      </c>
+      <c r="Y32">
+        <v>1.57</v>
+      </c>
+      <c r="Z32">
         <v>2</v>
       </c>
-      <c r="O32">
-        <v>2.9</v>
-      </c>
-      <c r="P32">
-        <v>3.6</v>
-      </c>
-      <c r="Q32">
-        <v>2.7</v>
-      </c>
-      <c r="R32">
-        <v>2.02</v>
-      </c>
-      <c r="S32">
-        <v>1.56</v>
-      </c>
-      <c r="T32">
-        <v>2.5</v>
-      </c>
-      <c r="U32">
-        <v>3.3</v>
-      </c>
-      <c r="V32">
-        <v>1.22</v>
-      </c>
-      <c r="W32">
-        <v>1.05</v>
-      </c>
-      <c r="X32">
-        <v>1.07</v>
-      </c>
-      <c r="Y32">
-        <v>1.5</v>
-      </c>
-      <c r="Z32">
-        <v>2.63</v>
-      </c>
       <c r="AA32">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AB32">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC32">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AD32">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG32">
         <v>1.65</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK32">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="R33">
         <v>2.11</v>
@@ -5724,10 +5724,10 @@
         <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB33">
         <v>1.85</v>
@@ -5742,10 +5742,10 @@
         <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG33">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P34">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S34">
         <v>1.42</v>
@@ -5881,7 +5881,7 @@
         <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.32</v>
@@ -5893,10 +5893,10 @@
         <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC34">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD34">
         <v>1.22</v>
@@ -5905,10 +5905,10 @@
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,16 +6017,16 @@
         <v>1.4</v>
       </c>
       <c r="O35">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
-        <v>5.75</v>
+        <v>6.14</v>
       </c>
       <c r="Q35">
         <v>1.87</v>
       </c>
       <c r="R35">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
         <v>1.24</v>
@@ -6035,7 +6035,7 @@
         <v>3.44</v>
       </c>
       <c r="U35">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="V35">
         <v>1.58</v>
@@ -6047,31 +6047,31 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z35">
         <v>4.65</v>
       </c>
       <c r="AA35">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
         <v>2.38</v>
       </c>
       <c r="AC35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD35">
         <v>1.5</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG35">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="O36">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="P36">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q36">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="AA36">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC36">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AG36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.15</v>
+        <v>2.92</v>
       </c>
       <c r="AK36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>4.2</v>
+        <v>3.33</v>
       </c>
       <c r="Q39">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S39">
         <v>1.41</v>
@@ -6699,31 +6699,31 @@
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB39">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
         <v>3.58</v>
       </c>
       <c r="AD39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE39">
         <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG39">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="O40">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P40">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="Q40">
         <v>5.14</v>
       </c>
       <c r="R40">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U40">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
         <v>1.16</v>
@@ -6865,16 +6865,16 @@
         <v>1.12</v>
       </c>
       <c r="Z40">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA40">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AB40">
+        <v>2.37</v>
+      </c>
+      <c r="AC40">
         <v>2.33</v>
-      </c>
-      <c r="AC40">
-        <v>2.25</v>
       </c>
       <c r="AD40">
         <v>1.57</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.55</v>
+      </c>
+      <c r="O41">
+        <v>3.3</v>
+      </c>
+      <c r="P41">
         <v>2.5</v>
-      </c>
-      <c r="O41">
-        <v>3.2</v>
-      </c>
-      <c r="P41">
-        <v>2.45</v>
       </c>
       <c r="Q41">
         <v>3.08</v>
@@ -7007,46 +7007,46 @@
         <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="U41">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="AA41">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC41">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
         <v>2.09</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q42">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S42">
         <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U42">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.33</v>
+        <v>4.66</v>
       </c>
       <c r="AA42">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG42">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
         <v>1.33</v>
@@ -7318,28 +7318,28 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P43">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q43">
         <v>4.52</v>
       </c>
       <c r="R43">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T43">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U43">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="V43">
         <v>1.28</v>
@@ -7348,25 +7348,25 @@
         <v>1.02</v>
       </c>
       <c r="X43">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y43">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z43">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA43">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB43">
         <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>3.13</v>
+        <v>4.5</v>
       </c>
       <c r="AD43">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
         <v>1.22</v>
@@ -7481,43 +7481,43 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.45</v>
+        <v>5</v>
       </c>
       <c r="O44">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P44">
-        <v>5.2</v>
+        <v>1.46</v>
       </c>
       <c r="Q44">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="R44">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="U44">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
         <v>1.95</v>
@@ -7526,19 +7526,19 @@
         <v>1.85</v>
       </c>
       <c r="AC44">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD44">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG44">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK44">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>4.18</v>
+        <v>1.6</v>
       </c>
       <c r="O45">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="Q45">
-        <v>4.56</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T45">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V45">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="W45">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA45">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB45">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AC45">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AD45">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AE45">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AF45">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG45">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>1.18</v>
+        <v>2.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>4.82</v>
+        <v>1.67</v>
       </c>
       <c r="Q46">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="R46">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
         <v>1.2</v>
@@ -7828,43 +7828,43 @@
         <v>3.88</v>
       </c>
       <c r="U46">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V46">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AB46">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC46">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AD46">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AE46">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
+        <v>2.05</v>
+      </c>
+      <c r="AK46">
         <v>1.2</v>
-      </c>
-      <c r="AK46">
-        <v>2.28</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="P47">
-        <v>3.43</v>
+        <v>3.08</v>
       </c>
       <c r="Q47">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="S47">
         <v>1.27</v>
@@ -7991,10 +7991,10 @@
         <v>3.28</v>
       </c>
       <c r="U47">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V47">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W47">
         <v>1.14</v>
@@ -8009,10 +8009,10 @@
         <v>4.95</v>
       </c>
       <c r="AA47">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC47">
         <v>2.19</v>
@@ -8027,7 +8027,7 @@
         <v>1.43</v>
       </c>
       <c r="AG47">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,22 +8133,22 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O48">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P48">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="Q48">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="R48">
         <v>2.47</v>
       </c>
       <c r="S48">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
         <v>3.75</v>
@@ -8166,31 +8166,31 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
         <v>5.3</v>
       </c>
       <c r="AA48">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB48">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AC48">
         <v>2.1</v>
       </c>
       <c r="AD48">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE48">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="O49">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P49">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="Q50">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
         <v>2.3</v>
@@ -8492,7 +8492,7 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
         <v>4.05</v>
@@ -8504,7 +8504,7 @@
         <v>2.1</v>
       </c>
       <c r="AC50">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="AD50">
         <v>1.39</v>
@@ -8532,7 +8532,7 @@
         <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U51">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8655,31 +8655,31 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z51">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA51">
         <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
       <c r="AD51">
         <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
         <v>3.4</v>
       </c>
       <c r="P52">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q52">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U52">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V52">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W52">
         <v>1.04</v>
@@ -8818,31 +8818,31 @@
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA52">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB52">
         <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD52">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE52">
         <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG52">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
         <v>1.64</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P53">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q53">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="R53">
+        <v>2.2</v>
+      </c>
+      <c r="S53">
+        <v>1.34</v>
+      </c>
+      <c r="T53">
+        <v>2.99</v>
+      </c>
+      <c r="U53">
+        <v>2.5</v>
+      </c>
+      <c r="V53">
+        <v>1.47</v>
+      </c>
+      <c r="W53">
+        <v>1.08</v>
+      </c>
+      <c r="X53">
+        <v>1.02</v>
+      </c>
+      <c r="Y53">
+        <v>1.25</v>
+      </c>
+      <c r="Z53">
+        <v>4.4</v>
+      </c>
+      <c r="AA53">
+        <v>1.72</v>
+      </c>
+      <c r="AB53">
         <v>2.1</v>
       </c>
-      <c r="S53">
-        <v>1.36</v>
-      </c>
-      <c r="T53">
-        <v>2.88</v>
-      </c>
-      <c r="U53">
-        <v>2.59</v>
-      </c>
-      <c r="V53">
-        <v>1.44</v>
-      </c>
-      <c r="W53">
-        <v>1.07</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.22</v>
-      </c>
-      <c r="Z53">
-        <v>3.54</v>
-      </c>
-      <c r="AA53">
-        <v>1.8</v>
-      </c>
-      <c r="AB53">
-        <v>2</v>
-      </c>
       <c r="AC53">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG53">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9114,13 +9114,13 @@
         <v>1.95</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="P54">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q54">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="R54">
         <v>2.2</v>
@@ -9129,19 +9129,19 @@
         <v>1.33</v>
       </c>
       <c r="T54">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V54">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.18</v>
@@ -9156,7 +9156,7 @@
         <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="AD54">
         <v>1.41</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="O55">
         <v>3.5</v>
@@ -9283,7 +9283,7 @@
         <v>2.6</v>
       </c>
       <c r="Q55">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="R55">
         <v>2.13</v>
@@ -9295,7 +9295,7 @@
         <v>2.99</v>
       </c>
       <c r="U55">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
         <v>1.42</v>
@@ -9313,10 +9313,10 @@
         <v>3.62</v>
       </c>
       <c r="AA55">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB55">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC55">
         <v>2.94</v>
@@ -9331,7 +9331,7 @@
         <v>1.67</v>
       </c>
       <c r="AG55">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O56">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P56">
         <v>10</v>
       </c>
       <c r="Q56">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="R56">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="S56">
         <v>1.21</v>
@@ -9464,7 +9464,7 @@
         <v>1.71</v>
       </c>
       <c r="W56">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.01</v>
@@ -9473,7 +9473,7 @@
         <v>1.08</v>
       </c>
       <c r="Z56">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AA56">
         <v>1.4</v>
@@ -9482,7 +9482,7 @@
         <v>3</v>
       </c>
       <c r="AC56">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD56">
         <v>1.78</v>
@@ -9491,10 +9491,10 @@
         <v>1.28</v>
       </c>
       <c r="AF56">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG56">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.11</v>
       </c>
       <c r="AK56">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q57">
         <v>3.04</v>
       </c>
       <c r="R57">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
         <v>1.41</v>
       </c>
       <c r="T57">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="U57">
         <v>2.94</v>
@@ -9627,7 +9627,7 @@
         <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X57">
         <v>1</v>
@@ -9636,7 +9636,7 @@
         <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="AA57">
         <v>2</v>
@@ -9645,10 +9645,10 @@
         <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AD57">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
         <v>1.04</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK57">
         <v>1.54</v>
@@ -9763,43 +9763,43 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="Q58">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R58">
         <v>2.01</v>
       </c>
       <c r="S58">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U58">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W58">
         <v>1.03</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
         <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA58">
         <v>2.05</v>
@@ -9808,19 +9808,19 @@
         <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD58">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
         <v>1.77</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P59">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="Q59">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="R59">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S59">
         <v>1.3</v>
@@ -9947,10 +9947,10 @@
         <v>3.22</v>
       </c>
       <c r="U59">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V59">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
         <v>1.07</v>
@@ -9962,7 +9962,7 @@
         <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA59">
         <v>1.7</v>
@@ -9971,19 +9971,19 @@
         <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="AD59">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
         <v>1.55</v>
       </c>
       <c r="AG59">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK59">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="O60">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P60">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="Q60">
         <v>2.77</v>
@@ -10122,7 +10122,7 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z60">
         <v>3.96</v>
@@ -10134,7 +10134,7 @@
         <v>2.07</v>
       </c>
       <c r="AC60">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AD60">
         <v>1.37</v>
@@ -10146,7 +10146,7 @@
         <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10421,10 +10421,10 @@
         <v>3.5</v>
       </c>
       <c r="P62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q62">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
         <v>2.18</v>
@@ -10445,34 +10445,34 @@
         <v>1.07</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y62">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AA62">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB62">
         <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD62">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE62">
         <v>1.11</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="O63">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="P63">
         <v>1.61</v>
       </c>
       <c r="Q63">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="R63">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S63">
         <v>1.28</v>
@@ -10599,7 +10599,7 @@
         <v>3.34</v>
       </c>
       <c r="U63">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="V63">
         <v>1.53</v>
@@ -10614,28 +10614,28 @@
         <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA63">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AB63">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC63">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD63">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AE63">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF63">
         <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O64">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q64">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="S64">
         <v>1.34</v>
@@ -10762,7 +10762,7 @@
         <v>2.99</v>
       </c>
       <c r="U64">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="V64">
         <v>1.44</v>
@@ -10774,31 +10774,31 @@
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z64">
         <v>3.62</v>
       </c>
       <c r="AA64">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB64">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC64">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="AD64">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG64">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>3.95</v>
+        <v>2.49</v>
       </c>
       <c r="Q2">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
         <v>1.32</v>
@@ -656,43 +656,43 @@
         <v>2.92</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB2">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3">
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="O3">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>3.06</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
         <v>1.33</v>
@@ -819,43 +819,43 @@
         <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC3">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
+        <v>1.84</v>
+      </c>
+      <c r="Q7">
+        <v>4.2</v>
+      </c>
+      <c r="R7">
+        <v>2.09</v>
+      </c>
+      <c r="S7">
+        <v>1.41</v>
+      </c>
+      <c r="T7">
+        <v>2.69</v>
+      </c>
+      <c r="U7">
+        <v>2.89</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.04</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.28</v>
+      </c>
+      <c r="Z7">
+        <v>3.08</v>
+      </c>
+      <c r="AA7">
+        <v>2.02</v>
+      </c>
+      <c r="AB7">
+        <v>1.81</v>
+      </c>
+      <c r="AC7">
+        <v>3.3</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.06</v>
+      </c>
+      <c r="AF7">
         <v>1.83</v>
       </c>
-      <c r="Q7">
-        <v>4.4</v>
-      </c>
-      <c r="R7">
-        <v>2.16</v>
-      </c>
-      <c r="S7">
-        <v>1.34</v>
-      </c>
-      <c r="T7">
-        <v>2.89</v>
-      </c>
-      <c r="U7">
-        <v>2.7</v>
-      </c>
-      <c r="V7">
-        <v>1.42</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
+      <c r="AG7">
+        <v>1.87</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.3</v>
+      </c>
+      <c r="AK7">
         <v>1.23</v>
-      </c>
-      <c r="Z7">
-        <v>3.44</v>
-      </c>
-      <c r="AA7">
-        <v>1.87</v>
-      </c>
-      <c r="AB7">
-        <v>1.97</v>
-      </c>
-      <c r="AC7">
-        <v>3.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.32</v>
-      </c>
-      <c r="AE7">
-        <v>1.09</v>
-      </c>
-      <c r="AF7">
-        <v>1.71</v>
-      </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.28</v>
-      </c>
-      <c r="AK7">
-        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>3.85</v>
+      </c>
+      <c r="O8">
+        <v>3.5</v>
+      </c>
+      <c r="P8">
+        <v>1.83</v>
+      </c>
+      <c r="Q8">
+        <v>4.4</v>
+      </c>
+      <c r="R8">
         <v>2.16</v>
       </c>
-      <c r="O8">
-        <v>3.3</v>
-      </c>
-      <c r="P8">
-        <v>3.1</v>
-      </c>
-      <c r="Q8">
+      <c r="S8">
+        <v>1.34</v>
+      </c>
+      <c r="T8">
+        <v>2.89</v>
+      </c>
+      <c r="U8">
         <v>2.7</v>
       </c>
-      <c r="R8">
-        <v>2.1</v>
-      </c>
-      <c r="S8">
-        <v>1.35</v>
-      </c>
-      <c r="T8">
-        <v>2.85</v>
-      </c>
-      <c r="U8">
-        <v>2.73</v>
-      </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AA8">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC8">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD8">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
         <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q17">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="R17">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S17">
         <v>1.75</v>
@@ -3107,7 +3107,7 @@
         <v>1.15</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>1.18</v>
@@ -3125,13 +3125,13 @@
         <v>1.22</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
         <v>2.9</v>
@@ -3153,7 +3153,7 @@
         <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.75</v>
+      </c>
+      <c r="O18">
         <v>2.7</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>2.6</v>
-      </c>
-      <c r="P18">
-        <v>2.7</v>
       </c>
       <c r="Q18">
         <v>4.14</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3409,10 +3409,10 @@
         <v>2.6</v>
       </c>
       <c r="O19">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P19">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:30:00</t>
+          <t>2026-09-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <v>3.8</v>
+      </c>
+      <c r="Q20">
         <v>2.7</v>
-      </c>
-      <c r="P20">
-        <v>3.73</v>
-      </c>
-      <c r="Q20">
-        <v>2.69</v>
       </c>
       <c r="R20">
         <v>2</v>
@@ -3626,7 +3626,7 @@
         <v>2.01</v>
       </c>
       <c r="AG20">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="Q21">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="R21">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA21">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC21">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD21">
         <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
+        <v>1.85</v>
+      </c>
+      <c r="AG21">
         <v>1.82</v>
       </c>
-      <c r="AG21">
-        <v>1.85</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T22">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U22">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -3928,31 +3928,31 @@
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB22">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC22">
         <v>3.8</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG22">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>1.82</v>
       </c>
       <c r="O23">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4227,58 +4227,58 @@
         <v>3.15</v>
       </c>
       <c r="P24">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q24">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U24">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
         <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC24">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AD24">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
         <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG24">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>1.78</v>
       </c>
       <c r="AC25">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD25">
         <v>1.26</v>
@@ -4719,16 +4719,16 @@
         <v>3.06</v>
       </c>
       <c r="Q27">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="R27">
         <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
         <v>2.75</v>
@@ -4746,19 +4746,19 @@
         <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AA27">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AB27">
         <v>1.83</v>
       </c>
       <c r="AC27">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="AD27">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P28">
         <v>4</v>
       </c>
       <c r="Q28">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>2.4</v>
@@ -4912,25 +4912,25 @@
         <v>5.9</v>
       </c>
       <c r="AA28">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB28">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC28">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD28">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF28">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG28">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O29">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q29">
         <v>3.88</v>
@@ -5051,19 +5051,19 @@
         <v>1.95</v>
       </c>
       <c r="S29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T29">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U29">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="V29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X29">
         <v>1.06</v>
@@ -5081,7 +5081,7 @@
         <v>1.43</v>
       </c>
       <c r="AC29">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AD29">
         <v>1.11</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O30">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="Q30">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
         <v>2.56</v>
@@ -5235,16 +5235,16 @@
         <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
         <v>2.09</v>
       </c>
       <c r="AC30">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AD30">
         <v>1.4</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P33">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="R33">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="U33">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="V33">
+        <v>1.32</v>
+      </c>
+      <c r="W33">
+        <v>1.03</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
+        <v>1.32</v>
+      </c>
+      <c r="Z33">
+        <v>2.88</v>
+      </c>
+      <c r="AA33">
+        <v>2.05</v>
+      </c>
+      <c r="AB33">
+        <v>1.69</v>
+      </c>
+      <c r="AC33">
+        <v>3.35</v>
+      </c>
+      <c r="AD33">
+        <v>1.22</v>
+      </c>
+      <c r="AE33">
+        <v>1.04</v>
+      </c>
+      <c r="AF33">
+        <v>1.8</v>
+      </c>
+      <c r="AG33">
+        <v>1.88</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.36</v>
       </c>
-      <c r="W33">
-        <v>1.04</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.26</v>
-      </c>
-      <c r="Z33">
-        <v>3.1</v>
-      </c>
-      <c r="AA33">
-        <v>1.93</v>
-      </c>
-      <c r="AB33">
-        <v>1.85</v>
-      </c>
-      <c r="AC33">
-        <v>3.2</v>
-      </c>
-      <c r="AD33">
-        <v>1.26</v>
-      </c>
-      <c r="AE33">
-        <v>1.06</v>
-      </c>
-      <c r="AF33">
-        <v>1.71</v>
-      </c>
-      <c r="AG33">
-        <v>2</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.24</v>
-      </c>
       <c r="AK33">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="R34">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="S34">
+        <v>1.35</v>
+      </c>
+      <c r="T34">
+        <v>2.82</v>
+      </c>
+      <c r="U34">
+        <v>2.78</v>
+      </c>
+      <c r="V34">
+        <v>1.36</v>
+      </c>
+      <c r="W34">
+        <v>1.04</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.26</v>
+      </c>
+      <c r="Z34">
+        <v>3.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.93</v>
+      </c>
+      <c r="AB34">
+        <v>1.85</v>
+      </c>
+      <c r="AC34">
+        <v>3.2</v>
+      </c>
+      <c r="AD34">
+        <v>1.26</v>
+      </c>
+      <c r="AE34">
+        <v>1.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.71</v>
+      </c>
+      <c r="AG34">
+        <v>2</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.24</v>
+      </c>
+      <c r="AK34">
         <v>1.42</v>
-      </c>
-      <c r="T34">
-        <v>2.56</v>
-      </c>
-      <c r="U34">
-        <v>2.96</v>
-      </c>
-      <c r="V34">
-        <v>1.32</v>
-      </c>
-      <c r="W34">
-        <v>1.03</v>
-      </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.32</v>
-      </c>
-      <c r="Z34">
-        <v>2.88</v>
-      </c>
-      <c r="AA34">
-        <v>2.05</v>
-      </c>
-      <c r="AB34">
-        <v>1.69</v>
-      </c>
-      <c r="AC34">
-        <v>3.35</v>
-      </c>
-      <c r="AD34">
-        <v>1.22</v>
-      </c>
-      <c r="AE34">
-        <v>1.04</v>
-      </c>
-      <c r="AF34">
-        <v>1.8</v>
-      </c>
-      <c r="AG34">
-        <v>1.88</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.36</v>
-      </c>
-      <c r="AK34">
-        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>4.4</v>
       </c>
       <c r="P35">
-        <v>6.14</v>
+        <v>5.75</v>
       </c>
       <c r="Q35">
         <v>1.87</v>
@@ -6047,16 +6047,16 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA35">
         <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC35">
         <v>2.3</v>
@@ -6065,7 +6065,7 @@
         <v>1.5</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
         <v>1.65</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="Q36">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T36">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="U36">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="V36">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W36">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
+        <v>1.32</v>
+      </c>
+      <c r="Z36">
+        <v>2.88</v>
+      </c>
+      <c r="AA36">
+        <v>2.04</v>
+      </c>
+      <c r="AB36">
+        <v>1.69</v>
+      </c>
+      <c r="AC36">
+        <v>3.7</v>
+      </c>
+      <c r="AD36">
         <v>1.22</v>
       </c>
-      <c r="Z36">
-        <v>3.65</v>
-      </c>
-      <c r="AA36">
-        <v>1.8</v>
-      </c>
-      <c r="AB36">
-        <v>1.87</v>
-      </c>
-      <c r="AC36">
-        <v>2.92</v>
-      </c>
-      <c r="AD36">
-        <v>1.35</v>
-      </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG36">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>2.92</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>1.04</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AA37">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-02 14:30:00</t>
+          <t>2026-09-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q39">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="R39">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S39">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
         <v>1.04</v>
@@ -6699,19 +6699,19 @@
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z39">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC39">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
         <v>1.22</v>
@@ -6720,10 +6720,10 @@
         <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.9</v>
+        <v>4.61</v>
       </c>
       <c r="O40">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q40">
-        <v>5.14</v>
+        <v>5.26</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6859,7 +6859,7 @@
         <v>1.16</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.12</v>
@@ -6871,13 +6871,13 @@
         <v>1.45</v>
       </c>
       <c r="AB40">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC40">
         <v>2.33</v>
       </c>
       <c r="AD40">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE40">
         <v>1.2</v>
@@ -6886,7 +6886,7 @@
         <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6995,10 +6995,10 @@
         <v>2.55</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q41">
         <v>3.08</v>
@@ -7007,28 +7007,28 @@
         <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AA41">
         <v>1.86</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q42">
         <v>3.22</v>
@@ -7170,19 +7170,19 @@
         <v>2.23</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
         <v>1.52</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
         <v>1.02</v>
@@ -7191,7 +7191,7 @@
         <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="AA42">
         <v>1.6</v>
@@ -7203,13 +7203,13 @@
         <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
         <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG42">
         <v>2.4</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P45">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R45">
         <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="U45">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA45">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AB45">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AC45">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AD45">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AE45">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
+        <v>2.05</v>
+      </c>
+      <c r="AK45">
         <v>1.2</v>
-      </c>
-      <c r="AK45">
-        <v>2.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="Q46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R46">
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T46">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="U46">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA46">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AC46">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AD46">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AF46">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AG46">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="O48">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="P48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
         <v>2.29</v>
@@ -8148,7 +8148,7 @@
         <v>2.47</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T48">
         <v>3.75</v>
@@ -8169,7 +8169,7 @@
         <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA48">
         <v>1.4</v>
@@ -8184,7 +8184,7 @@
         <v>1.74</v>
       </c>
       <c r="AE48">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="O49">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O61">
         <v>3.9</v>
@@ -10261,22 +10261,22 @@
         <v>5.77</v>
       </c>
       <c r="Q61">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R61">
         <v>2.15</v>
       </c>
       <c r="S61">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T61">
+        <v>2.66</v>
+      </c>
+      <c r="U61">
         <v>2.62</v>
       </c>
-      <c r="U61">
-        <v>2.88</v>
-      </c>
       <c r="V61">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W61">
         <v>1.06</v>
@@ -10285,31 +10285,31 @@
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z61">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AA61">
         <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC61">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="AD61">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG61">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="O65">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="P65">
-        <v>3.71</v>
+        <v>4.9</v>
       </c>
       <c r="Q65">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="R65">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S65">
         <v>1.44</v>
       </c>
       <c r="T65">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U65">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="V65">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z65">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB65">
         <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="AD65">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE65">
         <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AG65">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="O66">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>5.25</v>
+        <v>4.74</v>
       </c>
       <c r="Q66">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="R66">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="S66">
         <v>1.32</v>
@@ -11088,10 +11088,10 @@
         <v>3.05</v>
       </c>
       <c r="U66">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W66">
         <v>1.09</v>
@@ -11100,19 +11100,19 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA66">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB66">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC66">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AD66">
         <v>1.36</v>
@@ -11121,10 +11121,10 @@
         <v>1.11</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK66">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="O67">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="P67">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="Q67">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R67">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="S67">
         <v>1.24</v>
@@ -11251,40 +11251,40 @@
         <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V67">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA67">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AC67">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AD67">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE67">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG67">
         <v>1.66</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O68">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P68">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="Q68">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="R68">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S68">
         <v>1.29</v>
       </c>
       <c r="T68">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U68">
         <v>2.36</v>
       </c>
       <c r="V68">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
         <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z68">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="AA68">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AB68">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC68">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AD68">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="O72">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P72">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q72">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="R72">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S72">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T72">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U72">
         <v>2.91</v>
@@ -12072,25 +12072,25 @@
         <v>1.33</v>
       </c>
       <c r="W72">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z72">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="AA72">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB72">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC72">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD72">
         <v>1.24</v>
@@ -12102,7 +12102,7 @@
         <v>1.8</v>
       </c>
       <c r="AG72">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>2.8</v>
       </c>
       <c r="Q73">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R73">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S73">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U73">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V73">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W73">
         <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y73">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA73">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC73">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD73">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG73">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R2">
         <v>2.15</v>
@@ -656,16 +656,16 @@
         <v>2.92</v>
       </c>
       <c r="U2">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <v>1.2</v>
@@ -674,25 +674,25 @@
         <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB2">
         <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE2">
         <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG2">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -775,54 +775,54 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
         <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -834,44 +834,44 @@
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
         <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "50", "65"]</t>
         </is>
       </c>
       <c r="AJ3">
         <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -895,10 +895,10 @@
         <v>0</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,24 +950,24 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
         <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q4">
         <v>3.96</v>
@@ -979,7 +979,7 @@
         <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="U4">
         <v>2.62</v>
@@ -991,7 +991,7 @@
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.22</v>
@@ -1006,10 +1006,10 @@
         <v>2</v>
       </c>
       <c r="AC4">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79", "84"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90", "90+4"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1124,37 +1124,37 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P5">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q5">
         <v>3</v>
       </c>
       <c r="R5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="U5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V5">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.4</v>
@@ -1163,25 +1163,25 @@
         <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB5">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AD5">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1276,118 +1276,118 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S6">
         <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB6">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
+        <v>1.62</v>
+      </c>
+      <c r="AG6">
+        <v>2.16</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>["75", "81"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>["59"]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.28</v>
+      </c>
+      <c r="AK6">
+        <v>1.9</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>6</v>
+      </c>
+      <c r="AN6">
+        <v>2</v>
+      </c>
+      <c r="AO6">
+        <v>14</v>
+      </c>
+      <c r="AP6">
+        <v>9</v>
+      </c>
+      <c r="AQ6">
         <v>1.67</v>
       </c>
-      <c r="AG6">
-        <v>2.08</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.29</v>
-      </c>
-      <c r="AK6">
-        <v>1.86</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
-      <c r="AN6">
-        <v>-1</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>-1</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
         <v>4.2</v>
       </c>
       <c r="R7">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="S7">
+        <v>1.36</v>
+      </c>
+      <c r="T7">
+        <v>2.89</v>
+      </c>
+      <c r="U7">
+        <v>2.69</v>
+      </c>
+      <c r="V7">
         <v>1.41</v>
       </c>
-      <c r="T7">
-        <v>2.69</v>
-      </c>
-      <c r="U7">
-        <v>2.89</v>
-      </c>
-      <c r="V7">
-        <v>1.36</v>
-      </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="AA7">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
         <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="R8">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
         <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="U8">
         <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z8">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="AA8">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AB8">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AC8">
         <v>3.1</v>
       </c>
       <c r="AD8">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG8">
         <v>2</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
         <v>1.24</v>
@@ -1776,43 +1776,43 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
         <v>2.85</v>
       </c>
       <c r="U9">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V9">
         <v>1.38</v>
       </c>
       <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
         <v>1.04</v>
       </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA9">
         <v>1.85</v>
@@ -1824,16 +1824,16 @@
         <v>3.35</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
         <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,79 +1928,79 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>1.95</v>
       </c>
       <c r="R10">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="S10">
         <v>1.22</v>
       </c>
       <c r="T10">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA10">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB10">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="AC10">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AD10">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AE10">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "80", "90+1"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2009,37 +2009,37 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2082,36 +2082,36 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P11">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q11">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="R11">
         <v>1.88</v>
@@ -2126,34 +2126,34 @@
         <v>3.6</v>
       </c>
       <c r="V11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z11">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AA11">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AB11">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC11">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD11">
         <v>1.12</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
         <v>2.1</v>
@@ -2168,41 +2168,41 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "51"]</t>
         </is>
       </c>
       <c r="AJ11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2254,42 +2254,42 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>4.38</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="Q12">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="R12">
         <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U12">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
         <v>1.03</v>
@@ -2298,74 +2298,74 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
         <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,91 +2405,91 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q13">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="R13">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA13">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC13">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "68"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2498,37 +2498,37 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="R33">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
+        <v>1.35</v>
+      </c>
+      <c r="T33">
+        <v>2.82</v>
+      </c>
+      <c r="U33">
+        <v>2.78</v>
+      </c>
+      <c r="V33">
+        <v>1.36</v>
+      </c>
+      <c r="W33">
+        <v>1.04</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.26</v>
+      </c>
+      <c r="Z33">
+        <v>3.1</v>
+      </c>
+      <c r="AA33">
+        <v>1.93</v>
+      </c>
+      <c r="AB33">
+        <v>1.85</v>
+      </c>
+      <c r="AC33">
+        <v>3.2</v>
+      </c>
+      <c r="AD33">
+        <v>1.26</v>
+      </c>
+      <c r="AE33">
+        <v>1.06</v>
+      </c>
+      <c r="AF33">
+        <v>1.71</v>
+      </c>
+      <c r="AG33">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.24</v>
+      </c>
+      <c r="AK33">
         <v>1.42</v>
-      </c>
-      <c r="T33">
-        <v>2.56</v>
-      </c>
-      <c r="U33">
-        <v>2.96</v>
-      </c>
-      <c r="V33">
-        <v>1.32</v>
-      </c>
-      <c r="W33">
-        <v>1.03</v>
-      </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
-      <c r="Z33">
-        <v>2.88</v>
-      </c>
-      <c r="AA33">
-        <v>2.05</v>
-      </c>
-      <c r="AB33">
-        <v>1.69</v>
-      </c>
-      <c r="AC33">
-        <v>3.35</v>
-      </c>
-      <c r="AD33">
-        <v>1.22</v>
-      </c>
-      <c r="AE33">
-        <v>1.04</v>
-      </c>
-      <c r="AF33">
-        <v>1.8</v>
-      </c>
-      <c r="AG33">
-        <v>1.88</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.36</v>
-      </c>
-      <c r="AK33">
-        <v>1.55</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P34">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="R34">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="U34">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="V34">
+        <v>1.32</v>
+      </c>
+      <c r="W34">
+        <v>1.03</v>
+      </c>
+      <c r="X34">
+        <v>1.02</v>
+      </c>
+      <c r="Y34">
+        <v>1.32</v>
+      </c>
+      <c r="Z34">
+        <v>2.88</v>
+      </c>
+      <c r="AA34">
+        <v>2.05</v>
+      </c>
+      <c r="AB34">
+        <v>1.69</v>
+      </c>
+      <c r="AC34">
+        <v>3.35</v>
+      </c>
+      <c r="AD34">
+        <v>1.22</v>
+      </c>
+      <c r="AE34">
+        <v>1.04</v>
+      </c>
+      <c r="AF34">
+        <v>1.8</v>
+      </c>
+      <c r="AG34">
+        <v>1.88</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.36</v>
       </c>
-      <c r="W34">
-        <v>1.04</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.26</v>
-      </c>
-      <c r="Z34">
-        <v>3.1</v>
-      </c>
-      <c r="AA34">
-        <v>1.93</v>
-      </c>
-      <c r="AB34">
-        <v>1.85</v>
-      </c>
-      <c r="AC34">
-        <v>3.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.26</v>
-      </c>
-      <c r="AE34">
-        <v>1.06</v>
-      </c>
-      <c r="AF34">
-        <v>1.71</v>
-      </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.24</v>
-      </c>
       <c r="AK34">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="O45">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R45">
         <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T45">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V45">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="W45">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA45">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AB45">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AC45">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AD45">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AE45">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AG45">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R46">
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="U46">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V46">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AB46">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AC46">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AD46">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AE46">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
+        <v>2.05</v>
+      </c>
+      <c r="AK46">
         <v>1.2</v>
-      </c>
-      <c r="AK46">
-        <v>2.22</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>3.58</v>
+        <v>4.49</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S50">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="U50">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="V50">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z50">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>2.81</v>
+        <v>3.74</v>
       </c>
       <c r="AD50">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P51">
-        <v>4.49</v>
+        <v>3.58</v>
       </c>
       <c r="Q51">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA51">
+        <v>1.72</v>
+      </c>
+      <c r="AB51">
         <v>2.1</v>
       </c>
-      <c r="AB51">
-        <v>1.8</v>
-      </c>
       <c r="AC51">
-        <v>3.74</v>
+        <v>2.81</v>
       </c>
       <c r="AD51">
+        <v>1.39</v>
+      </c>
+      <c r="AE51">
+        <v>1.12</v>
+      </c>
+      <c r="AF51">
+        <v>1.59</v>
+      </c>
+      <c r="AG51">
+        <v>2.21</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.24</v>
       </c>
-      <c r="AE51">
-        <v>1.06</v>
-      </c>
-      <c r="AF51">
-        <v>1.85</v>
-      </c>
-      <c r="AG51">
+      <c r="AK51">
         <v>1.83</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.26</v>
-      </c>
-      <c r="AK51">
-        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11556,28 +11556,28 @@
         </is>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O69">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P69">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="Q69">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="R69">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S69">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="T69">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="U69">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V69">
         <v>1.16</v>
@@ -11586,22 +11586,22 @@
         <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Y69">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z69">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AA69">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="AB69">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC69">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AD69">
         <v>1.06</v>
@@ -11610,26 +11610,26 @@
         <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG69">
+        <v>1.51</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.34</v>
+      </c>
+      <c r="AK69">
         <v>1.5</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.33</v>
-      </c>
-      <c r="AK69">
-        <v>1.61</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "34"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "83", "85"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "21", "48", "55"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "83"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "90+4"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1765,14 +1765,14 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2568,130 +2568,130 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
         <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "82"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "10", "19", "62", "79", "90"]</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
         <v>2.5</v>
       </c>
       <c r="P15">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q15">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="R15">
         <v>1.84</v>
       </c>
       <c r="S15">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="T15">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="U15">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="V15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
+        <v>1.18</v>
+      </c>
+      <c r="Y15">
+        <v>1.7</v>
+      </c>
+      <c r="Z15">
+        <v>2.03</v>
+      </c>
+      <c r="AA15">
+        <v>3.46</v>
+      </c>
+      <c r="AB15">
+        <v>1.31</v>
+      </c>
+      <c r="AC15">
+        <v>7.5</v>
+      </c>
+      <c r="AD15">
         <v>1.11</v>
       </c>
-      <c r="Y15">
-        <v>1.67</v>
-      </c>
-      <c r="Z15">
-        <v>2.04</v>
-      </c>
-      <c r="AA15">
-        <v>2.97</v>
-      </c>
-      <c r="AB15">
-        <v>1.33</v>
-      </c>
-      <c r="AC15">
-        <v>7</v>
-      </c>
-      <c r="AD15">
-        <v>1.06</v>
-      </c>
       <c r="AE15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="O16">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="Q16">
-        <v>3.36</v>
+        <v>4.36</v>
       </c>
       <c r="R16">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2938,19 +2938,19 @@
         <v>2.78</v>
       </c>
       <c r="U16">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
         <v>3.58</v>
@@ -2959,7 +2959,7 @@
         <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC16">
         <v>3.1</v>
@@ -2971,10 +2971,10 @@
         <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="P17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R17">
         <v>1.69</v>
@@ -3113,13 +3113,13 @@
         <v>1.18</v>
       </c>
       <c r="Y17">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Z17">
         <v>1.8</v>
       </c>
       <c r="AA17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB17">
         <v>1.22</v>
@@ -3134,10 +3134,10 @@
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AG17">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
         <v>2.7</v>
@@ -3409,10 +3409,10 @@
         <v>2.6</v>
       </c>
       <c r="O19">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P19">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
         <v>1.38</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
         <v>3</v>
       </c>
       <c r="P20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q20">
         <v>2.7</v>
@@ -3611,7 +3611,7 @@
         <v>2.5</v>
       </c>
       <c r="AB20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC20">
         <v>4.1</v>
@@ -3620,7 +3620,7 @@
         <v>1.16</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
         <v>2.01</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="Q21">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
         <v>2.15</v>
@@ -3762,7 +3762,7 @@
         <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.27</v>
@@ -3780,7 +3780,7 @@
         <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P22">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
@@ -3934,10 +3934,10 @@
         <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
         <v>3.8</v>
@@ -3946,7 +3946,7 @@
         <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
         <v>1.82</v>
@@ -3968,7 +3968,7 @@
         <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,43 +4058,43 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA23">
         <v>1.95</v>
@@ -4103,19 +4103,19 @@
         <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P24">
+        <v>3.2</v>
+      </c>
+      <c r="Q24">
         <v>2.9</v>
-      </c>
-      <c r="Q24">
-        <v>2.78</v>
       </c>
       <c r="R24">
         <v>2.02</v>
@@ -4260,10 +4260,10 @@
         <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
         <v>3.5</v>
@@ -4396,13 +4396,13 @@
         <v>2.41</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T25">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U25">
         <v>2.75</v>
@@ -4411,7 +4411,7 @@
         <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.02</v>
@@ -4423,25 +4423,25 @@
         <v>3.14</v>
       </c>
       <c r="AA25">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF25">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG25">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>2.45</v>
       </c>
       <c r="Q29">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="R29">
         <v>1.95</v>
@@ -5057,10 +5057,10 @@
         <v>2.31</v>
       </c>
       <c r="U29">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V29">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
         <v>1</v>
@@ -5069,16 +5069,16 @@
         <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z29">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AA29">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AB29">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AC29">
         <v>4.95</v>
@@ -5087,13 +5087,13 @@
         <v>1.11</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AG29">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O31">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P31">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q31">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R31">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S31">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U31">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="V31">
         <v>1.22</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z31">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AA31">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB31">
         <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD31">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG31">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O32">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P32">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q32">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="R32">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="S32">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="T32">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="U32">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y32">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="Z32">
         <v>2</v>
       </c>
       <c r="AA32">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AB32">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="AD32">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG32">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AK32">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="P33">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q33">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="R33">
         <v>2.11</v>
@@ -5715,7 +5715,7 @@
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5724,10 +5724,10 @@
         <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
         <v>1.85</v>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="O34">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q34">
         <v>2.85</v>
       </c>
       <c r="R34">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S34">
         <v>1.42</v>
@@ -5893,7 +5893,7 @@
         <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
         <v>3.35</v>
@@ -5908,7 +5908,7 @@
         <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
         <v>1.55</v>
@@ -6180,46 +6180,46 @@
         <v>6</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q36">
         <v>6.25</v>
       </c>
       <c r="R36">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T36">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U36">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V36">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W36">
         <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA36">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AB36">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC36">
         <v>3.7</v>
@@ -6234,7 +6234,7 @@
         <v>2.1</v>
       </c>
       <c r="AG36">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="Q39">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="R39">
         <v>2.02</v>
@@ -6708,13 +6708,13 @@
         <v>2.01</v>
       </c>
       <c r="AB39">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
         <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
         <v>1.05</v>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O43">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="P43">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="Q43">
-        <v>4.52</v>
+        <v>1.88</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="S43">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.36</v>
+        <v>2.91</v>
       </c>
       <c r="U43">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="V43">
+        <v>1.38</v>
+      </c>
+      <c r="W43">
+        <v>1.07</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.22</v>
+      </c>
+      <c r="Z43">
+        <v>3.5</v>
+      </c>
+      <c r="AA43">
+        <v>1.95</v>
+      </c>
+      <c r="AB43">
+        <v>1.85</v>
+      </c>
+      <c r="AC43">
+        <v>3.05</v>
+      </c>
+      <c r="AD43">
         <v>1.28</v>
       </c>
-      <c r="W43">
-        <v>1.02</v>
-      </c>
-      <c r="X43">
-        <v>1.07</v>
-      </c>
-      <c r="Y43">
-        <v>1.44</v>
-      </c>
-      <c r="Z43">
-        <v>2.7</v>
-      </c>
-      <c r="AA43">
-        <v>2.3</v>
-      </c>
-      <c r="AB43">
-        <v>1.57</v>
-      </c>
-      <c r="AC43">
-        <v>4.5</v>
-      </c>
-      <c r="AD43">
-        <v>1.2</v>
-      </c>
       <c r="AE43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AG43">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK43">
-        <v>1.22</v>
+        <v>2.76</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="O44">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="P44">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="Q44">
-        <v>1.88</v>
+        <v>4.52</v>
       </c>
       <c r="R44">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="T44">
-        <v>2.91</v>
+        <v>2.36</v>
       </c>
       <c r="U44">
+        <v>3.18</v>
+      </c>
+      <c r="V44">
+        <v>1.28</v>
+      </c>
+      <c r="W44">
+        <v>1.02</v>
+      </c>
+      <c r="X44">
+        <v>1.07</v>
+      </c>
+      <c r="Y44">
+        <v>1.44</v>
+      </c>
+      <c r="Z44">
         <v>2.7</v>
       </c>
-      <c r="V44">
-        <v>1.38</v>
-      </c>
-      <c r="W44">
-        <v>1.07</v>
-      </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
-      <c r="Y44">
+      <c r="AA44">
+        <v>2.3</v>
+      </c>
+      <c r="AB44">
+        <v>1.57</v>
+      </c>
+      <c r="AC44">
+        <v>4.5</v>
+      </c>
+      <c r="AD44">
+        <v>1.2</v>
+      </c>
+      <c r="AE44">
+        <v>1.01</v>
+      </c>
+      <c r="AF44">
+        <v>1.95</v>
+      </c>
+      <c r="AG44">
+        <v>1.74</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.29</v>
+      </c>
+      <c r="AK44">
         <v>1.22</v>
-      </c>
-      <c r="Z44">
-        <v>3.5</v>
-      </c>
-      <c r="AA44">
-        <v>1.95</v>
-      </c>
-      <c r="AB44">
-        <v>1.85</v>
-      </c>
-      <c r="AC44">
-        <v>3.05</v>
-      </c>
-      <c r="AD44">
-        <v>1.28</v>
-      </c>
-      <c r="AE44">
-        <v>1.08</v>
-      </c>
-      <c r="AF44">
-        <v>2.07</v>
-      </c>
-      <c r="AG44">
-        <v>1.66</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.14</v>
-      </c>
-      <c r="AK44">
-        <v>2.76</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,65 +9111,65 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="O54">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q54">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="R54">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T54">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U54">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="V54">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z54">
-        <v>3.94</v>
+        <v>3.62</v>
       </c>
       <c r="AA54">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
+        <v>2</v>
+      </c>
+      <c r="AC54">
+        <v>2.94</v>
+      </c>
+      <c r="AD54">
+        <v>1.31</v>
+      </c>
+      <c r="AE54">
+        <v>1.08</v>
+      </c>
+      <c r="AF54">
+        <v>1.67</v>
+      </c>
+      <c r="AG54">
         <v>2.1</v>
       </c>
-      <c r="AC54">
-        <v>2.8</v>
-      </c>
-      <c r="AD54">
-        <v>1.41</v>
-      </c>
-      <c r="AE54">
-        <v>1.13</v>
-      </c>
-      <c r="AF54">
-        <v>1.58</v>
-      </c>
-      <c r="AG54">
-        <v>2.23</v>
-      </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="P55">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q55">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="R55">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="V55">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="AA55">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB55">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AD55">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG55">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="P58">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="R58">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="U58">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="V58">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA58">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB58">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="AD58">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O59">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="Q59">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="R59">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="S59">
+        <v>1.44</v>
+      </c>
+      <c r="T59">
+        <v>2.59</v>
+      </c>
+      <c r="U59">
+        <v>2.7</v>
+      </c>
+      <c r="V59">
+        <v>1.38</v>
+      </c>
+      <c r="W59">
+        <v>1.03</v>
+      </c>
+      <c r="X59">
+        <v>1.05</v>
+      </c>
+      <c r="Y59">
         <v>1.3</v>
       </c>
-      <c r="T59">
-        <v>3.22</v>
-      </c>
-      <c r="U59">
-        <v>2.4</v>
-      </c>
-      <c r="V59">
-        <v>1.5</v>
-      </c>
-      <c r="W59">
-        <v>1.07</v>
-      </c>
-      <c r="X59">
-        <v>1.01</v>
-      </c>
-      <c r="Y59">
-        <v>1.16</v>
-      </c>
       <c r="Z59">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE59">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF59">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG59">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AL59">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -2734,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2897,23 +2897,23 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "90+3"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3072,11 +3072,11 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -3232,14 +3232,14 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+9"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "70"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -3558,14 +3558,14 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3724,11 +3724,11 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "70"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89", "90+4"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4536,118 +4536,118 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Q26">
+        <v>2.49</v>
+      </c>
+      <c r="R26">
+        <v>1.93</v>
+      </c>
+      <c r="S26">
+        <v>1.51</v>
+      </c>
+      <c r="T26">
         <v>2.47</v>
-      </c>
-      <c r="R26">
-        <v>1.95</v>
-      </c>
-      <c r="S26">
-        <v>1.47</v>
-      </c>
-      <c r="T26">
-        <v>2.41</v>
       </c>
       <c r="U26">
         <v>3.18</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z26">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="AA26">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB26">
         <v>1.61</v>
       </c>
       <c r="AC26">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE26">
         <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG26">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK26">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4699,27 +4699,27 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="R27">
         <v>2.1</v>
@@ -4743,74 +4743,74 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC27">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AD27">
         <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG27">
         <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>["60"]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
+        <v>1.53</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>3</v>
+      </c>
+      <c r="AN27">
+        <v>4</v>
+      </c>
+      <c r="AO27">
+        <v>12</v>
+      </c>
+      <c r="AP27">
+        <v>12</v>
+      </c>
+      <c r="AQ27">
+        <v>1.34</v>
+      </c>
+      <c r="AR27">
         <v>1.57</v>
       </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
       <c r="AS27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S28">
         <v>1.19</v>
       </c>
       <c r="T28">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="U28">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V28">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W28">
         <v>1.14</v>
@@ -4912,7 +4912,7 @@
         <v>5.9</v>
       </c>
       <c r="AA28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB28">
         <v>2.7</v>
@@ -4927,53 +4927,53 @@
         <v>1.27</v>
       </c>
       <c r="AF28">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "23", "72"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "81"]</t>
         </is>
       </c>
       <c r="AJ28">
         <v>1.16</v>
       </c>
       <c r="AK28">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5025,14 +5025,14 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5199,52 +5199,52 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O30">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
-        <v>3.71</v>
+        <v>3.95</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
       </c>
       <c r="R30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
         <v>1.34</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U30">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="V30">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
         <v>1.4</v>
@@ -5253,10 +5253,10 @@
         <v>1.13</v>
       </c>
       <c r="AF30">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,65 +5362,65 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="O31">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P31">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q31">
-        <v>2.75</v>
+        <v>4.55</v>
       </c>
       <c r="R31">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="S31">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="T31">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="U31">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="V31">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W31">
         <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Y31">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="Z31">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AA31">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB31">
+        <v>1.3</v>
+      </c>
+      <c r="AC31">
+        <v>6.4</v>
+      </c>
+      <c r="AD31">
+        <v>1.05</v>
+      </c>
+      <c r="AE31">
+        <v>1.02</v>
+      </c>
+      <c r="AF31">
+        <v>2.38</v>
+      </c>
+      <c r="AG31">
         <v>1.5</v>
       </c>
-      <c r="AC31">
-        <v>5.5</v>
-      </c>
-      <c r="AD31">
-        <v>1.14</v>
-      </c>
-      <c r="AE31">
-        <v>1.04</v>
-      </c>
-      <c r="AF31">
-        <v>2.2</v>
-      </c>
-      <c r="AG31">
-        <v>1.55</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AK31">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P32">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q32">
-        <v>4.55</v>
+        <v>2.75</v>
       </c>
       <c r="R32">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="T32">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="U32">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="V32">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y32">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="Z32">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA32">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AB32">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC32">
-        <v>6.15</v>
+        <v>5.25</v>
       </c>
       <c r="AD32">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AG32">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,22 +5691,22 @@
         <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="P33">
         <v>2.38</v>
       </c>
       <c r="Q33">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="R33">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="U33">
         <v>2.78</v>
@@ -5730,7 +5730,7 @@
         <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC33">
         <v>3.2</v>
@@ -5742,7 +5742,7 @@
         <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
         <v>2</v>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="Q34">
         <v>2.85</v>
@@ -5893,7 +5893,7 @@
         <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC34">
         <v>3.35</v>
@@ -6023,10 +6023,10 @@
         <v>5.75</v>
       </c>
       <c r="Q35">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S35">
         <v>1.24</v>
@@ -6035,10 +6035,10 @@
         <v>3.44</v>
       </c>
       <c r="U35">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
         <v>1.11</v>
@@ -6050,25 +6050,25 @@
         <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA35">
         <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AC35">
         <v>2.3</v>
       </c>
       <c r="AD35">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
         <v>2.04</v>
@@ -6087,7 +6087,7 @@
         <v>1.16</v>
       </c>
       <c r="AK35">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6329,36 +6329,36 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Q37">
         <v>7</v>
       </c>
       <c r="R37">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
         <v>2.6</v>
@@ -6367,80 +6367,80 @@
         <v>1.43</v>
       </c>
       <c r="W37">
+        <v>1.04</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.27</v>
+      </c>
+      <c r="Z37">
+        <v>3.14</v>
+      </c>
+      <c r="AA37">
+        <v>1.88</v>
+      </c>
+      <c r="AB37">
+        <v>1.79</v>
+      </c>
+      <c r="AC37">
+        <v>3.16</v>
+      </c>
+      <c r="AD37">
+        <v>1.26</v>
+      </c>
+      <c r="AE37">
         <v>1.06</v>
       </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.22</v>
-      </c>
-      <c r="Z37">
-        <v>3.66</v>
-      </c>
-      <c r="AA37">
+      <c r="AF37">
+        <v>2.15</v>
+      </c>
+      <c r="AG37">
+        <v>1.62</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>["57"]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>["70", "75"]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.17</v>
+      </c>
+      <c r="AK37">
+        <v>1.05</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>3</v>
+      </c>
+      <c r="AN37">
+        <v>6</v>
+      </c>
+      <c r="AO37">
+        <v>5</v>
+      </c>
+      <c r="AP37">
+        <v>12</v>
+      </c>
+      <c r="AQ37">
+        <v>0.73</v>
+      </c>
+      <c r="AR37">
         <v>1.81</v>
       </c>
-      <c r="AB37">
-        <v>1.86</v>
-      </c>
-      <c r="AC37">
-        <v>3.13</v>
-      </c>
-      <c r="AD37">
-        <v>1.31</v>
-      </c>
-      <c r="AE37">
-        <v>1.08</v>
-      </c>
-      <c r="AF37">
-        <v>2.2</v>
-      </c>
-      <c r="AG37">
-        <v>1.57</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.15</v>
-      </c>
-      <c r="AK37">
-        <v>1.04</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>-1</v>
-      </c>
-      <c r="AN37">
-        <v>-1</v>
-      </c>
-      <c r="AO37">
-        <v>-1</v>
-      </c>
-      <c r="AP37">
-        <v>-1</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
       <c r="AS37">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
         <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P40">
         <v>1.55</v>
       </c>
       <c r="Q40">
-        <v>5.26</v>
+        <v>5.18</v>
       </c>
       <c r="R40">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="S40">
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
         <v>2.15</v>
@@ -6856,16 +6856,16 @@
         <v>1.62</v>
       </c>
       <c r="W40">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>4.7</v>
+        <v>5.66</v>
       </c>
       <c r="AA40">
         <v>1.45</v>
@@ -6874,7 +6874,7 @@
         <v>2.33</v>
       </c>
       <c r="AC40">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AD40">
         <v>1.6</v>
@@ -6883,7 +6883,7 @@
         <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
         <v>2.3</v>
@@ -6902,7 +6902,7 @@
         <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q41">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
         <v>1.36</v>
@@ -7028,13 +7028,13 @@
         <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AA41">
         <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
         <v>3.25</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7161,19 +7161,19 @@
         <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q42">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="R42">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
         <v>2.3</v>
@@ -7182,37 +7182,37 @@
         <v>1.52</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="AA42">
         <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
         <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
         <v>1.51</v>
       </c>
       <c r="AG42">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AK42">
         <v>1.33</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="O43">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>1.46</v>
+        <v>8</v>
       </c>
       <c r="Q43">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="R43">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U43">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
         <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA43">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB43">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC43">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
         <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AG43">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK43">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="O44">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P44">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q44">
-        <v>4.52</v>
+        <v>4.75</v>
       </c>
       <c r="R44">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S44">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T44">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U44">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="V44">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W44">
         <v>1.02</v>
       </c>
       <c r="X44">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y44">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z44">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA44">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AB44">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC44">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD44">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE44">
         <v>1.01</v>
       </c>
       <c r="AF44">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG44">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK44">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P45">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="R45">
         <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T45">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="U45">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>7</v>
+        <v>5.97</v>
       </c>
       <c r="AA45">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AB45">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="AC45">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AD45">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AE45">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AF45">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>2.22</v>
+        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.9</v>
+        <v>1.61</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
-        <v>1.67</v>
+        <v>3.92</v>
       </c>
       <c r="Q46">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T46">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="U46">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
       <c r="AA46">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>3.33</v>
       </c>
       <c r="AC46">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AD46">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF46">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AG46">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="AK46">
-        <v>1.2</v>
+        <v>2.14</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="R47">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S47">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T47">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U47">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="V47">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="AA47">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC47">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AD47">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AG47">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="O48">
-        <v>3.81</v>
+        <v>3.99</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q48">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="R48">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="S48">
         <v>1.21</v>
@@ -8157,40 +8157,40 @@
         <v>2.1</v>
       </c>
       <c r="V48">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W48">
         <v>1.16</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z48">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB48">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC48">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD48">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE48">
         <v>1.26</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG48">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="O49">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB49">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P50">
-        <v>4.49</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U50">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AA50">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG50">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
         <v>2</v>
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="P51">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="Q51">
         <v>2.38</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="V51">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
+        <v>1.18</v>
+      </c>
+      <c r="Z51">
+        <v>4.55</v>
+      </c>
+      <c r="AA51">
+        <v>1.57</v>
+      </c>
+      <c r="AB51">
+        <v>2.37</v>
+      </c>
+      <c r="AC51">
+        <v>2.38</v>
+      </c>
+      <c r="AD51">
+        <v>1.47</v>
+      </c>
+      <c r="AE51">
+        <v>1.16</v>
+      </c>
+      <c r="AF51">
+        <v>1.52</v>
+      </c>
+      <c r="AG51">
+        <v>2.37</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.22</v>
       </c>
-      <c r="Z51">
-        <v>4.05</v>
-      </c>
-      <c r="AA51">
-        <v>1.72</v>
-      </c>
-      <c r="AB51">
-        <v>2.1</v>
-      </c>
-      <c r="AC51">
-        <v>2.81</v>
-      </c>
-      <c r="AD51">
-        <v>1.39</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.59</v>
-      </c>
-      <c r="AG51">
-        <v>2.21</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.24</v>
-      </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,37 +8785,37 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P52">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
         <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T52">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U52">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="V52">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W52">
         <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.28</v>
@@ -8824,25 +8824,25 @@
         <v>3.4</v>
       </c>
       <c r="AA52">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
         <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>3.05</v>
+        <v>3.47</v>
       </c>
       <c r="AD52">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
         <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="Q53">
         <v>3.05</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U53">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA53">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC53">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="AD53">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG53">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P54">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q54">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="R54">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S54">
         <v>1.34</v>
@@ -9132,7 +9132,7 @@
         <v>2.99</v>
       </c>
       <c r="U54">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V54">
         <v>1.42</v>
@@ -9141,7 +9141,7 @@
         <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.21</v>
@@ -9150,22 +9150,22 @@
         <v>3.62</v>
       </c>
       <c r="AA54">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB54">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC54">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
         <v>2.1</v>
@@ -9184,7 +9184,7 @@
         <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,43 +9274,43 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O55">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="Q55">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S55">
         <v>1.33</v>
       </c>
       <c r="T55">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U55">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="V55">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>3.94</v>
+        <v>4.48</v>
       </c>
       <c r="AA55">
         <v>1.72</v>
@@ -9319,19 +9319,19 @@
         <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="AD55">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE55">
         <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG55">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9440,22 +9440,22 @@
         <v>1.25</v>
       </c>
       <c r="O56">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P56">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q56">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="R56">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S56">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U56">
         <v>2.07</v>
@@ -9470,31 +9470,31 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
         <v>5.7</v>
       </c>
       <c r="AA56">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB56">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AC56">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD56">
         <v>1.78</v>
       </c>
       <c r="AE56">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF56">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG56">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK56">
         <v>3.88</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q57">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="R57">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="U57">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W57">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z57">
-        <v>3.35</v>
+        <v>3.93</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB57">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC57">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG57">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.35</v>
       </c>
       <c r="AK57">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O58">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="Q58">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="R58">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="U58">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
+        <v>1.06</v>
+      </c>
+      <c r="Y58">
+        <v>1.31</v>
+      </c>
+      <c r="Z58">
+        <v>3.25</v>
+      </c>
+      <c r="AA58">
+        <v>2.1</v>
+      </c>
+      <c r="AB58">
+        <v>1.73</v>
+      </c>
+      <c r="AC58">
+        <v>3.8</v>
+      </c>
+      <c r="AD58">
+        <v>1.25</v>
+      </c>
+      <c r="AE58">
         <v>1.07</v>
       </c>
-      <c r="X58">
-        <v>1.01</v>
-      </c>
-      <c r="Y58">
-        <v>1.16</v>
-      </c>
-      <c r="Z58">
-        <v>4.15</v>
-      </c>
-      <c r="AA58">
-        <v>1.7</v>
-      </c>
-      <c r="AB58">
-        <v>2.1</v>
-      </c>
-      <c r="AC58">
-        <v>2.57</v>
-      </c>
-      <c r="AD58">
-        <v>1.4</v>
-      </c>
-      <c r="AE58">
-        <v>1.12</v>
-      </c>
       <c r="AF58">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O59">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q59">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="R59">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="U59">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="V59">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="W59">
+        <v>1.09</v>
+      </c>
+      <c r="X59">
         <v>1.03</v>
       </c>
-      <c r="X59">
-        <v>1.05</v>
-      </c>
       <c r="Y59">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA59">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AB59">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC59">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD59">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AE59">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AG59">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O60">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="Q60">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="R60">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S60">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T60">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U60">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="V60">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,28 +10125,28 @@
         <v>1.22</v>
       </c>
       <c r="Z60">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AA60">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB60">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC60">
         <v>2.75</v>
       </c>
       <c r="AD60">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE60">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF60">
         <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>2.85</v>
+      </c>
+      <c r="O62">
+        <v>3.65</v>
+      </c>
+      <c r="P62">
+        <v>2.35</v>
+      </c>
+      <c r="Q62">
+        <v>3.42</v>
+      </c>
+      <c r="R62">
+        <v>2.2</v>
+      </c>
+      <c r="S62">
+        <v>1.3</v>
+      </c>
+      <c r="T62">
+        <v>3.22</v>
+      </c>
+      <c r="U62">
+        <v>2.36</v>
+      </c>
+      <c r="V62">
+        <v>1.51</v>
+      </c>
+      <c r="W62">
+        <v>1.09</v>
+      </c>
+      <c r="X62">
+        <v>1.03</v>
+      </c>
+      <c r="Y62">
+        <v>1.15</v>
+      </c>
+      <c r="Z62">
+        <v>4.25</v>
+      </c>
+      <c r="AA62">
+        <v>1.66</v>
+      </c>
+      <c r="AB62">
+        <v>2.2</v>
+      </c>
+      <c r="AC62">
         <v>2.7</v>
       </c>
-      <c r="O62">
-        <v>3.5</v>
-      </c>
-      <c r="P62">
-        <v>2.45</v>
-      </c>
-      <c r="Q62">
-        <v>3.3</v>
-      </c>
-      <c r="R62">
-        <v>2.18</v>
-      </c>
-      <c r="S62">
-        <v>1.32</v>
-      </c>
-      <c r="T62">
-        <v>3.1</v>
-      </c>
-      <c r="U62">
-        <v>2.53</v>
-      </c>
-      <c r="V62">
-        <v>1.46</v>
-      </c>
-      <c r="W62">
-        <v>1.07</v>
-      </c>
-      <c r="X62">
-        <v>1</v>
-      </c>
-      <c r="Y62">
-        <v>1.18</v>
-      </c>
-      <c r="Z62">
-        <v>3.85</v>
-      </c>
-      <c r="AA62">
-        <v>1.75</v>
-      </c>
-      <c r="AB62">
-        <v>2.1</v>
-      </c>
-      <c r="AC62">
-        <v>2.9</v>
-      </c>
       <c r="AD62">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O63">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="P63">
         <v>1.61</v>
       </c>
       <c r="Q63">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="R63">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S63">
         <v>1.28</v>
@@ -10599,7 +10599,7 @@
         <v>3.34</v>
       </c>
       <c r="U63">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V63">
         <v>1.53</v>
@@ -10617,7 +10617,7 @@
         <v>4.75</v>
       </c>
       <c r="AA63">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB63">
         <v>2.38</v>
@@ -10626,16 +10626,16 @@
         <v>2.4</v>
       </c>
       <c r="AD63">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE63">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF63">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG63">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
         <v>1.14</v>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="O64">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P64">
         <v>3.3</v>
@@ -10753,52 +10753,52 @@
         <v>2.5</v>
       </c>
       <c r="R64">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>2.99</v>
+        <v>3.29</v>
       </c>
       <c r="U64">
         <v>2.5</v>
       </c>
       <c r="V64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y64">
         <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>3.62</v>
+        <v>4.35</v>
       </c>
       <c r="AA64">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB64">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC64">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL64">
         <v>0</v>

--- a/jogos_2026-09-02.xlsx
+++ b/jogos_2026-09-02.xlsx
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5191,11 +5191,11 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5354,11 +5354,11 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68", "90+6"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "63"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5677,14 +5677,14 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ33">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,26 +5828,26 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "71"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "45+1"]</t>
         </is>
       </c>
       <c r="AJ34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,26 +5991,26 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "66"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "90+6"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6480,26 +6480,26 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "76"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6821,11 +6821,11 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81", "84"]</t>
         </is>
       </c>
       <c r="AJ40">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,26 +6969,26 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7135,23 +7135,23 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "56"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,26 +7295,26 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "50"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -7470,14 +7470,14 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90", "90+5"]</t>
         </is>
       </c>
       <c r="AJ44">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,26 +7621,26 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "69"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -7796,14 +7796,14 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "90+1"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46"]</t>
         </is>
       </c>
       <c r="AJ46">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,26 +8110,26 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "15", "21", "46", "90"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ48">
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8276,23 +8276,23 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "55", "63"]</t>
         </is>
       </c>
       <c r="AJ49">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8427,139 +8427,139 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="O50">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="U50">
-        <v>2.91</v>
+        <v>2.31</v>
       </c>
       <c r="V50">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>3.24</v>
+        <v>4.55</v>
       </c>
       <c r="AA50">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AC50">
+        <v>2.38</v>
+      </c>
+      <c r="AD50">
+        <v>1.47</v>
+      </c>
+      <c r="AE50">
+        <v>1.16</v>
+      </c>
+      <c r="AF50">
+        <v>1.52</v>
+      </c>
+      <c r="AG50">
+        <v>2.37</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>["36", "53"]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>["74"]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.22</v>
+      </c>
+      <c r="AK50">
+        <v>1.88</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>4</v>
+      </c>
+      <c r="AN50">
         <v>3</v>
       </c>
-      <c r="AD50">
-        <v>1.28</v>
-      </c>
-      <c r="AE50">
-        <v>1.12</v>
-      </c>
-      <c r="AF50">
-        <v>1.84</v>
-      </c>
-      <c r="AG50">
-        <v>1.9</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.15</v>
-      </c>
-      <c r="AK50">
-        <v>2</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8590,19 +8590,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -8611,118 +8611,118 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="O51">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P51">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R51">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="U51">
-        <v>2.31</v>
+        <v>2.91</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>4.55</v>
+        <v>3.24</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AB51">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AD51">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="AG51">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK51">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8765,23 +8765,23 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "52", "69"]</t>
         </is>
       </c>
       <c r="AJ52">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8916,139 +8916,139 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>2.41</v>
+        <v>3.08</v>
       </c>
       <c r="Q53">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="R53">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U53">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="V53">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="AA53">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AC53">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="AD53">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
+          <t>["19", "65", "67"]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ53">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK53">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL53">
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9079,25 +9079,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -9107,68 +9107,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="O54">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="Q54">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="R54">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S54">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U54">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="V54">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.62</v>
+        <v>4.65</v>
       </c>
       <c r="AA54">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AB54">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="AC54">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="AD54">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG54">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9177,41 +9177,41 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AJ54">
         <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL54">
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -9242,19 +9242,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -9263,118 +9263,118 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P55">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q55">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="R55">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U55">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z55">
-        <v>4.48</v>
+        <v>3.62</v>
       </c>
       <c r="AA55">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB55">
+        <v>1.97</v>
+      </c>
+      <c r="AC55">
+        <v>2.89</v>
+      </c>
+      <c r="AD55">
+        <v>1.32</v>
+      </c>
+      <c r="AE55">
+        <v>1.08</v>
+      </c>
+      <c r="AF55">
+        <v>1.62</v>
+      </c>
+      <c r="AG55">
         <v>2.1</v>
       </c>
-      <c r="AC55">
-        <v>2.57</v>
-      </c>
-      <c r="AD55">
-        <v>1.4</v>
-      </c>
-      <c r="AE55">
-        <v>1.13</v>
-      </c>
-      <c r="AF55">
-        <v>1.57</v>
-      </c>
-      <c r="AG55">
-        <v>2.25</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ55">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "34", "45+1"]</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
@@ -9516,28 +9516,28 @@
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -9577,26 +9577,26 @@
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N57">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "48", "74"]</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ57">
@@ -9679,28 +9679,28 @@
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN57">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO57">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP57">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
@@ -9731,16 +9731,16 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -9752,118 +9752,118 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N58">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q58">
-        <v>2.77</v>
+        <v>3.26</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>2.57</v>
+        <v>3.34</v>
       </c>
       <c r="U58">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W58">
+        <v>1.09</v>
+      </c>
+      <c r="X58">
         <v>1.03</v>
       </c>
-      <c r="X58">
-        <v>1.06</v>
-      </c>
       <c r="Y58">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z58">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA58">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AB58">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AE58">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
+          <t>["50", "76"]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK58">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AL58">
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN58">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO58">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP58">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
@@ -9894,139 +9894,139 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P59">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q59">
-        <v>3.26</v>
+        <v>2.77</v>
       </c>
       <c r="R59">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S59">
+        <v>1.44</v>
+      </c>
+      <c r="T59">
+        <v>2.57</v>
+      </c>
+      <c r="U59">
+        <v>2.7</v>
+      </c>
+      <c r="V59">
+        <v>1.4</v>
+      </c>
+      <c r="W59">
+        <v>1.03</v>
+      </c>
+      <c r="X59">
+        <v>1.06</v>
+      </c>
+      <c r="Y59">
+        <v>1.31</v>
+      </c>
+      <c r="Z59">
+        <v>3.25</v>
+      </c>
+      <c r="AA59">
+        <v>2.1</v>
+      </c>
+      <c r="AB59">
+        <v>1.73</v>
+      </c>
+      <c r="AC59">
+        <v>3.8</v>
+      </c>
+      <c r="AD59">
         <v>1.25</v>
       </c>
-      <c r="T59">
-        <v>3.34</v>
-      </c>
-      <c r="U59">
-        <v>2.33</v>
-      </c>
-      <c r="V59">
-        <v>1.53</v>
-      </c>
-      <c r="W59">
-        <v>1.09</v>
-      </c>
-      <c r="X59">
-        <v>1.03</v>
-      </c>
-      <c r="Y59">
-        <v>1.13</v>
-      </c>
-      <c r="Z59">
-        <v>4.6</v>
-      </c>
-      <c r="AA59">
-        <v>1.59</v>
-      </c>
-      <c r="AB59">
-        <v>2.35</v>
-      </c>
-      <c r="AC59">
-        <v>2.38</v>
-      </c>
-      <c r="AD59">
-        <v>1.47</v>
-      </c>
       <c r="AE59">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF59">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AG59">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "34", "46", "76"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK59">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -10078,14 +10078,14 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
@@ -10150,12 +10150,12 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "87"]</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ60">
@@ -10168,28 +10168,28 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10229,42 +10229,42 @@
         </is>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O61">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>5.77</v>
+        <v>5.4</v>
       </c>
       <c r="Q61">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R61">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S61">
         <v>1.39</v>
@@ -10273,7 +10273,7 @@
         <v>2.66</v>
       </c>
       <c r="U61">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V61">
         <v>1.35</v>
@@ -10288,13 +10288,13 @@
         <v>1.28</v>
       </c>
       <c r="Z61">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA61">
         <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC61">
         <v>3.31</v>
@@ -10303,56 +10303,56 @@
         <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF61">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG61">
         <v>1.67</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "61", "80", "89"]</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "55", "85"]</t>
         </is>
       </c>
       <c r="AJ61">
         <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN61">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO61">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP61">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
@@ -10392,26 +10392,26 @@
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AJ62">
@@ -10494,28 +10494,28 @@
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN62">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO62">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP62">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR62">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS62">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT62">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -10555,26 +10555,26 @@
         </is>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N63">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "79"]</t>
         </is>
       </c>
       <c r="AJ63">
@@ -10657,28 +10657,28 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN63">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO63">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP63">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -10718,26 +10718,26 @@
         </is>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N64">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "40", "44", "58", "80"]</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
@@ -10820,28 +10820,28 @@
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN64">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO64">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP64">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ64">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR64">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS64">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -10904,37 +10904,37 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q65">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S65">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T65">
         <v>2.53</v>
       </c>
       <c r="U65">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="V65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W65">
         <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.4</v>
@@ -10943,25 +10943,25 @@
         <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB65">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC65">
         <v>4.33</v>
       </c>
       <c r="AD65">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG65">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
-        <v>4.74</v>
+        <v>5.27</v>
       </c>
       <c r="Q66">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="R66">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S66">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="U66">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="V66">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="W66">
+        <v>1.05</v>
+      </c>
+      <c r="X66">
+        <v>1.04</v>
+      </c>
+      <c r="Y66">
+        <v>1.38</v>
+      </c>
+      <c r="Z66">
+        <v>3.1</v>
+      </c>
+      <c r="AA66">
+        <v>2.2</v>
+      </c>
+      <c r="AB66">
+        <v>1.65</v>
+      </c>
+      <c r="AC66">
+        <v>3.5</v>
+      </c>
+      <c r="AD66">
+        <v>1.27</v>
+      </c>
+      <c r="AE66">
         <v>1.09</v>
       </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.26</v>
-      </c>
-      <c r="Z66">
-        <v>3.95</v>
-      </c>
-      <c r="AA66">
-        <v>1.64</v>
-      </c>
-      <c r="AB66">
+      <c r="AF66">
         <v>2</v>
       </c>
-      <c r="AC66">
-        <v>2.95</v>
-      </c>
-      <c r="AD66">
-        <v>1.36</v>
-      </c>
-      <c r="AE66">
-        <v>1.11</v>
-      </c>
-      <c r="AF66">
-        <v>1.78</v>
-      </c>
       <c r="AG66">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,65 +11230,65 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="O67">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="P67">
         <v>14</v>
       </c>
       <c r="Q67">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R67">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="S67">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U67">
+        <v>2.15</v>
+      </c>
+      <c r="V67">
+        <v>1.6</v>
+      </c>
+      <c r="W67">
+        <v>1.14</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.1</v>
+      </c>
+      <c r="Z67">
+        <v>5</v>
+      </c>
+      <c r="AA67">
+        <v>1.46</v>
+      </c>
+      <c r="AB67">
+        <v>2.39</v>
+      </c>
+      <c r="AC67">
+        <v>2.38</v>
+      </c>
+      <c r="AD67">
+        <v>1.63</v>
+      </c>
+      <c r="AE67">
+        <v>1.19</v>
+      </c>
+      <c r="AF67">
         <v>2.2</v>
       </c>
-      <c r="V67">
+      <c r="AG67">
         <v>1.58</v>
       </c>
-      <c r="W67">
-        <v>1.1</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.2</v>
-      </c>
-      <c r="Z67">
-        <v>4.5</v>
-      </c>
-      <c r="AA67">
-        <v>1.57</v>
-      </c>
-      <c r="AB67">
-        <v>2.35</v>
-      </c>
-      <c r="AC67">
-        <v>2.45</v>
-      </c>
-      <c r="AD67">
-        <v>1.53</v>
-      </c>
-      <c r="AE67">
-        <v>1.18</v>
-      </c>
-      <c r="AF67">
-        <v>2</v>
-      </c>
-      <c r="AG67">
-        <v>1.66</v>
-      </c>
       <c r="AH67" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK67">
-        <v>4.24</v>
+        <v>4.9</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O68">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="Q68">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R68">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
         <v>1.29</v>
       </c>
       <c r="T68">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U68">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V68">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
         <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z68">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="AA68">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AB68">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC68">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD68">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG68">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="O72">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
         <v>2.08</v>
       </c>
       <c r="Q72">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="R72">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S72">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T72">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U72">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V72">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W72">
+        <v>1.04</v>
+      </c>
+      <c r="X72">
+        <v>1.02</v>
+      </c>
+      <c r="Y72">
+        <v>1.31</v>
+      </c>
+      <c r="Z72">
+        <v>3.42</v>
+      </c>
+      <c r="AA72">
+        <v>2</v>
+      </c>
+      <c r="AB72">
+        <v>1.8</v>
+      </c>
+      <c r="AC72">
+        <v>3.24</v>
+      </c>
+      <c r="AD72">
+        <v>1.27</v>
+      </c>
+      <c r="AE72">
         <v>1.06</v>
       </c>
-      <c r="X72">
-        <v>1.03</v>
-      </c>
-      <c r="Y72">
-        <v>1.35</v>
-      </c>
-      <c r="Z72">
-        <v>3.15</v>
-      </c>
-      <c r="AA72">
-        <v>2.1</v>
-      </c>
-      <c r="AB72">
+      <c r="AF72">
         <v>1.75</v>
       </c>
-      <c r="AC72">
-        <v>2.88</v>
-      </c>
-      <c r="AD72">
-        <v>1.24</v>
-      </c>
-      <c r="AE72">
-        <v>1.05</v>
-      </c>
-      <c r="AF72">
-        <v>1.8</v>
-      </c>
       <c r="AG72">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P73">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q73">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="R73">
         <v>2.2</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T73">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U73">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V73">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W73">
         <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
         <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB73">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AC73">
         <v>2.78</v>
       </c>
       <c r="AD73">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG73">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK73">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AL73">
         <v>0</v>
